--- a/supplementary_materials/combined_sensitivity_analisys_second_level.xlsx
+++ b/supplementary_materials/combined_sensitivity_analisys_second_level.xlsx
@@ -483,7345 +483,7345 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_100_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_100_2ndlvl</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.024647845144196</v>
+        <v>-0.0038572304519327</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5027168902258088</v>
+        <v>0.8932996679582891</v>
       </c>
       <c r="D2" t="n">
-        <v>1.955983651056102</v>
+        <v>-0.2212460692301397</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0511541268458263</v>
+        <v>0.8250134547951321</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0791133294232102</v>
+        <v>0.1123540490488252</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06547056393318371</v>
+        <v>0.0990725634984337</v>
       </c>
       <c r="H2" t="n">
-        <v>686.377968827939</v>
+        <v>935.4216761568116</v>
       </c>
       <c r="I2" t="n">
-        <v>714.5251322733857</v>
+        <v>963.5005463776406</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4811221409359504</v>
+        <v>0.9428725197658652</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_24_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_24_2ndlvl</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0057222063413987</v>
+        <v>0.0080237313026865</v>
       </c>
       <c r="C3" t="n">
-        <v>0.511790491334873</v>
+        <v>0.8772808142370321</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4666534198209197</v>
+        <v>0.478771307090056</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6409987804070758</v>
+        <v>0.6323622793764629</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0709136462300512</v>
+        <v>0.1127528680469751</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0571494039519778</v>
+        <v>0.0994773498631393</v>
       </c>
       <c r="H3" t="n">
-        <v>690.030229216597</v>
+        <v>935.2383207135445</v>
       </c>
       <c r="I3" t="n">
-        <v>718.1773926620438</v>
+        <v>963.3171909343736</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9324022592583854</v>
+        <v>0.9922579936011444</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_25_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_25_2ndlvl</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0070401645443442</v>
+        <v>0.0284805265131022</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5148706037722927</v>
+        <v>0.86556295138228</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4964026793335317</v>
+        <v>1.471966328957378</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6198796422306052</v>
+        <v>0.1418143344993712</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0709793309942664</v>
+        <v>0.1170166340620068</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0572160618238111</v>
+        <v>0.1038049128759022</v>
       </c>
       <c r="H4" t="n">
-        <v>690.0011005146049</v>
+        <v>933.2729044581548</v>
       </c>
       <c r="I4" t="n">
-        <v>718.1482639600516</v>
+        <v>961.351774678984</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9324022592583854</v>
+        <v>0.9922579936011444</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_26_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_26_2ndlvl</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.0012047620623082</v>
+        <v>-0.0023346546267025</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5237549906406709</v>
+        <v>0.8955497997283608</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0848755630569954</v>
+        <v>-0.1202731340755509</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9324022592583854</v>
+        <v>0.9043270225006066</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0704306181167724</v>
+        <v>0.1122777182430745</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0566592198666505</v>
+        <v>0.0989950905858637</v>
       </c>
       <c r="H5" t="n">
-        <v>690.2443706343256</v>
+        <v>935.4567595476168</v>
       </c>
       <c r="I5" t="n">
-        <v>718.3915340797723</v>
+        <v>963.5356297684458</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9324022592583854</v>
+        <v>0.9922579936011444</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_27_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_27_2ndlvl</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0035980694083375</v>
+        <v>0.008599228790475401</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5196592541417038</v>
+        <v>0.886791266759646</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2637376111289141</v>
+        <v>0.4620425489444966</v>
       </c>
       <c r="E6" t="n">
-        <v>0.792116250900699</v>
+        <v>0.644301379630833</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0705737097364259</v>
+        <v>0.1127180634593972</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0568044313621507</v>
+        <v>0.0994420245086651</v>
       </c>
       <c r="H6" t="n">
-        <v>690.1809452608327</v>
+        <v>935.2543252659476</v>
       </c>
       <c r="I6" t="n">
-        <v>718.3281087062794</v>
+        <v>963.3331954867766</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9324022592583854</v>
+        <v>0.9922579936011444</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_28_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_28_2ndlvl</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0134534670954401</v>
+        <v>-0.0001711414895674</v>
       </c>
       <c r="C7" t="n">
-        <v>0.537787512515564</v>
+        <v>0.8905628668160502</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.044538593956834</v>
+        <v>-0.009709370237775201</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2968593183675831</v>
+        <v>0.9922579936011444</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07291163873198089</v>
+        <v>0.112245903357854</v>
       </c>
       <c r="G7" t="n">
-        <v>0.059176996342825</v>
+        <v>0.09896279966744791</v>
       </c>
       <c r="H7" t="n">
-        <v>689.1432725933355</v>
+        <v>935.471381508606</v>
       </c>
       <c r="I7" t="n">
-        <v>717.2904360387822</v>
+        <v>963.5502517294352</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9324022592583854</v>
+        <v>0.9922579936011444</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_29_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_29_2ndlvl</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.0064563592500148</v>
+        <v>0.020521364651621</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5285681753276563</v>
+        <v>0.8703628376960153</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5039621733545689</v>
+        <v>1.174372320613938</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6145619870114728</v>
+        <v>0.2409428641548262</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0709966670080006</v>
+        <v>0.1152884632904822</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0572336546673784</v>
+        <v>0.1020508841875967</v>
       </c>
       <c r="H8" t="n">
-        <v>689.9934123064321</v>
+        <v>934.0706596571596</v>
       </c>
       <c r="I8" t="n">
-        <v>718.1405757518788</v>
+        <v>962.1495298779888</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9324022592583854</v>
+        <v>0.9922579936011444</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_30_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_30_2ndlvl</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0043484397062561</v>
+        <v>-0.014502116816046</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5228404549024631</v>
+        <v>0.8828715442587258</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3043455644470089</v>
+        <v>-0.7442132342559751</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7610209519001698</v>
+        <v>0.4571833558275695</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0706266375121901</v>
+        <v>0.1134701522984624</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0568581432531114</v>
+        <v>0.1002053665473172</v>
       </c>
       <c r="H9" t="n">
-        <v>690.1574825454309</v>
+        <v>934.9083446298368</v>
       </c>
       <c r="I9" t="n">
-        <v>718.3046459908776</v>
+        <v>962.987214850666</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9324022592583854</v>
+        <v>0.9922579936011444</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_38_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_38_2ndlvl</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0003790817636868</v>
+        <v>0.025503178616369</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5217063260814301</v>
+        <v>0.8556326659290885</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0299175190952517</v>
+        <v>1.479327061170157</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9761475709253064</v>
+        <v>0.1398380503372596</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07041613797508819</v>
+        <v>0.1170642089623956</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0566445252043488</v>
+        <v>0.1038531996201871</v>
       </c>
       <c r="H10" t="n">
-        <v>690.2507884144558</v>
+        <v>933.2509209383696</v>
       </c>
       <c r="I10" t="n">
-        <v>718.3979518599025</v>
+        <v>961.3297911591987</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9929661489661934</v>
+        <v>0.5950176078921831</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_39_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_39_2ndlvl</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.0239039240701155</v>
+        <v>4.913138615019862e-05</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5275797394654775</v>
+        <v>0.8903673220899138</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.839332829956642</v>
+        <v>0.0027628968874658</v>
       </c>
       <c r="E11" t="n">
-        <v>0.06659804710753831</v>
+        <v>0.9977969039701472</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0781149993043484</v>
+        <v>0.1122457115536678</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0644574437384868</v>
+        <v>0.0989626049933736</v>
       </c>
       <c r="H11" t="n">
-        <v>686.8243747018981</v>
+        <v>935.4714696592548</v>
       </c>
       <c r="I11" t="n">
-        <v>714.9715381473449</v>
+        <v>963.550339880084</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4811221409359504</v>
+        <v>0.9977969039701472</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_40_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_40_2ndlvl</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.0046369750660791</v>
+        <v>0.0114732523926168</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5206722297824504</v>
+        <v>0.8921801421230513</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3314566985985991</v>
+        <v>0.6019507215291214</v>
       </c>
       <c r="E12" t="n">
-        <v>0.740470986027316</v>
+        <v>0.5475471257211687</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0706661821096095</v>
+        <v>0.1130471476206503</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0568982736964185</v>
+        <v>0.0997760326224557</v>
       </c>
       <c r="H12" t="n">
-        <v>690.1399516784809</v>
+        <v>935.1029740015384</v>
       </c>
       <c r="I12" t="n">
-        <v>718.2871151239276</v>
+        <v>963.1818442223674</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9929661489661934</v>
+        <v>0.8683563875042806</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_41_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_41_2ndlvl</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0008434009952656</v>
+        <v>0.0287199546408428</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5196834538601438</v>
+        <v>0.8372715377059197</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0660813947827547</v>
+        <v>1.657286832251331</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9473456304809492</v>
+        <v>0.0982436014070463</v>
       </c>
       <c r="F13" t="n">
-        <v>0.07042410635729419</v>
+        <v>0.1182848926596076</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0566526116366615</v>
+        <v>0.1050921479113723</v>
       </c>
       <c r="H13" t="n">
-        <v>690.2472567400434</v>
+        <v>932.6864591194808</v>
       </c>
       <c r="I13" t="n">
-        <v>718.3944201854902</v>
+        <v>960.76532934031</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9929661489661934</v>
+        <v>0.5950176078921831</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_42_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_42_2ndlvl</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.0122005870556071</v>
+        <v>0.0273504324244424</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5398374625501409</v>
+        <v>0.8484629041823071</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.8780028631877118</v>
+        <v>1.446727745720304</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3804627268954597</v>
+        <v>0.1487544019730457</v>
       </c>
       <c r="F14" t="n">
-        <v>0.07218012348403779</v>
+        <v>0.1168552722390205</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0584346438319494</v>
+        <v>0.1036411366615496</v>
       </c>
       <c r="H14" t="n">
-        <v>689.468231307344</v>
+        <v>933.3474580810732</v>
       </c>
       <c r="I14" t="n">
-        <v>717.6153947527907</v>
+        <v>961.4263283019023</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9929661489661934</v>
+        <v>0.5950176078921831</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_43_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_43_2ndlvl</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.0248666033633084</v>
+        <v>0.0189542519242571</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5533720542440781</v>
+        <v>0.8673968641625807</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.75399894949658</v>
+        <v>0.9779129723079256</v>
       </c>
       <c r="E15" t="n">
-        <v>0.08018702348932499</v>
+        <v>0.3287069539649605</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0774222853065013</v>
+        <v>0.1143577940230242</v>
       </c>
       <c r="G15" t="n">
-        <v>0.06375446731104201</v>
+        <v>0.1011062896941917</v>
       </c>
       <c r="H15" t="n">
-        <v>687.1338395429602</v>
+        <v>934.4996282716756</v>
       </c>
       <c r="I15" t="n">
-        <v>715.281002988407</v>
+        <v>962.5784984925048</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4811221409359504</v>
+        <v>0.8683563875042806</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_44_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_44_2ndlvl</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.0006851432653134</v>
+        <v>0.0135112981198865</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5223730370051598</v>
+        <v>0.8657568698884918</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0464833536206249</v>
+        <v>0.6721959568424474</v>
       </c>
       <c r="E16" t="n">
-        <v>0.96294791326166</v>
+        <v>0.5018460656394242</v>
       </c>
       <c r="F16" t="n">
-        <v>0.07041904295326271</v>
+        <v>0.1132448916466435</v>
       </c>
       <c r="G16" t="n">
-        <v>0.056647473219237</v>
+        <v>0.0999767354119299</v>
       </c>
       <c r="H16" t="n">
-        <v>690.249500899766</v>
+        <v>935.0120012318088</v>
       </c>
       <c r="I16" t="n">
-        <v>718.3966643452127</v>
+        <v>963.090871452638</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9929661489661934</v>
+        <v>0.8683563875042806</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_45_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_45_2ndlvl</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0187650724681327</v>
+        <v>0.012604825598227</v>
       </c>
       <c r="C17" t="n">
-        <v>0.49522356622056</v>
+        <v>0.8721769398384105</v>
       </c>
       <c r="D17" t="n">
-        <v>1.337390018365652</v>
+        <v>0.6528010605805854</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1818459525137652</v>
+        <v>0.5142586063169917</v>
       </c>
       <c r="F17" t="n">
-        <v>0.074501387234382</v>
+        <v>0.1131881240639423</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0607902966748914</v>
+        <v>0.09991911843896389</v>
       </c>
       <c r="H17" t="n">
-        <v>688.4361786183272</v>
+        <v>935.0381194150576</v>
       </c>
       <c r="I17" t="n">
-        <v>716.5833420637739</v>
+        <v>963.1169896358869</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7783221777550435</v>
+        <v>0.8683563875042806</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_46_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_46_2ndlvl</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.0164391797576862</v>
+        <v>-0.0060597550490769</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5449108581779227</v>
+        <v>0.8994762081256813</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.157055179469588</v>
+        <v>-0.312598989782396</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2479317922988837</v>
+        <v>0.7547478438775631</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0734768184817452</v>
+        <v>0.1124619753389662</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0597505491259192</v>
+        <v>0.09918210464578379</v>
       </c>
       <c r="H18" t="n">
-        <v>688.8920289441198</v>
+        <v>935.3720656071032</v>
       </c>
       <c r="I18" t="n">
-        <v>717.0391923895666</v>
+        <v>963.4509358279324</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7783221777550435</v>
+        <v>0.9056974126530756</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_47_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_47_2ndlvl</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.0034799209654855</v>
+        <v>0.009449511090667899</v>
       </c>
       <c r="C19" t="n">
-        <v>0.528377116053707</v>
+        <v>0.8706354201104238</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2428244182775704</v>
+        <v>0.4833730467651964</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8082643475256435</v>
+        <v>0.6290947027202682</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0705494017110454</v>
+        <v>0.1127626586521766</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0567797632178757</v>
+        <v>0.0994872869611868</v>
       </c>
       <c r="H19" t="n">
-        <v>690.1917204837849</v>
+        <v>935.2338184854524</v>
       </c>
       <c r="I19" t="n">
-        <v>718.3388839292317</v>
+        <v>963.3126887062816</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9929661489661934</v>
+        <v>0.8683563875042806</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_48_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_48_2ndlvl</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0153024017910349</v>
+        <v>0.0147125777424376</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5021434826916346</v>
+        <v>0.8744221401987277</v>
       </c>
       <c r="D20" t="n">
-        <v>1.194490448346037</v>
+        <v>0.8331742049971493</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2329852551465099</v>
+        <v>0.405242458915532</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07367750043098641</v>
+        <v>0.1137798483831645</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0599542041410751</v>
+        <v>0.1005196964886483</v>
       </c>
       <c r="H20" t="n">
-        <v>688.8027813999184</v>
+        <v>934.7657909658768</v>
       </c>
       <c r="I20" t="n">
-        <v>716.9499448453652</v>
+        <v>962.844661186706</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7783221777550435</v>
+        <v>0.8683563875042806</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_49_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_49_2ndlvl</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0031397796942068</v>
+        <v>0.0011207143345709</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5143581723172401</v>
+        <v>0.8880836092277433</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2592165201861327</v>
+        <v>0.0674558511232236</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7955998892474082</v>
+        <v>0.9462524280148944</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0705682847991189</v>
+        <v>0.1122557682084883</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0567989260554021</v>
+        <v>0.0989728121218324</v>
       </c>
       <c r="H21" t="n">
-        <v>690.1833500428698</v>
+        <v>935.466847728997</v>
       </c>
       <c r="I21" t="n">
-        <v>718.3305134883166</v>
+        <v>963.545717949826</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9929661489661934</v>
+        <v>0.9873938379285851</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_50_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_50_2ndlvl</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0247101895606952</v>
+        <v>0.0291201016876674</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4643233731179515</v>
+        <v>0.8235583758977909</v>
       </c>
       <c r="D22" t="n">
-        <v>1.895280502462797</v>
+        <v>1.631690712453917</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0587670590624542</v>
+        <v>0.1035296929891241</v>
       </c>
       <c r="F22" t="n">
-        <v>0.07858642631650541</v>
+        <v>0.1181010082071677</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0649358548545278</v>
+        <v>0.1049055120706167</v>
       </c>
       <c r="H22" t="n">
-        <v>686.6136351766331</v>
+        <v>932.77153992815</v>
       </c>
       <c r="I22" t="n">
-        <v>714.7607986220798</v>
+        <v>960.8504101489792</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4811221409359504</v>
+        <v>0.5950176078921831</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_74_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_74_2ndlvl</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0046186278721734</v>
+        <v>-0.0046712210989891</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5103934695899218</v>
+        <v>0.9002216793700021</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3856572902855393</v>
+        <v>-0.2841489657448428</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6999529846006119</v>
+        <v>0.7764428884359384</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0707553378846341</v>
+        <v>0.11242440641661</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0569887502977398</v>
+        <v>0.09914397359491341</v>
       </c>
       <c r="H23" t="n">
-        <v>690.1004245024874</v>
+        <v>935.3893356231364</v>
       </c>
       <c r="I23" t="n">
-        <v>718.2475879479341</v>
+        <v>963.4682058439654</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9324022592583854</v>
+        <v>0.9922579936011444</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_75_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_75_2ndlvl</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0086788117843704</v>
+        <v>-0.0022524871307646</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5055117490047351</v>
+        <v>0.8941033115454261</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6589428661749043</v>
+        <v>-0.1246239882643744</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5103069156235103</v>
+        <v>0.9008836848817604</v>
       </c>
       <c r="F24" t="n">
-        <v>0.07140963722910131</v>
+        <v>0.1122800769508497</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0576527429658286</v>
+        <v>0.0989974845860245</v>
       </c>
       <c r="H24" t="n">
-        <v>689.8102250634041</v>
+        <v>935.4556754765388</v>
       </c>
       <c r="I24" t="n">
-        <v>717.9573885088508</v>
+        <v>963.534545697368</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9324022592583854</v>
+        <v>0.9922579936011444</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_76_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_76_2ndlvl</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0015894035900994</v>
+        <v>-0.0033566438117758</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5180129968521296</v>
+        <v>0.8965901181480816</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1372480629246145</v>
+        <v>-0.2112591828451385</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8909029255344022</v>
+        <v>0.8327923518781347</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0704573177101246</v>
+        <v>0.1123444888138824</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0566863150095339</v>
+        <v>0.0990628602175814</v>
       </c>
       <c r="H25" t="n">
-        <v>690.2325367780736</v>
+        <v>935.4260704255483</v>
       </c>
       <c r="I25" t="n">
-        <v>718.3797002235203</v>
+        <v>963.5049406463776</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9324022592583854</v>
+        <v>0.9922579936011444</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_77_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_77_2ndlvl</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.001280396126554</v>
+        <v>0.0219683626532696</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5194342100684712</v>
+        <v>0.8599983747924133</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0874448974248319</v>
+        <v>1.096419167517439</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9303611017940731</v>
+        <v>0.2735533868042165</v>
       </c>
       <c r="F26" t="n">
-        <v>0.07043163430944779</v>
+        <v>0.1148990881120151</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0566602511140322</v>
+        <v>0.1016556829466088</v>
       </c>
       <c r="H26" t="n">
-        <v>690.2439202412518</v>
+        <v>934.2501872398748</v>
       </c>
       <c r="I26" t="n">
-        <v>718.3910836866985</v>
+        <v>962.329057460704</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9324022592583854</v>
+        <v>0.9922579936011444</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_78_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_78_2ndlvl</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0148203468420709</v>
+        <v>-0.0014945757231057</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4803123634491497</v>
+        <v>0.8943621838581595</v>
       </c>
       <c r="D27" t="n">
-        <v>1.25880224205656</v>
+        <v>-0.0927711180965522</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2088268716505296</v>
+        <v>0.9261317267155944</v>
       </c>
       <c r="F27" t="n">
-        <v>0.07403696102965281</v>
+        <v>0.1122647477113908</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0603189900819439</v>
+        <v>0.09898192598138671</v>
       </c>
       <c r="H27" t="n">
-        <v>688.6428732589452</v>
+        <v>935.4627208019136</v>
       </c>
       <c r="I27" t="n">
-        <v>716.7900367043919</v>
+        <v>963.5415910227428</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9324022592583854</v>
+        <v>0.9922579936011444</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_90_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_90_2ndlvl</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0069563118857936</v>
+        <v>-0.0027547916145776</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5191388284001226</v>
+        <v>0.889191319832829</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5533079583820192</v>
+        <v>-0.1605949114791218</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5803578550499333</v>
+        <v>0.8724933329532866</v>
       </c>
       <c r="F28" t="n">
-        <v>0.07111625018978041</v>
+        <v>0.1123027878091511</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0573550094518512</v>
+        <v>0.0990205352576671</v>
       </c>
       <c r="H28" t="n">
-        <v>689.9403754223099</v>
+        <v>935.4452373321686</v>
       </c>
       <c r="I28" t="n">
-        <v>718.0875388677566</v>
+        <v>963.5241075529976</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9929661489661934</v>
+        <v>0.9518109086763128</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_91_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_91_2ndlvl</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.000109398192534</v>
+        <v>-0.0085393982536364</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5211343726660529</v>
+        <v>0.8936311440704874</v>
       </c>
       <c r="D29" t="n">
-        <v>0.008821183040567501</v>
+        <v>-0.5053886954087304</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9929661489661934</v>
+        <v>0.6135635198817055</v>
       </c>
       <c r="F29" t="n">
-        <v>0.07041426217923979</v>
+        <v>0.1128107915536665</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0566426216189323</v>
+        <v>0.0995361400557165</v>
       </c>
       <c r="H29" t="n">
-        <v>690.2516197833525</v>
+        <v>935.2116837582475</v>
       </c>
       <c r="I29" t="n">
-        <v>718.3987832287992</v>
+        <v>963.2905539790768</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9929661489661934</v>
+        <v>0.8683563875042806</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_92_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_92_2ndlvl</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0105580356850958</v>
+        <v>0.008924579207477201</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5165142394478415</v>
+        <v>0.893626772753163</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7756709172039303</v>
+        <v>0.4798773534122432</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4383960091032947</v>
+        <v>0.6315762431907295</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0717930218397639</v>
+        <v>0.1127552127275566</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0580418073485011</v>
+        <v>0.0994797296262233</v>
       </c>
       <c r="H30" t="n">
-        <v>689.6400886049378</v>
+        <v>935.2372425123234</v>
       </c>
       <c r="I30" t="n">
-        <v>717.7872520503845</v>
+        <v>963.3161127331524</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9929661489661934</v>
+        <v>0.8683563875042806</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_93_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_93_2ndlvl</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0061037515995802</v>
+        <v>0.0132286757788023</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5303721445787234</v>
+        <v>0.8707495878111482</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4732464958864198</v>
+        <v>0.7534517481901869</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6362922970169138</v>
+        <v>0.4516206380397105</v>
       </c>
       <c r="F31" t="n">
-        <v>0.07092785415516931</v>
+        <v>0.1135006980907226</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0571638223648754</v>
+        <v>0.1002363693838506</v>
       </c>
       <c r="H31" t="n">
-        <v>690.0239287151596</v>
+        <v>934.8942865606324</v>
       </c>
       <c r="I31" t="n">
-        <v>718.1710921606063</v>
+        <v>962.9731567814614</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9929661489661934</v>
+        <v>0.8683563875042806</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_94_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_94_2ndlvl</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0027182537179275</v>
+        <v>0.0109835752351736</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5241408929084311</v>
+        <v>0.8789677370598206</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1996221211704479</v>
+        <v>0.5912453595939814</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8418763130610271</v>
+        <v>0.5546891595579231</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0705055389262767</v>
+        <v>0.1130189189189343</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0567352506140734</v>
+        <v>0.0997473815461503</v>
       </c>
       <c r="H32" t="n">
-        <v>690.2111631964535</v>
+        <v>935.1159590514141</v>
       </c>
       <c r="I32" t="n">
-        <v>718.3583266419002</v>
+        <v>963.1948292722432</v>
       </c>
       <c r="J32" t="n">
-        <v>0.9929661489661934</v>
+        <v>0.8683563875042806</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_95_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_95_2ndlvl</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.0023227011785764</v>
+        <v>0.007783647011611</v>
       </c>
       <c r="C33" t="n">
-        <v>0.526605668396221</v>
+        <v>0.8730462817238782</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1842469191251531</v>
+        <v>0.4523419077191039</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8539119710365068</v>
+        <v>0.6512672906282104</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0704919945409524</v>
+        <v>0.1126984468023374</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0567215055711887</v>
+        <v>0.09942211433553939</v>
       </c>
       <c r="H33" t="n">
-        <v>690.2171667245329</v>
+        <v>935.263345519012</v>
       </c>
       <c r="I33" t="n">
-        <v>718.3643301699797</v>
+        <v>963.342215739841</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9929661489661934</v>
+        <v>0.8683563875042806</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_96_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_96_2ndlvl</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.0142851034727623</v>
+        <v>0.0066303331854856</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5299702130139066</v>
+        <v>0.8861557345611843</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.129297648977014</v>
+        <v>0.3837097917963903</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2594407259183478</v>
+        <v>0.7013969146073843</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0733320880249308</v>
+        <v>0.1125715274161696</v>
       </c>
       <c r="G34" t="n">
-        <v>0.059603674514189</v>
+        <v>0.0992932959061871</v>
       </c>
       <c r="H34" t="n">
-        <v>688.9563816690365</v>
+        <v>935.3217015606548</v>
       </c>
       <c r="I34" t="n">
-        <v>717.1035451144833</v>
+        <v>963.400571781484</v>
       </c>
       <c r="J34" t="n">
-        <v>0.7783221777550435</v>
+        <v>0.8859750500303802</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_97_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_97_2ndlvl</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0011818987176865</v>
+        <v>0.0258386360354721</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5188263123264074</v>
+        <v>0.8405694651233178</v>
       </c>
       <c r="D35" t="n">
-        <v>0.09924129264717781</v>
+        <v>1.594856995097853</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9209957919423676</v>
+        <v>0.1115320261197346</v>
       </c>
       <c r="F35" t="n">
-        <v>0.07043668879848181</v>
+        <v>0.1178412842221228</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0566653804843853</v>
+        <v>0.104641901941157</v>
       </c>
       <c r="H35" t="n">
-        <v>690.2416800024266</v>
+        <v>932.8916804271933</v>
       </c>
       <c r="I35" t="n">
-        <v>718.3888434478733</v>
+        <v>960.9705506480224</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9929661489661934</v>
+        <v>0.5950176078921831</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_98_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_98_2ndlvl</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.0019940432734179</v>
+        <v>0.0162536670803316</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5238112475157546</v>
+        <v>0.8708476945619658</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1470423985831316</v>
+        <v>0.879095886404837</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8831717236164423</v>
+        <v>0.3798757589510195</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0704637081153793</v>
+        <v>0.1139532891285006</v>
       </c>
       <c r="G36" t="n">
-        <v>0.056692800087459</v>
+        <v>0.100695732357356</v>
       </c>
       <c r="H36" t="n">
-        <v>690.2297043572871</v>
+        <v>934.6859341160751</v>
       </c>
       <c r="I36" t="n">
-        <v>718.3768678027338</v>
+        <v>962.7648043369044</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9929661489661934</v>
+        <v>0.8683563875042806</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cl_p_fl-DCPutamen-roi_99_2ndlvl</t>
+          <t>dawba_p-DCPutamen-roi_99_2ndlvl</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.003499974680991</v>
+        <v>0.0287680117482341</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5167018280311528</v>
+        <v>0.8521648205531982</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2451024315322056</v>
+        <v>1.481694991612355</v>
       </c>
       <c r="E37" t="n">
-        <v>0.806501263645849</v>
+        <v>0.1392068271628988</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0705519521670496</v>
+        <v>0.1170795630535433</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0567823514584133</v>
+        <v>0.1038687834483595</v>
       </c>
       <c r="H37" t="n">
-        <v>690.1905899349238</v>
+        <v>933.243825831657</v>
       </c>
       <c r="I37" t="n">
-        <v>718.3377533803705</v>
+        <v>961.322696052486</v>
       </c>
       <c r="J37" t="n">
-        <v>0.9929661489661934</v>
+        <v>0.5950176078921831</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_100_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_100_2ndlvl</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.005883216553888</v>
+        <v>-0.0097470329969091</v>
       </c>
       <c r="C38" t="n">
-        <v>0.501022728914543</v>
+        <v>0.9214886364403267</v>
       </c>
       <c r="D38" t="n">
-        <v>0.428627934505209</v>
+        <v>-0.5155064542141592</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6684218919579356</v>
+        <v>0.6064832402899106</v>
       </c>
       <c r="F38" t="n">
-        <v>0.07083558445955029</v>
+        <v>0.1128336291096155</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0570701857108029</v>
+        <v>0.099559319320732</v>
       </c>
       <c r="H38" t="n">
-        <v>690.064843973654</v>
+        <v>935.2011811025944</v>
       </c>
       <c r="I38" t="n">
-        <v>718.2120074191007</v>
+        <v>963.2800513234235</v>
       </c>
       <c r="J38" t="n">
-        <v>0.944132257776076</v>
+        <v>0.8243576813363779</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_24_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_24_2ndlvl</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.0124507057034974</v>
+        <v>0.0134713695031676</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5119893097686109</v>
+        <v>0.8802304591334624</v>
       </c>
       <c r="D39" t="n">
-        <v>0.788357033661646</v>
+        <v>0.6261745345610065</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4309490911104804</v>
+        <v>0.5315567286445884</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0718384261475509</v>
+        <v>0.1131128856813941</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0580878843126998</v>
+        <v>0.0998427542950808</v>
       </c>
       <c r="H39" t="n">
-        <v>689.6199346599773</v>
+        <v>935.072733247807</v>
       </c>
       <c r="I39" t="n">
-        <v>717.767098105424</v>
+        <v>963.1516034686362</v>
       </c>
       <c r="J39" t="n">
-        <v>0.5171389093325764</v>
+        <v>0.6958887444274009</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_25_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_25_2ndlvl</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.0040388325170031</v>
+        <v>-0.0048759469308091</v>
       </c>
       <c r="C40" t="n">
-        <v>0.5173175634349568</v>
+        <v>0.8943348018647361</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2590021812724096</v>
+        <v>-0.2287617140017411</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7957651460938429</v>
+        <v>0.8191707438865348</v>
       </c>
       <c r="F40" t="n">
-        <v>0.07056802993737921</v>
+        <v>0.1123615346209752</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0567986674179329</v>
+        <v>0.0990801610741569</v>
       </c>
       <c r="H40" t="n">
-        <v>690.1834630183802</v>
+        <v>935.418235453554</v>
       </c>
       <c r="I40" t="n">
-        <v>718.3306264638269</v>
+        <v>963.4971056743832</v>
       </c>
       <c r="J40" t="n">
-        <v>0.7957651460938429</v>
+        <v>0.8936408115125835</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_26_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_26_2ndlvl</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.0219731449840629</v>
+        <v>0.0393007216531212</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4987493947431085</v>
+        <v>0.8550354829670492</v>
       </c>
       <c r="D41" t="n">
-        <v>1.370582503374714</v>
+        <v>1.794019279439646</v>
       </c>
       <c r="E41" t="n">
-        <v>0.171264273931099</v>
+        <v>0.0735633079163556</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0747058409724078</v>
+        <v>0.1193142523506717</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0609977793571842</v>
+        <v>0.1061369094930758</v>
       </c>
       <c r="H41" t="n">
-        <v>688.3451528247399</v>
+        <v>932.2098606197452</v>
       </c>
       <c r="I41" t="n">
-        <v>716.4923162701866</v>
+        <v>960.2887308405744</v>
       </c>
       <c r="J41" t="n">
-        <v>0.2935958981675983</v>
+        <v>0.1514572662892536</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_27_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_27_2ndlvl</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.0239089348675391</v>
+        <v>0.0257385171573726</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5060521859954967</v>
+        <v>0.8762243683563724</v>
       </c>
       <c r="D42" t="n">
-        <v>1.616589936791542</v>
+        <v>1.274536615742122</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1067454414544772</v>
+        <v>0.2032113683711243</v>
       </c>
       <c r="F42" t="n">
-        <v>0.07637400953022461</v>
+        <v>0.1158274612586897</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0626906615232649</v>
+        <v>0.1025979469633084</v>
       </c>
       <c r="H42" t="n">
-        <v>687.6017073790301</v>
+        <v>933.8220156890368</v>
       </c>
       <c r="I42" t="n">
-        <v>715.7488708244769</v>
+        <v>961.900885909866</v>
       </c>
       <c r="J42" t="n">
-        <v>0.2899054159995846</v>
+        <v>0.3048170525566866</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_28_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_28_2ndlvl</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.0222751510686176</v>
+        <v>0.0445165366346739</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4860882280497435</v>
+        <v>0.8213352882896815</v>
       </c>
       <c r="D43" t="n">
-        <v>1.548451679743365</v>
+        <v>2.275488592739652</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1222946216704497</v>
+        <v>0.023403550868377</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0758850780339294</v>
+        <v>0.123562552949638</v>
       </c>
       <c r="G43" t="n">
-        <v>0.062194486597395</v>
+        <v>0.1104487756870391</v>
       </c>
       <c r="H43" t="n">
-        <v>687.8197463690415</v>
+        <v>930.2369653475176</v>
       </c>
       <c r="I43" t="n">
-        <v>715.9669098144882</v>
+        <v>958.3158355683468</v>
       </c>
       <c r="J43" t="n">
-        <v>0.2899054159995846</v>
+        <v>0.1514572662892536</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_29_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_29_2ndlvl</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.0128934762587434</v>
+        <v>0.0455266669934502</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5005977076529722</v>
+        <v>0.8195363058518107</v>
       </c>
       <c r="D44" t="n">
-        <v>0.8623907707113029</v>
+        <v>2.244869852078315</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3889828687297124</v>
+        <v>0.0253209185498675</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0721179907493512</v>
+        <v>0.123263799518016</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0583715906123045</v>
+        <v>0.1101455521292582</v>
       </c>
       <c r="H44" t="n">
-        <v>689.4958205304802</v>
+        <v>930.3760176330152</v>
       </c>
       <c r="I44" t="n">
-        <v>717.6429839759269</v>
+        <v>958.4548878538444</v>
       </c>
       <c r="J44" t="n">
-        <v>0.5171389093325764</v>
+        <v>0.1514572662892536</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_30_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_30_2ndlvl</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.0208256784821246</v>
+        <v>0.0329580474015062</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4786304288511362</v>
+        <v>0.8260122218073391</v>
       </c>
       <c r="D45" t="n">
-        <v>1.534433435853468</v>
+        <v>1.780637695950614</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1257038507978617</v>
+        <v>0.0757286331446268</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0757870377789224</v>
+        <v>0.1192100210746839</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0620949938941657</v>
+        <v>0.1060311186468737</v>
       </c>
       <c r="H45" t="n">
-        <v>687.8634535331721</v>
+        <v>932.2581455435862</v>
       </c>
       <c r="I45" t="n">
-        <v>716.0106169786188</v>
+        <v>960.3370157644154</v>
       </c>
       <c r="J45" t="n">
-        <v>0.2899054159995846</v>
+        <v>0.1514572662892536</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_38_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_38_2ndlvl</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.0039200783147715</v>
+        <v>0.009186236275673099</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5157383495201853</v>
+        <v>0.8783854321281874</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2627813391709787</v>
+        <v>0.4504679674047365</v>
       </c>
       <c r="E46" t="n">
-        <v>0.7928527428537064</v>
+        <v>0.6526164977246325</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0705725544722282</v>
+        <v>0.1126947051863704</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0568032589829278</v>
+        <v>0.09941831673529369</v>
       </c>
       <c r="H46" t="n">
-        <v>690.1814573708932</v>
+        <v>935.2650659894545</v>
       </c>
       <c r="I46" t="n">
-        <v>718.3286208163399</v>
+        <v>963.3439362102836</v>
       </c>
       <c r="J46" t="n">
-        <v>0.944132257776076</v>
+        <v>0.8243576813363779</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_39_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_39_2ndlvl</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0094647048269785</v>
+        <v>0.0092200466381227</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5089989895914628</v>
+        <v>0.8793425386435266</v>
       </c>
       <c r="D47" t="n">
-        <v>0.7488323084284183</v>
+        <v>0.5345100357524226</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4543929575877431</v>
+        <v>0.5932849311101626</v>
       </c>
       <c r="F47" t="n">
-        <v>0.07169937842135241</v>
+        <v>0.112877743772454</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0579467766201872</v>
+        <v>0.0996040940533387</v>
       </c>
       <c r="H47" t="n">
-        <v>689.6816516865258</v>
+        <v>935.1808926532784</v>
       </c>
       <c r="I47" t="n">
-        <v>717.8288151319725</v>
+        <v>963.2597628741074</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8175156975602451</v>
+        <v>0.8243576813363779</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_40_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_40_2ndlvl</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0120802093568778</v>
+        <v>0.0114141794996667</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5229696731989193</v>
+        <v>0.8895196739975528</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.7869095818476645</v>
+        <v>0.5413562854210801</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4317950241110992</v>
+        <v>0.5885626579622768</v>
       </c>
       <c r="F48" t="n">
-        <v>0.071833208638203</v>
+        <v>0.1128940267140182</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0580825895069171</v>
+        <v>0.0996206206299388</v>
       </c>
       <c r="H48" t="n">
-        <v>689.6222506444674</v>
+        <v>935.1734038307608</v>
       </c>
       <c r="I48" t="n">
-        <v>717.7694140899141</v>
+        <v>963.2522740515898</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8175156975602451</v>
+        <v>0.8243576813363779</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_41_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_41_2ndlvl</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.008724950598270401</v>
+        <v>0.0199142566252612</v>
       </c>
       <c r="C49" t="n">
-        <v>0.5162193251612526</v>
+        <v>0.8780413883193858</v>
       </c>
       <c r="D49" t="n">
-        <v>0.6579449317375891</v>
+        <v>1.095998457484156</v>
       </c>
       <c r="E49" t="n">
-        <v>0.5109473109751532</v>
+        <v>0.2737372320831702</v>
       </c>
       <c r="F49" t="n">
-        <v>0.07140662730200439</v>
+        <v>0.1148970583011786</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0576496884472192</v>
+        <v>0.101653622764538</v>
       </c>
       <c r="H49" t="n">
-        <v>689.8115605155083</v>
+        <v>934.2511229093114</v>
       </c>
       <c r="I49" t="n">
-        <v>717.958723960955</v>
+        <v>962.3299931301406</v>
       </c>
       <c r="J49" t="n">
-        <v>0.8175156975602451</v>
+        <v>0.8243576813363779</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_42_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_42_2ndlvl</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.0267970078238307</v>
+        <v>0.0554736025604633</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4775335425863772</v>
+        <v>0.7943419658548758</v>
       </c>
       <c r="D50" t="n">
-        <v>1.705666374011926</v>
+        <v>2.600164777684809</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0888369341977563</v>
+        <v>0.009662118249659001</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0770440923975072</v>
+        <v>0.1269650569812715</v>
       </c>
       <c r="G50" t="n">
-        <v>0.06337067154413679</v>
+        <v>0.1139021900034352</v>
       </c>
       <c r="H50" t="n">
-        <v>687.3026963752654</v>
+        <v>928.6499458516701</v>
       </c>
       <c r="I50" t="n">
-        <v>715.4498598207122</v>
+        <v>956.7288160724992</v>
       </c>
       <c r="J50" t="n">
-        <v>0.4126919918559031</v>
+        <v>0.2318908379918173</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_43_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_43_2ndlvl</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0344397600129548</v>
+        <v>0.044779381496177</v>
       </c>
       <c r="C51" t="n">
-        <v>0.4912799449353791</v>
+        <v>0.8496002576855091</v>
       </c>
       <c r="D51" t="n">
-        <v>2.320507905643818</v>
+        <v>2.212673375005521</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0208094410584174</v>
+        <v>0.0274828487037398</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0826114036043136</v>
+        <v>0.1229538020356308</v>
       </c>
       <c r="G51" t="n">
-        <v>0.06902046143548859</v>
+        <v>0.109830916280553</v>
       </c>
       <c r="H51" t="n">
-        <v>684.8099682916951</v>
+        <v>930.5202532853314</v>
       </c>
       <c r="I51" t="n">
-        <v>712.9571317371418</v>
+        <v>958.5991235061604</v>
       </c>
       <c r="J51" t="n">
-        <v>0.3471905949645549</v>
+        <v>0.329794184444878</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_44_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_44_2ndlvl</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.0223579677095075</v>
+        <v>0.0200229895243412</v>
       </c>
       <c r="C52" t="n">
-        <v>0.4962278630416167</v>
+        <v>0.8710873508075103</v>
       </c>
       <c r="D52" t="n">
-        <v>1.556507590864653</v>
+        <v>1.018148330780804</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1203684976246384</v>
+        <v>0.3092213498677862</v>
       </c>
       <c r="F52" t="n">
-        <v>0.07594181306765049</v>
+        <v>0.1145347130065799</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0622520621501342</v>
+        <v>0.1012858558445836</v>
       </c>
       <c r="H52" t="n">
-        <v>687.7944512992367</v>
+        <v>934.4181166233795</v>
       </c>
       <c r="I52" t="n">
-        <v>715.9416147446834</v>
+        <v>962.4969868442088</v>
       </c>
       <c r="J52" t="n">
-        <v>0.4126919918559031</v>
+        <v>0.8243576813363779</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_45_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_45_2ndlvl</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.0060768590682547</v>
+        <v>0.0043548797980517</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5155702417806622</v>
+        <v>0.8868827903432075</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3735203373570537</v>
+        <v>0.1954496428658208</v>
       </c>
       <c r="E53" t="n">
-        <v>0.7089566520614932</v>
+        <v>0.8451399523955563</v>
       </c>
       <c r="F53" t="n">
-        <v>0.07073420403868209</v>
+        <v>0.1123302569578819</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0569673033577736</v>
+        <v>0.0990484154161046</v>
       </c>
       <c r="H53" t="n">
-        <v>690.1097945272777</v>
+        <v>935.4326118716688</v>
       </c>
       <c r="I53" t="n">
-        <v>718.2569579727244</v>
+        <v>963.511482092498</v>
       </c>
       <c r="J53" t="n">
-        <v>0.944132257776076</v>
+        <v>0.8818851677171021</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_46_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_46_2ndlvl</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.0118623764584242</v>
+        <v>0.0184022891851438</v>
       </c>
       <c r="C54" t="n">
-        <v>0.5087104100630369</v>
+        <v>0.8706332326169244</v>
       </c>
       <c r="D54" t="n">
-        <v>0.8668503749877036</v>
+        <v>0.986908816926254</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3865372716374051</v>
+        <v>0.3242824414045281</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0721356261194986</v>
+        <v>0.1143967366697158</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0583894872471949</v>
+        <v>0.1011458150238762</v>
       </c>
       <c r="H54" t="n">
-        <v>689.4879899642272</v>
+        <v>934.4816876754928</v>
       </c>
       <c r="I54" t="n">
-        <v>717.6351534096739</v>
+        <v>962.5605578963221</v>
       </c>
       <c r="J54" t="n">
-        <v>0.8175156975602451</v>
+        <v>0.8243576813363779</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_47_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_47_2ndlvl</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.0026628426435988</v>
+        <v>-0.0114322691661191</v>
       </c>
       <c r="C55" t="n">
-        <v>0.5201316772075264</v>
+        <v>0.8931956436681329</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2021520399455952</v>
+        <v>-0.635774297532388</v>
       </c>
       <c r="E55" t="n">
-        <v>0.8398993701217221</v>
+        <v>0.5252862070921493</v>
       </c>
       <c r="F55" t="n">
-        <v>0.070507871506262</v>
+        <v>0.1131396520022106</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0567376177507992</v>
+        <v>0.0998699211094756</v>
       </c>
       <c r="H55" t="n">
-        <v>690.2101292751124</v>
+        <v>935.0604195908452</v>
       </c>
       <c r="I55" t="n">
-        <v>718.3572927205591</v>
+        <v>963.1392898116744</v>
       </c>
       <c r="J55" t="n">
-        <v>0.944132257776076</v>
+        <v>0.8243576813363779</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_48_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_48_2ndlvl</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.0110133133459286</v>
+        <v>0.0042388279230992</v>
       </c>
       <c r="C56" t="n">
-        <v>0.4997564651361196</v>
+        <v>0.8824622612781352</v>
       </c>
       <c r="D56" t="n">
-        <v>0.817895622295107</v>
+        <v>0.230837718292258</v>
       </c>
       <c r="E56" t="n">
-        <v>0.4138977135362619</v>
+        <v>0.8175586046571841</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0719469825425432</v>
+        <v>0.1123636463673878</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0581980489505808</v>
+        <v>0.0990823044177727</v>
       </c>
       <c r="H56" t="n">
-        <v>689.5717449355808</v>
+        <v>935.4172647953473</v>
       </c>
       <c r="I56" t="n">
-        <v>717.7189083810275</v>
+        <v>963.4961350161764</v>
       </c>
       <c r="J56" t="n">
-        <v>0.8175156975602451</v>
+        <v>0.8818851677171021</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_49_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_49_2ndlvl</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.0230931954319605</v>
+        <v>0.0273168055781594</v>
       </c>
       <c r="C57" t="n">
-        <v>0.4748335439118302</v>
+        <v>0.8416019104764125</v>
       </c>
       <c r="D57" t="n">
-        <v>1.833122875934012</v>
+        <v>1.5845582630905</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0675181367377221</v>
+        <v>0.1138550073383051</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0780635146093924</v>
+        <v>0.1177696991361906</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0644051963073093</v>
+        <v>0.1045692457566822</v>
       </c>
       <c r="H57" t="n">
-        <v>686.8473831053554</v>
+        <v>932.9247873155276</v>
       </c>
       <c r="I57" t="n">
-        <v>714.9945465508022</v>
+        <v>961.0036575363569</v>
       </c>
       <c r="J57" t="n">
-        <v>0.4051088204263331</v>
+        <v>0.8243576813363779</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_50_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_50_2ndlvl</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.0119919316705812</v>
+        <v>0.0123156802541548</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4895865215745429</v>
+        <v>0.8576411373610109</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9429304786113208</v>
+        <v>0.7082317537568132</v>
       </c>
       <c r="E58" t="n">
-        <v>0.3462785942475783</v>
+        <v>0.4792128183519233</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0724503822350105</v>
+        <v>0.1133547578777431</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0587089064162699</v>
+        <v>0.1000882455267867</v>
       </c>
       <c r="H58" t="n">
-        <v>689.3482049659262</v>
+        <v>934.9614481546834</v>
       </c>
       <c r="I58" t="n">
-        <v>717.495368411373</v>
+        <v>963.0403183755124</v>
       </c>
       <c r="J58" t="n">
-        <v>0.8175156975602451</v>
+        <v>0.8243576813363779</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_74_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_74_2ndlvl</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.0121582820028808</v>
+        <v>0.0012897826821144</v>
       </c>
       <c r="C59" t="n">
-        <v>0.5073536542924103</v>
+        <v>0.8891229087784156</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9937238842445406</v>
+        <v>0.0771356976988697</v>
       </c>
       <c r="E59" t="n">
-        <v>0.3209506435952631</v>
+        <v>0.9385540664268091</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0726751240860601</v>
+        <v>0.1122588666865549</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0589369777762239</v>
+        <v>0.09897595696116671</v>
       </c>
       <c r="H59" t="n">
-        <v>689.2483667899189</v>
+        <v>935.4654236912932</v>
       </c>
       <c r="I59" t="n">
-        <v>717.3955302353656</v>
+        <v>963.5442939121224</v>
       </c>
       <c r="J59" t="n">
-        <v>0.4814259653928947</v>
+        <v>0.9385540664268091</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_75_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_75_2ndlvl</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.0356493392923596</v>
+        <v>0.0364481422720515</v>
       </c>
       <c r="C60" t="n">
-        <v>0.4848638906220299</v>
+        <v>0.8554026044802272</v>
       </c>
       <c r="D60" t="n">
-        <v>2.555592362903113</v>
+        <v>1.910190259364545</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0109650758214184</v>
+        <v>0.0568217763124133</v>
       </c>
       <c r="F60" t="n">
-        <v>0.08516673523364519</v>
+        <v>0.1202508129451178</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0716136498296992</v>
+        <v>0.107087483463</v>
       </c>
       <c r="H60" t="n">
-        <v>683.6607654181846</v>
+        <v>931.7757443101318</v>
       </c>
       <c r="I60" t="n">
-        <v>711.8079288636313</v>
+        <v>959.8546145309608</v>
       </c>
       <c r="J60" t="n">
-        <v>0.1315809098570217</v>
+        <v>0.1514572662892536</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_76_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_76_2ndlvl</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.0254109328754087</v>
+        <v>0.0287042800519365</v>
       </c>
       <c r="C61" t="n">
-        <v>0.485930527186576</v>
+        <v>0.8528982447553722</v>
       </c>
       <c r="D61" t="n">
-        <v>1.840110443759696</v>
+        <v>1.52125484274653</v>
       </c>
       <c r="E61" t="n">
-        <v>0.06648356660714699</v>
+        <v>0.1289840126940859</v>
       </c>
       <c r="F61" t="n">
-        <v>0.07812145810632221</v>
+        <v>0.1173396273689482</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0644639982264158</v>
+        <v>0.1041327390004038</v>
       </c>
       <c r="H61" t="n">
-        <v>686.821488185974</v>
+        <v>933.1236316826528</v>
       </c>
       <c r="I61" t="n">
-        <v>714.9686516314207</v>
+        <v>961.2025019034818</v>
       </c>
       <c r="J61" t="n">
-        <v>0.2899054159995846</v>
+        <v>0.2211154503327187</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_77_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_77_2ndlvl</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.0076982898724434</v>
+        <v>-0.0395872426738212</v>
       </c>
       <c r="C62" t="n">
-        <v>0.5203916086669993</v>
+        <v>0.8826497460580265</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5096440778310177</v>
+        <v>-1.91970065089195</v>
       </c>
       <c r="E62" t="n">
-        <v>0.6105784272140873</v>
+        <v>0.0556049412624583</v>
       </c>
       <c r="F62" t="n">
-        <v>0.07100986922972451</v>
+        <v>0.1203299949143605</v>
       </c>
       <c r="G62" t="n">
-        <v>0.0572470524775722</v>
+        <v>0.1071678501998623</v>
       </c>
       <c r="H62" t="n">
-        <v>689.987557263929</v>
+        <v>931.7390205508171</v>
       </c>
       <c r="I62" t="n">
-        <v>718.1347207093758</v>
+        <v>959.8178907716464</v>
       </c>
       <c r="J62" t="n">
-        <v>0.6660855569608225</v>
+        <v>0.1514572662892536</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_78_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_78_2ndlvl</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.0194717940366915</v>
+        <v>0.0100897433654231</v>
       </c>
       <c r="C63" t="n">
-        <v>0.4964729701113701</v>
+        <v>0.8786727681545176</v>
       </c>
       <c r="D63" t="n">
-        <v>1.460410046160041</v>
+        <v>0.5539712663322359</v>
       </c>
       <c r="E63" t="n">
-        <v>0.1449527079997923</v>
+        <v>0.5799072870228341</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0752837932473148</v>
+        <v>0.11292457096667</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0615842938880157</v>
+        <v>0.0996516219038272</v>
       </c>
       <c r="H63" t="n">
-        <v>688.0877311914207</v>
+        <v>935.1593555997658</v>
       </c>
       <c r="I63" t="n">
-        <v>716.2348946368675</v>
+        <v>963.2382258205949</v>
       </c>
       <c r="J63" t="n">
-        <v>0.2899054159995846</v>
+        <v>0.6958887444274009</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_90_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_90_2ndlvl</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.0223755756750675</v>
+        <v>0.0135671220680338</v>
       </c>
       <c r="C64" t="n">
-        <v>0.5031614043150757</v>
+        <v>0.8813893172623202</v>
       </c>
       <c r="D64" t="n">
-        <v>1.58337635077779</v>
+        <v>0.7005059053212291</v>
       </c>
       <c r="E64" t="n">
-        <v>0.1141162448258037</v>
+        <v>0.484017654664119</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0761331176523754</v>
+        <v>0.1133307225140913</v>
       </c>
       <c r="G64" t="n">
-        <v>0.062446200876855</v>
+        <v>0.1000638505317585</v>
       </c>
       <c r="H64" t="n">
-        <v>687.7091475274566</v>
+        <v>934.9725081536424</v>
       </c>
       <c r="I64" t="n">
-        <v>715.8563109729033</v>
+        <v>963.0513783744716</v>
       </c>
       <c r="J64" t="n">
-        <v>0.4126919918559031</v>
+        <v>0.8243576813363779</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_91_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_91_2ndlvl</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.0281492703507484</v>
+        <v>0.0222750534375637</v>
       </c>
       <c r="C65" t="n">
-        <v>0.4873425918456912</v>
+        <v>0.8653209623938147</v>
       </c>
       <c r="D65" t="n">
-        <v>1.927555124831269</v>
+        <v>1.114721120140685</v>
       </c>
       <c r="E65" t="n">
-        <v>0.0546095012281743</v>
+        <v>0.2656375828724705</v>
       </c>
       <c r="F65" t="n">
-        <v>0.07886457712403069</v>
+        <v>0.1149881349384216</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0652181264147571</v>
+        <v>0.1017460621444829</v>
       </c>
       <c r="H65" t="n">
-        <v>686.4892443096493</v>
+        <v>934.2091377590986</v>
       </c>
       <c r="I65" t="n">
-        <v>714.636407755096</v>
+        <v>962.2880079799276</v>
       </c>
       <c r="J65" t="n">
-        <v>0.4051088204263331</v>
+        <v>0.8243576813363779</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_92_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_92_2ndlvl</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.0015619742364865</v>
+        <v>0.0068537542600373</v>
       </c>
       <c r="C66" t="n">
-        <v>0.5204923849650229</v>
+        <v>0.8890060358652547</v>
       </c>
       <c r="D66" t="n">
-        <v>0.1530519583168052</v>
+        <v>0.4909959638936877</v>
       </c>
       <c r="E66" t="n">
-        <v>0.8784335259673771</v>
+        <v>0.6236978963810009</v>
       </c>
       <c r="F66" t="n">
-        <v>0.070467847032157</v>
+        <v>0.1127790826578232</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0566970003215222</v>
+        <v>0.0995039567125537</v>
       </c>
       <c r="H66" t="n">
-        <v>690.2278698538645</v>
+        <v>935.2262657641968</v>
       </c>
       <c r="I66" t="n">
-        <v>718.3750332993112</v>
+        <v>963.305135985026</v>
       </c>
       <c r="J66" t="n">
-        <v>0.944132257776076</v>
+        <v>0.8243576813363779</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_93_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_93_2ndlvl</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.0003169454396455</v>
+        <v>0.010384774575513</v>
       </c>
       <c r="C67" t="n">
-        <v>0.5213255568328752</v>
+        <v>0.8880701251082931</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.0222198519592717</v>
+        <v>0.5277275095881977</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9822835249875403</v>
+        <v>0.5979803524906421</v>
       </c>
       <c r="F67" t="n">
-        <v>0.07041521680192089</v>
+        <v>0.1128618161587876</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0566435903841716</v>
+        <v>0.0995879281212632</v>
       </c>
       <c r="H67" t="n">
-        <v>690.2511966865573</v>
+        <v>935.1882179210118</v>
       </c>
       <c r="I67" t="n">
-        <v>718.398360132004</v>
+        <v>963.2670881418408</v>
       </c>
       <c r="J67" t="n">
-        <v>0.9822835249875403</v>
+        <v>0.8243576813363779</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_94_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_94_2ndlvl</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.001615644806644</v>
+        <v>0.0146671514054102</v>
       </c>
       <c r="C68" t="n">
-        <v>0.5207630937051777</v>
+        <v>0.8892604790667182</v>
       </c>
       <c r="D68" t="n">
-        <v>0.1196832518823789</v>
+        <v>0.7931450860621319</v>
       </c>
       <c r="E68" t="n">
-        <v>0.904793413702073</v>
+        <v>0.4281623278277692</v>
       </c>
       <c r="F68" t="n">
-        <v>0.07044696010202441</v>
+        <v>0.1136362008023607</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0566758039553877</v>
+        <v>0.1003738995674833</v>
       </c>
       <c r="H68" t="n">
-        <v>690.2371275417297</v>
+        <v>934.8319183987348</v>
       </c>
       <c r="I68" t="n">
-        <v>718.3842909871764</v>
+        <v>962.9107886195638</v>
       </c>
       <c r="J68" t="n">
-        <v>0.944132257776076</v>
+        <v>0.8243576813363779</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_95_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_95_2ndlvl</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.0050885367607743</v>
+        <v>0.0106618794192694</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5140079208333687</v>
+        <v>0.8775858229720765</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3419222789434688</v>
+        <v>0.5222685393416238</v>
       </c>
       <c r="E69" t="n">
-        <v>0.7325867350948154</v>
+        <v>0.6017717580333229</v>
       </c>
       <c r="F69" t="n">
-        <v>0.07068234854380361</v>
+        <v>0.1128491440182538</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0569146796333414</v>
+        <v>0.0995750663726416</v>
       </c>
       <c r="H69" t="n">
-        <v>690.132784578034</v>
+        <v>935.1940458703726</v>
       </c>
       <c r="I69" t="n">
-        <v>718.2799480234808</v>
+        <v>963.2729160912018</v>
       </c>
       <c r="J69" t="n">
-        <v>0.944132257776076</v>
+        <v>0.8243576813363779</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_96_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_96_2ndlvl</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.0034662240735598</v>
+        <v>-0.0058641806709822</v>
       </c>
       <c r="C70" t="n">
-        <v>0.5185202462405734</v>
+        <v>0.8945114319646059</v>
       </c>
       <c r="D70" t="n">
-        <v>0.2871965131952853</v>
+        <v>-0.3547299549952716</v>
       </c>
       <c r="E70" t="n">
-        <v>0.7741087387910969</v>
+        <v>0.7229783880258362</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0706033634334557</v>
+        <v>0.1125241835493146</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0568345243732105</v>
+        <v>0.09924524365229689</v>
       </c>
       <c r="H70" t="n">
-        <v>690.1678000354311</v>
+        <v>935.3434675767728</v>
       </c>
       <c r="I70" t="n">
-        <v>718.3149634808779</v>
+        <v>963.422337797602</v>
       </c>
       <c r="J70" t="n">
-        <v>0.944132257776076</v>
+        <v>0.8675740656310035</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_97_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_97_2ndlvl</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.009186747633358101</v>
+        <v>0.0022624490705305</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5092224530501535</v>
+        <v>0.8876361037672904</v>
       </c>
       <c r="D71" t="n">
-        <v>0.691600426341947</v>
+        <v>0.1243467546457485</v>
       </c>
       <c r="E71" t="n">
-        <v>0.489584554073961</v>
+        <v>0.9011030369960608</v>
       </c>
       <c r="F71" t="n">
-        <v>0.07151064360504369</v>
+        <v>0.1122799241558798</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0577552457325258</v>
+        <v>0.0989973295048456</v>
       </c>
       <c r="H71" t="n">
-        <v>689.7654077876568</v>
+        <v>935.4557457017762</v>
       </c>
       <c r="I71" t="n">
-        <v>717.9125712331036</v>
+        <v>963.5346159226052</v>
       </c>
       <c r="J71" t="n">
-        <v>0.8175156975602451</v>
+        <v>0.9011030369960608</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_98_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_98_2ndlvl</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.0305002159537874</v>
+        <v>0.0223387173439987</v>
       </c>
       <c r="C72" t="n">
-        <v>0.4780318630054139</v>
+        <v>0.8605415070231719</v>
       </c>
       <c r="D72" t="n">
-        <v>2.192213653309417</v>
+        <v>1.172659645104946</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0289325495803795</v>
+        <v>0.2416284631484118</v>
       </c>
       <c r="F72" t="n">
-        <v>0.081315355939761</v>
+        <v>0.1152796250736555</v>
       </c>
       <c r="G72" t="n">
-        <v>0.06770521306479441</v>
+        <v>0.1020419137281242</v>
       </c>
       <c r="H72" t="n">
-        <v>685.3916136364633</v>
+        <v>934.0747355330852</v>
       </c>
       <c r="I72" t="n">
-        <v>713.53877708191</v>
+        <v>962.1536057539143</v>
       </c>
       <c r="J72" t="n">
-        <v>0.3471905949645549</v>
+        <v>0.8243576813363779</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>cl_p_fl-DorsalCaudate-roi_99_2ndlvl</t>
+          <t>dawba_p-DorsalCaudate-roi_99_2ndlvl</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.0170382147389204</v>
+        <v>0.0052298760178982</v>
       </c>
       <c r="C73" t="n">
-        <v>0.5039492240213652</v>
+        <v>0.8862292799910503</v>
       </c>
       <c r="D73" t="n">
-        <v>1.227474843709266</v>
+        <v>0.2739325400376675</v>
       </c>
       <c r="E73" t="n">
-        <v>0.2203571494040669</v>
+        <v>0.7842775118405892</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0738595421606775</v>
+        <v>0.1124117888289971</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0601389427852802</v>
+        <v>0.099131167215466</v>
       </c>
       <c r="H73" t="n">
-        <v>688.7218068329782</v>
+        <v>935.3951356239388</v>
       </c>
       <c r="I73" t="n">
-        <v>716.868970278425</v>
+        <v>963.4740058447678</v>
       </c>
       <c r="J73" t="n">
-        <v>0.661071448212201</v>
+        <v>0.8818851677171021</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_100_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_100_2ndlvl</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.0279519882419281</v>
+        <v>0.0050276637394786</v>
       </c>
       <c r="C74" t="n">
-        <v>0.5588640128929466</v>
+        <v>0.8833858605413193</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.854833231668693</v>
+        <v>0.2437987857379034</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0643465980761414</v>
+        <v>0.8075113400173217</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0782442424194472</v>
+        <v>0.1123772616997411</v>
       </c>
       <c r="G74" t="n">
-        <v>0.064588601566402</v>
+        <v>0.09909612347080959</v>
       </c>
       <c r="H74" t="n">
-        <v>686.76661055965</v>
+        <v>935.411006491277</v>
       </c>
       <c r="I74" t="n">
-        <v>714.9137740050967</v>
+        <v>963.489876712106</v>
       </c>
       <c r="J74" t="n">
-        <v>0.4226878817466874</v>
+        <v>0.8809214618370783</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_24_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_24_2ndlvl</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.0195271252779267</v>
+        <v>-0.0001600331082642</v>
       </c>
       <c r="C75" t="n">
-        <v>0.5347434842517349</v>
+        <v>0.890263736364076</v>
       </c>
       <c r="D75" t="n">
-        <v>1.126237511729942</v>
+        <v>-0.006735442250221</v>
       </c>
       <c r="E75" t="n">
-        <v>0.2607318976100634</v>
+        <v>0.9946292847199166</v>
       </c>
       <c r="F75" t="n">
-        <v>0.07331634451450959</v>
+        <v>0.1122457950879786</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0595876977665764</v>
+        <v>0.0989626897775743</v>
       </c>
       <c r="H75" t="n">
-        <v>688.9633812328618</v>
+        <v>935.471431268001</v>
       </c>
       <c r="I75" t="n">
-        <v>717.1105446783085</v>
+        <v>963.55030148883</v>
       </c>
       <c r="J75" t="n">
-        <v>0.7390200436973444</v>
+        <v>0.9946292847199166</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_25_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_25_2ndlvl</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.0159386073162062</v>
+        <v>-0.0011747951331194</v>
       </c>
       <c r="C76" t="n">
-        <v>0.5031917608583298</v>
+        <v>0.891752375810271</v>
       </c>
       <c r="D76" t="n">
-        <v>1.151736949760827</v>
+        <v>-0.0622199880553181</v>
       </c>
       <c r="E76" t="n">
-        <v>0.2501086195510158</v>
+        <v>0.95041864552943</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0734488200910401</v>
+        <v>0.1122542651127587</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0597221359442406</v>
+        <v>0.0989712865358922</v>
       </c>
       <c r="H76" t="n">
-        <v>688.9044788891536</v>
+        <v>935.4675385389356</v>
       </c>
       <c r="I76" t="n">
-        <v>717.0516423346003</v>
+        <v>963.5464087597647</v>
       </c>
       <c r="J76" t="n">
-        <v>0.7390200436973444</v>
+        <v>0.9946292847199166</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_26_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_26_2ndlvl</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.0057412542912969</v>
+        <v>-0.0108813406236448</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5196411621240757</v>
+        <v>0.8875545948998974</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.4049207884036123</v>
+        <v>-0.5625291284958208</v>
       </c>
       <c r="E77" t="n">
-        <v>0.6857495215642</v>
+        <v>0.5740698959343623</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0707902663246702</v>
+        <v>0.1129456911541116</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0570241961961468</v>
+        <v>0.0996730581040485</v>
       </c>
       <c r="H77" t="n">
-        <v>690.084937959122</v>
+        <v>935.1496415001794</v>
       </c>
       <c r="I77" t="n">
-        <v>718.2321014045688</v>
+        <v>963.2285117210084</v>
       </c>
       <c r="J77" t="n">
-        <v>0.7390200436973444</v>
+        <v>0.920602531370999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_27_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_27_2ndlvl</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.0136835304305621</v>
+        <v>-0.0590561453392966</v>
       </c>
       <c r="C78" t="n">
-        <v>0.5355839599202937</v>
+        <v>0.9558920588379918</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.9182354222247322</v>
+        <v>-2.931379041817904</v>
       </c>
       <c r="E78" t="n">
-        <v>0.3590421400254383</v>
+        <v>0.0035678349414561</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0723453375621016</v>
+        <v>0.1308701780950891</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0586023055259845</v>
+        <v>0.1178657418571105</v>
       </c>
       <c r="H78" t="n">
-        <v>689.3948611813591</v>
+        <v>926.8208512505108</v>
       </c>
       <c r="I78" t="n">
-        <v>717.5420246268059</v>
+        <v>954.8997214713399</v>
       </c>
       <c r="J78" t="n">
-        <v>0.7390200436973444</v>
+        <v>0.0428140192974737</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_28_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_28_2ndlvl</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.0053618676482516</v>
+        <v>0.0056226025727654</v>
       </c>
       <c r="C79" t="n">
-        <v>0.5315623821931486</v>
+        <v>0.8788784578161788</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.3873442905390151</v>
+        <v>0.2962811319058407</v>
       </c>
       <c r="E79" t="n">
-        <v>0.6987048112430918</v>
+        <v>0.7671687761424992</v>
       </c>
       <c r="F79" t="n">
-        <v>0.07075832883856401</v>
+        <v>0.1124399895286213</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0569917855620982</v>
+        <v>0.0991597898706955</v>
       </c>
       <c r="H79" t="n">
-        <v>690.0990983985532</v>
+        <v>935.3821723284716</v>
       </c>
       <c r="I79" t="n">
-        <v>718.2462618439999</v>
+        <v>963.4610425493008</v>
       </c>
       <c r="J79" t="n">
-        <v>0.7390200436973444</v>
+        <v>0.920602531370999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_29_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_29_2ndlvl</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.005188508440616</v>
+        <v>0.0137298230025311</v>
       </c>
       <c r="C80" t="n">
-        <v>0.505337169057387</v>
+        <v>0.8454246372895377</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3812127254807148</v>
+        <v>0.7356460337113028</v>
       </c>
       <c r="E80" t="n">
-        <v>0.7032453072222132</v>
+        <v>0.4623761993480482</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0707475203422339</v>
+        <v>0.1134421610269874</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0569808169398966</v>
+        <v>0.1001769564538251</v>
       </c>
       <c r="H80" t="n">
-        <v>690.103890558363</v>
+        <v>934.9212266083748</v>
       </c>
       <c r="I80" t="n">
-        <v>718.2510540038097</v>
+        <v>963.0000968292038</v>
       </c>
       <c r="J80" t="n">
-        <v>0.7390200436973444</v>
+        <v>0.920602531370999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_30_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_30_2ndlvl</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.0171988394045303</v>
+        <v>-0.0076238776722394</v>
       </c>
       <c r="C81" t="n">
-        <v>0.5575037090735312</v>
+        <v>0.9068633023036078</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.138810428186569</v>
+        <v>-0.3695189675577883</v>
       </c>
       <c r="E81" t="n">
-        <v>0.2554553850347668</v>
+        <v>0.7119359929325314</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0733812978464404</v>
+        <v>0.1125478804383171</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0596536133700913</v>
+        <v>0.0992692951082171</v>
       </c>
       <c r="H81" t="n">
-        <v>688.9345022184299</v>
+        <v>935.3325732407072</v>
       </c>
       <c r="I81" t="n">
-        <v>717.0816656638766</v>
+        <v>963.4114434615364</v>
       </c>
       <c r="J81" t="n">
-        <v>0.7390200436973444</v>
+        <v>0.920602531370999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_38_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_38_2ndlvl</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.009480198133329201</v>
+        <v>0.0014913677794832</v>
       </c>
       <c r="C82" t="n">
-        <v>0.4955146793910733</v>
+        <v>0.8862610255752119</v>
       </c>
       <c r="D82" t="n">
-        <v>0.7290659160984333</v>
+        <v>0.0840611631587759</v>
       </c>
       <c r="E82" t="n">
-        <v>0.4663827358328486</v>
+        <v>0.9330497512975302</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0716325077095586</v>
+        <v>0.1122613380684768</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0578789152311817</v>
+        <v>0.09897846532137169</v>
       </c>
       <c r="H82" t="n">
-        <v>689.7113292934876</v>
+        <v>935.4642878587968</v>
       </c>
       <c r="I82" t="n">
-        <v>717.8584927389343</v>
+        <v>963.543158079626</v>
       </c>
       <c r="J82" t="n">
-        <v>0.8394484088858698</v>
+        <v>0.9330497512975302</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_39_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_39_2ndlvl</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.007836222470644401</v>
+        <v>0.0066024783726273</v>
       </c>
       <c r="C83" t="n">
-        <v>0.504247252879032</v>
+        <v>0.8761755240463504</v>
       </c>
       <c r="D83" t="n">
-        <v>0.6488552914652687</v>
+        <v>0.3999630975381883</v>
       </c>
       <c r="E83" t="n">
-        <v>0.5167996681352394</v>
+        <v>0.6893966633361299</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0713794206425086</v>
+        <v>0.1125997042568163</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0576220787261013</v>
+        <v>0.099321894345447</v>
       </c>
       <c r="H83" t="n">
-        <v>689.8236314389478</v>
+        <v>935.3087469013776</v>
       </c>
       <c r="I83" t="n">
-        <v>717.9707948843945</v>
+        <v>963.3876171222066</v>
       </c>
       <c r="J83" t="n">
-        <v>0.8394484088858698</v>
+        <v>0.8561738777337133</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_40_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_40_2ndlvl</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.013317545988112</v>
+        <v>0.0192182755315872</v>
       </c>
       <c r="C84" t="n">
-        <v>0.4755221033357526</v>
+        <v>0.8238395255300263</v>
       </c>
       <c r="D84" t="n">
-        <v>1.276218260514875</v>
+        <v>1.349909350449533</v>
       </c>
       <c r="E84" t="n">
-        <v>0.2026097445659593</v>
+        <v>0.1778065509075358</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0741374980340211</v>
+        <v>0.1162616469169779</v>
       </c>
       <c r="G84" t="n">
-        <v>0.060421016523414</v>
+        <v>0.1030386291651123</v>
       </c>
       <c r="H84" t="n">
-        <v>688.5981376778391</v>
+        <v>933.6216122038132</v>
       </c>
       <c r="I84" t="n">
-        <v>716.7453011232858</v>
+        <v>961.7004824246424</v>
       </c>
       <c r="J84" t="n">
-        <v>0.607829233697878</v>
+        <v>0.8260269932896634</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_41_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_41_2ndlvl</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.0087411873998086</v>
+        <v>-0.0106066180639629</v>
       </c>
       <c r="C85" t="n">
-        <v>0.4986588535699637</v>
+        <v>0.9170716599517268</v>
       </c>
       <c r="D85" t="n">
-        <v>0.6717088657855603</v>
+        <v>-0.5972393551968438</v>
       </c>
       <c r="E85" t="n">
-        <v>0.5021520205568077</v>
+        <v>0.550684662193109</v>
       </c>
       <c r="F85" t="n">
-        <v>0.07144854217539361</v>
+        <v>0.1130346621498512</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0576922242816957</v>
+        <v>0.09976336033663211</v>
       </c>
       <c r="H85" t="n">
-        <v>689.7929632283658</v>
+        <v>935.1087173014428</v>
       </c>
       <c r="I85" t="n">
-        <v>717.9401266738125</v>
+        <v>963.1875875222718</v>
       </c>
       <c r="J85" t="n">
-        <v>0.8394484088858698</v>
+        <v>0.8260269932896634</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_42_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_42_2ndlvl</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.0037350897120371</v>
+        <v>-0.0240941367371861</v>
       </c>
       <c r="C86" t="n">
-        <v>0.5163213900883697</v>
+        <v>0.921976526321266</v>
       </c>
       <c r="D86" t="n">
-        <v>0.2535349707939806</v>
+        <v>-1.200075526350903</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7999834938140903</v>
+        <v>0.2308185152080426</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0705616003247999</v>
+        <v>0.1154226317032796</v>
       </c>
       <c r="G86" t="n">
-        <v>0.056792142551834</v>
+        <v>0.1021870601078175</v>
       </c>
       <c r="H86" t="n">
-        <v>690.1863131368455</v>
+        <v>934.0087808849916</v>
       </c>
       <c r="I86" t="n">
-        <v>718.3334765822922</v>
+        <v>962.0876511058208</v>
       </c>
       <c r="J86" t="n">
-        <v>0.8727092659790077</v>
+        <v>0.8260269932896634</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_43_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_43_2ndlvl</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.0018844767383721</v>
+        <v>-0.0032407877262227</v>
       </c>
       <c r="C87" t="n">
-        <v>0.5170840087311883</v>
+        <v>0.8971991699672925</v>
       </c>
       <c r="D87" t="n">
-        <v>0.1270790335126995</v>
+        <v>-0.1603539613708771</v>
       </c>
       <c r="E87" t="n">
-        <v>0.8989409144143798</v>
+        <v>0.8726829994745581</v>
       </c>
       <c r="F87" t="n">
-        <v>0.07045114866161779</v>
+        <v>0.1123026166281283</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0566800545677158</v>
+        <v>0.09902036151533231</v>
       </c>
       <c r="H87" t="n">
-        <v>690.2352710683856</v>
+        <v>935.4453160097283</v>
       </c>
       <c r="I87" t="n">
-        <v>718.3824345138323</v>
+        <v>963.5241862305576</v>
       </c>
       <c r="J87" t="n">
-        <v>0.9355751785555464</v>
+        <v>0.9106257385821476</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_44_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_44_2ndlvl</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-0.0259659279548095</v>
+        <v>-0.023287491101455</v>
       </c>
       <c r="C88" t="n">
-        <v>0.5645131143005312</v>
+        <v>0.9301616833800802</v>
       </c>
       <c r="D88" t="n">
-        <v>-1.633894810987963</v>
+        <v>-1.073509403538546</v>
       </c>
       <c r="E88" t="n">
-        <v>0.1030580053692213</v>
+        <v>0.2836881886193698</v>
       </c>
       <c r="F88" t="n">
-        <v>0.07650144912561201</v>
+        <v>0.1147896753069849</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0628199891126581</v>
+        <v>0.1015446330422515</v>
       </c>
       <c r="H88" t="n">
-        <v>687.5448567312176</v>
+        <v>934.3006195295048</v>
       </c>
       <c r="I88" t="n">
-        <v>715.6920201766643</v>
+        <v>962.3794897503338</v>
       </c>
       <c r="J88" t="n">
-        <v>0.4226878817466874</v>
+        <v>0.8260269932896634</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_45_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_45_2ndlvl</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.0207657845511155</v>
+        <v>-0.044053029317262</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5002907691804249</v>
+        <v>0.8446620704697174</v>
       </c>
       <c r="D89" t="n">
-        <v>-1.41607983996606</v>
+        <v>-2.211838961936765</v>
       </c>
       <c r="E89" t="n">
-        <v>0.1575207357902462</v>
+        <v>0.0275409403615577</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0749940782172898</v>
+        <v>0.1229458246931273</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0612902867834719</v>
+        <v>0.1098228195763163</v>
       </c>
       <c r="H89" t="n">
-        <v>688.2167912177944</v>
+        <v>930.5239643109844</v>
       </c>
       <c r="I89" t="n">
-        <v>716.3639546632411</v>
+        <v>958.6028345318134</v>
       </c>
       <c r="J89" t="n">
-        <v>0.5400710941379869</v>
+        <v>0.6609825686773856</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_46_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_46_2ndlvl</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.0101374832705261</v>
+        <v>-0.0138122628908977</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5566787246159577</v>
+        <v>0.9380488932901584</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.6367379748227064</v>
+        <v>-0.6350515322823237</v>
       </c>
       <c r="E90" t="n">
-        <v>0.5246552555536687</v>
+        <v>0.525756988212977</v>
       </c>
       <c r="F90" t="n">
-        <v>0.07134373785426081</v>
+        <v>0.1131376226491686</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0575858673039535</v>
+        <v>0.0998678613920489</v>
       </c>
       <c r="H90" t="n">
-        <v>689.8394624754757</v>
+        <v>935.0613531934082</v>
       </c>
       <c r="I90" t="n">
-        <v>717.9866259209224</v>
+        <v>963.1402234142372</v>
       </c>
       <c r="J90" t="n">
-        <v>0.8394484088858698</v>
+        <v>0.8260269932896634</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_47_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_47_2ndlvl</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.0088701616381122</v>
+        <v>-0.0115026880089824</v>
       </c>
       <c r="C91" t="n">
-        <v>0.5282453857828238</v>
+        <v>0.8999383391514418</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.6515114470406956</v>
+        <v>-0.6188087263888198</v>
       </c>
       <c r="E91" t="n">
-        <v>0.5150859070801523</v>
+        <v>0.5363937316184741</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0713873319399035</v>
+        <v>0.1130926231654775</v>
       </c>
       <c r="G91" t="n">
-        <v>0.057630107227902</v>
+        <v>0.0998221885993749</v>
       </c>
       <c r="H91" t="n">
-        <v>689.8201214279882</v>
+        <v>935.082054628086</v>
       </c>
       <c r="I91" t="n">
-        <v>717.9672848734349</v>
+        <v>963.1609248489152</v>
       </c>
       <c r="J91" t="n">
-        <v>0.8394484088858698</v>
+        <v>0.8260269932896634</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_48_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_48_2ndlvl</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-0.0310650713803803</v>
+        <v>-0.0189636767254137</v>
       </c>
       <c r="C92" t="n">
-        <v>0.51978337759535</v>
+        <v>0.8918008585506056</v>
       </c>
       <c r="D92" t="n">
-        <v>-2.128860715443939</v>
+        <v>-0.9431794423587418</v>
       </c>
       <c r="E92" t="n">
-        <v>0.0338686451965281</v>
+        <v>0.3461570184972533</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0807012588148503</v>
+        <v>0.1142107495414052</v>
       </c>
       <c r="G92" t="n">
-        <v>0.0670820182046999</v>
+        <v>0.1009570450457654</v>
       </c>
       <c r="H92" t="n">
-        <v>685.6669240956427</v>
+        <v>934.5673634904678</v>
       </c>
       <c r="I92" t="n">
-        <v>713.8140875410894</v>
+        <v>962.6462337112968</v>
       </c>
       <c r="J92" t="n">
-        <v>0.4226878817466874</v>
+        <v>0.8260269932896634</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_49_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_49_2ndlvl</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-0.0219891343161464</v>
+        <v>-0.0182648532440847</v>
       </c>
       <c r="C93" t="n">
-        <v>0.5460901723021303</v>
+        <v>0.9110988137349056</v>
       </c>
       <c r="D93" t="n">
-        <v>-1.638351492945684</v>
+        <v>-0.9951935524132548</v>
       </c>
       <c r="E93" t="n">
-        <v>0.1021249980295595</v>
+        <v>0.3202422747522334</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0765344837954723</v>
+        <v>0.1144329133109532</v>
       </c>
       <c r="G93" t="n">
-        <v>0.06285351318503481</v>
+        <v>0.1011825329614912</v>
       </c>
       <c r="H93" t="n">
-        <v>687.5301187249656</v>
+        <v>934.4650206511984</v>
       </c>
       <c r="I93" t="n">
-        <v>715.6772821704124</v>
+        <v>962.5438908720274</v>
       </c>
       <c r="J93" t="n">
-        <v>0.4226878817466874</v>
+        <v>0.8260269932896634</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_50_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_50_2ndlvl</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-0.0230427031355719</v>
+        <v>-0.0278904756479612</v>
       </c>
       <c r="C94" t="n">
-        <v>0.5160343617355102</v>
+        <v>0.8841627288850238</v>
       </c>
       <c r="D94" t="n">
-        <v>-1.621577876057919</v>
+        <v>-1.440327268509948</v>
       </c>
       <c r="E94" t="n">
-        <v>0.1056719704366718</v>
+        <v>0.1505551101043389</v>
       </c>
       <c r="F94" t="n">
-        <v>0.07641060699755289</v>
+        <v>0.1168147853948659</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0627278011752945</v>
+        <v>0.103600044029203</v>
       </c>
       <c r="H94" t="n">
-        <v>687.5853820964711</v>
+        <v>933.3661619845986</v>
       </c>
       <c r="I94" t="n">
-        <v>715.7325455419178</v>
+        <v>961.4450322054278</v>
       </c>
       <c r="J94" t="n">
-        <v>0.4226878817466874</v>
+        <v>0.8260269932896634</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_74_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_74_2ndlvl</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.0043327837535395</v>
+        <v>0.0242036285900883</v>
       </c>
       <c r="C95" t="n">
-        <v>0.5281981537572225</v>
+        <v>0.8479578612661027</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.3333799204648662</v>
+        <v>1.366857670523031</v>
       </c>
       <c r="E95" t="n">
-        <v>0.7390200436973444</v>
+        <v>0.1724357238141411</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0706691153109401</v>
+        <v>0.1163626511700154</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0569012503525836</v>
+        <v>0.1031411447037313</v>
       </c>
       <c r="H95" t="n">
-        <v>690.1386513052112</v>
+        <v>933.5749783893508</v>
       </c>
       <c r="I95" t="n">
-        <v>718.2858147506579</v>
+        <v>961.65384861018</v>
       </c>
       <c r="J95" t="n">
-        <v>0.7390200436973444</v>
+        <v>0.8704074633594142</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_75_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_75_2ndlvl</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-0.010437934176588</v>
+        <v>0.0173830582470757</v>
       </c>
       <c r="C96" t="n">
-        <v>0.5527833833377065</v>
+        <v>0.8373692786077916</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.7604572156059103</v>
+        <v>0.9265944193115851</v>
       </c>
       <c r="E96" t="n">
-        <v>0.4474238164485459</v>
+        <v>0.3546944827666831</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0717395367830815</v>
+        <v>0.1141423957943494</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0579875299206086</v>
+        <v>0.1008876685493771</v>
       </c>
       <c r="H96" t="n">
-        <v>689.6638281468962</v>
+        <v>934.5988464338536</v>
       </c>
       <c r="I96" t="n">
-        <v>717.8109915923429</v>
+        <v>962.6777166546829</v>
       </c>
       <c r="J96" t="n">
-        <v>0.7390200436973444</v>
+        <v>0.8704074633594142</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_76_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_76_2ndlvl</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.0064247490501342</v>
+        <v>0.0178682938007887</v>
       </c>
       <c r="C97" t="n">
-        <v>0.5159096214774013</v>
+        <v>0.8753437079434507</v>
       </c>
       <c r="D97" t="n">
-        <v>0.445980856278614</v>
+        <v>0.9113285781912688</v>
       </c>
       <c r="E97" t="n">
-        <v>0.6558494022487272</v>
+        <v>0.3626697763997559</v>
       </c>
       <c r="F97" t="n">
-        <v>0.07087038698500329</v>
+        <v>0.1140805416151056</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0571055038292256</v>
+        <v>0.100824888871192</v>
       </c>
       <c r="H97" t="n">
-        <v>690.0494119265527</v>
+        <v>934.6273336579796</v>
       </c>
       <c r="I97" t="n">
-        <v>718.1965753719994</v>
+        <v>962.7062038788088</v>
       </c>
       <c r="J97" t="n">
-        <v>0.7390200436973444</v>
+        <v>0.8704074633594142</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_77_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_77_2ndlvl</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.0064579892281663</v>
+        <v>0.0202482564704145</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5105265015817815</v>
+        <v>0.8552184603156199</v>
       </c>
       <c r="D98" t="n">
-        <v>0.5169774811564246</v>
+        <v>1.190071855770603</v>
       </c>
       <c r="E98" t="n">
-        <v>0.6054540802543065</v>
+        <v>0.2347222336920548</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0710271270334449</v>
+        <v>0.1153700730347242</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0572645659524588</v>
+        <v>0.1021337150252688</v>
       </c>
       <c r="H98" t="n">
-        <v>689.9799034892105</v>
+        <v>934.0330221786312</v>
       </c>
       <c r="I98" t="n">
-        <v>718.1270669346573</v>
+        <v>962.1118923994604</v>
       </c>
       <c r="J98" t="n">
-        <v>0.7390200436973444</v>
+        <v>0.8704074633594142</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_78_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_78_2ndlvl</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-0.0136912677902964</v>
+        <v>-0.007111290933373</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5222664969241223</v>
+        <v>0.8916622504982255</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.9718359562722204</v>
+        <v>-0.3697408097125975</v>
       </c>
       <c r="E99" t="n">
-        <v>0.331712217148244</v>
+        <v>0.7117708057122182</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0725768461093608</v>
+        <v>0.1125482432603701</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0588372438294995</v>
+        <v>0.099269663359029</v>
       </c>
       <c r="H99" t="n">
-        <v>689.2920282747</v>
+        <v>935.332406435733</v>
       </c>
       <c r="I99" t="n">
-        <v>717.4391917201467</v>
+        <v>963.411276656562</v>
       </c>
       <c r="J99" t="n">
-        <v>0.7390200436973444</v>
+        <v>0.920602531370999</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_90_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_90_2ndlvl</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-0.0076349980648749</v>
+        <v>0.0072274864813306</v>
       </c>
       <c r="C100" t="n">
-        <v>0.5372518402171136</v>
+        <v>0.8741019764188562</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.5353917073151898</v>
+        <v>0.367448658642341</v>
       </c>
       <c r="E100" t="n">
-        <v>0.5926728824705358</v>
+        <v>0.7134782314447612</v>
       </c>
       <c r="F100" t="n">
-        <v>0.0710715453747576</v>
+        <v>0.1125445049398363</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0573096423432726</v>
+        <v>0.0992658691035247</v>
       </c>
       <c r="H100" t="n">
-        <v>689.9602034584796</v>
+        <v>935.3341250999352</v>
       </c>
       <c r="I100" t="n">
-        <v>718.1073669039263</v>
+        <v>963.4129953207644</v>
       </c>
       <c r="J100" t="n">
-        <v>0.8727092659790077</v>
+        <v>0.8561738777337133</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_91_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_91_2ndlvl</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.0049278648016132</v>
+        <v>-0.0213203458121637</v>
       </c>
       <c r="C101" t="n">
-        <v>0.5150374425671986</v>
+        <v>0.9197292419555068</v>
       </c>
       <c r="D101" t="n">
-        <v>0.3551391013209347</v>
+        <v>-1.127433530104914</v>
       </c>
       <c r="E101" t="n">
-        <v>0.7226702578317381</v>
+        <v>0.2602333822701461</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0707034820722565</v>
+        <v>0.1150508430478576</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0569361262511047</v>
+        <v>0.1018097085298704</v>
       </c>
       <c r="H101" t="n">
-        <v>690.1234152168547</v>
+        <v>934.1802276211438</v>
       </c>
       <c r="I101" t="n">
-        <v>718.2705786623014</v>
+        <v>962.2590978419728</v>
       </c>
       <c r="J101" t="n">
-        <v>0.8727092659790077</v>
+        <v>0.8260269932896634</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_92_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_92_2ndlvl</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.0045068506127548</v>
+        <v>-0.0103885096767759</v>
       </c>
       <c r="C102" t="n">
-        <v>0.5172660526159627</v>
+        <v>0.8998608648162374</v>
       </c>
       <c r="D102" t="n">
-        <v>0.2989559613614485</v>
+        <v>-0.5053379874504744</v>
       </c>
       <c r="E102" t="n">
-        <v>0.7651269883653222</v>
+        <v>0.6135990967024486</v>
       </c>
       <c r="F102" t="n">
-        <v>0.0706191776539376</v>
+        <v>0.1128106782340094</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0568505728784404</v>
+        <v>0.09953602504050341</v>
       </c>
       <c r="H102" t="n">
-        <v>690.1607895578645</v>
+        <v>935.2117358716148</v>
       </c>
       <c r="I102" t="n">
-        <v>718.3079530033112</v>
+        <v>963.290606092444</v>
       </c>
       <c r="J102" t="n">
-        <v>0.8727092659790077</v>
+        <v>0.8351264227078459</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_93_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_93_2ndlvl</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.0043203082858361</v>
+        <v>-0.0105333005116386</v>
       </c>
       <c r="C103" t="n">
-        <v>0.519483644620665</v>
+        <v>0.8944727297426927</v>
       </c>
       <c r="D103" t="n">
-        <v>0.2729522369171012</v>
+        <v>-0.487253679305375</v>
       </c>
       <c r="E103" t="n">
-        <v>0.785029054262675</v>
+        <v>0.6263448170308844</v>
       </c>
       <c r="F103" t="n">
-        <v>0.0705850567383503</v>
+        <v>0.1127709876577593</v>
       </c>
       <c r="G103" t="n">
-        <v>0.0568159464678074</v>
+        <v>0.09949574059029451</v>
       </c>
       <c r="H103" t="n">
-        <v>690.17591528333</v>
+        <v>935.2299883375656</v>
       </c>
       <c r="I103" t="n">
-        <v>718.3230787287767</v>
+        <v>963.3088585583946</v>
       </c>
       <c r="J103" t="n">
-        <v>0.8727092659790077</v>
+        <v>0.8351264227078459</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_94_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_94_2ndlvl</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.0066602456898007</v>
+        <v>0.0143185610040053</v>
       </c>
       <c r="C104" t="n">
-        <v>0.5093496104404203</v>
+        <v>0.8634683492083876</v>
       </c>
       <c r="D104" t="n">
-        <v>0.4965211349310715</v>
+        <v>0.7831143372664922</v>
       </c>
       <c r="E104" t="n">
-        <v>0.6197961606826603</v>
+        <v>0.434022219146863</v>
       </c>
       <c r="F104" t="n">
-        <v>0.07097960063008429</v>
+        <v>0.1136013056572678</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0572163354542337</v>
+        <v>0.1003384823005187</v>
       </c>
       <c r="H104" t="n">
-        <v>690.0009809371005</v>
+        <v>934.8479805833214</v>
       </c>
       <c r="I104" t="n">
-        <v>718.1481443825472</v>
+        <v>962.9268508041504</v>
       </c>
       <c r="J104" t="n">
-        <v>0.8727092659790077</v>
+        <v>0.8260269932896634</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_95_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_95_2ndlvl</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.0114781300933204</v>
+        <v>0.0210343298133175</v>
       </c>
       <c r="C105" t="n">
-        <v>0.5011100779424444</v>
+        <v>0.8506161671247143</v>
       </c>
       <c r="D105" t="n">
-        <v>0.8646433018828112</v>
+        <v>1.161213942069963</v>
       </c>
       <c r="E105" t="n">
-        <v>0.3877464264867728</v>
+        <v>0.2462456668125597</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0721268870305414</v>
+        <v>0.115220886481386</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0583806186902532</v>
+        <v>0.1019822962541748</v>
       </c>
       <c r="H105" t="n">
-        <v>689.4918703672215</v>
+        <v>934.1018226792656</v>
       </c>
       <c r="I105" t="n">
-        <v>717.6390338126682</v>
+        <v>962.1806929000948</v>
       </c>
       <c r="J105" t="n">
-        <v>0.8394484088858698</v>
+        <v>0.8260269932896634</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_96_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_96_2ndlvl</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.0045196797747258</v>
+        <v>0.0107235170890155</v>
       </c>
       <c r="C106" t="n">
-        <v>0.5068987692911642</v>
+        <v>0.8557672385782029</v>
       </c>
       <c r="D106" t="n">
-        <v>0.4053922504615562</v>
+        <v>0.7047934942275705</v>
       </c>
       <c r="E106" t="n">
-        <v>0.6854032691275337</v>
+        <v>0.4813478970587905</v>
       </c>
       <c r="F106" t="n">
-        <v>0.0707911424820184</v>
+        <v>0.1133440289468372</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0570250853336038</v>
+        <v>0.1000773560632488</v>
       </c>
       <c r="H106" t="n">
-        <v>690.0845494817045</v>
+        <v>934.9663851656968</v>
       </c>
       <c r="I106" t="n">
-        <v>718.2317129271512</v>
+        <v>963.0452553865258</v>
       </c>
       <c r="J106" t="n">
-        <v>0.8727092659790077</v>
+        <v>0.8260269932896634</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_97_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_97_2ndlvl</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-0.0010311942062433</v>
+        <v>-0.0116526728991546</v>
       </c>
       <c r="C107" t="n">
-        <v>0.5232722417798965</v>
+        <v>0.9143704658141882</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.08088271688777809</v>
+        <v>-0.6703376354661307</v>
       </c>
       <c r="E107" t="n">
-        <v>0.9355751785555464</v>
+        <v>0.5030284394553433</v>
       </c>
       <c r="F107" t="n">
-        <v>0.0704290990474884</v>
+        <v>0.1132393807924443</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0566576782926363</v>
+        <v>0.09997114210105951</v>
       </c>
       <c r="H107" t="n">
-        <v>690.2450439095493</v>
+        <v>935.014536792648</v>
       </c>
       <c r="I107" t="n">
-        <v>718.392207354996</v>
+        <v>963.0934070134772</v>
       </c>
       <c r="J107" t="n">
-        <v>0.9355751785555464</v>
+        <v>0.8260269932896634</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_98_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_98_2ndlvl</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-0.0165404954792146</v>
+        <v>0.0052698092363555</v>
       </c>
       <c r="C108" t="n">
-        <v>0.5545725079192168</v>
+        <v>0.8794849067717828</v>
       </c>
       <c r="D108" t="n">
-        <v>-1.163683858469044</v>
+        <v>0.2714955227020371</v>
       </c>
       <c r="E108" t="n">
-        <v>0.2452372565404932</v>
+        <v>0.7861496554997668</v>
       </c>
       <c r="F108" t="n">
-        <v>0.07351189406291581</v>
+        <v>0.1124088472302776</v>
       </c>
       <c r="G108" t="n">
-        <v>0.0597861443453293</v>
+        <v>0.0991281816028005</v>
       </c>
       <c r="H108" t="n">
-        <v>688.8764314790188</v>
+        <v>935.3964877940932</v>
       </c>
       <c r="I108" t="n">
-        <v>717.0235949244656</v>
+        <v>963.4753580149224</v>
       </c>
       <c r="J108" t="n">
-        <v>0.6539660174413153</v>
+        <v>0.8809214618370783</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>cl_p_fl-DRPutamen-roi_99_2ndlvl</t>
+          <t>dawba_p-DRPutamen-roi_99_2ndlvl</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-0.0267913564468139</v>
+        <v>-0.0177398107267057</v>
       </c>
       <c r="C109" t="n">
-        <v>0.5710188365738231</v>
+        <v>0.9240941153934316</v>
       </c>
       <c r="D109" t="n">
-        <v>-1.678194978453032</v>
+        <v>-0.812962348170193</v>
       </c>
       <c r="E109" t="n">
-        <v>0.09408045574443499</v>
+        <v>0.4167220446352192</v>
       </c>
       <c r="F109" t="n">
-        <v>0.07683370989554569</v>
+        <v>0.1137064385685004</v>
       </c>
       <c r="G109" t="n">
-        <v>0.0631571722643685</v>
+        <v>0.1004451882727673</v>
       </c>
       <c r="H109" t="n">
-        <v>687.3965987088064</v>
+        <v>934.7995861395666</v>
       </c>
       <c r="I109" t="n">
-        <v>715.5437621542532</v>
+        <v>962.8784563603956</v>
       </c>
       <c r="J109" t="n">
-        <v>0.4226878817466874</v>
+        <v>0.8260269932896634</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_100_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_100_2ndlvl</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-0.0021267056219435</v>
+        <v>-0.0090800910638293</v>
       </c>
       <c r="C110" t="n">
-        <v>0.5245193914408677</v>
+        <v>0.9027873943953316</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.217475225040466</v>
+        <v>-0.6802051527401941</v>
       </c>
       <c r="E110" t="n">
-        <v>0.8279475328801258</v>
+        <v>0.4967670830011691</v>
       </c>
       <c r="F110" t="n">
-        <v>0.0705226269653265</v>
+        <v>0.1132688167022174</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0567525918092572</v>
+        <v>0.1000010184483853</v>
       </c>
       <c r="H110" t="n">
-        <v>690.2035888244707</v>
+        <v>935.000993057998</v>
       </c>
       <c r="I110" t="n">
-        <v>718.3507522699174</v>
+        <v>963.0798632788272</v>
       </c>
       <c r="J110" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_24_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_24_2ndlvl</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>-0.0041908487325084</v>
+        <v>-0.0022478742627605</v>
       </c>
       <c r="C111" t="n">
-        <v>0.5230709378314592</v>
+        <v>0.8913731893639422</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.4132319800685002</v>
+        <v>-0.1622865025965358</v>
       </c>
       <c r="E111" t="n">
-        <v>0.6796553614814949</v>
+        <v>0.8711619861794631</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0708058608929318</v>
+        <v>0.1123039968205713</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0570400217950493</v>
+        <v>0.0990217623590338</v>
       </c>
       <c r="H111" t="n">
-        <v>690.0780234641428</v>
+        <v>935.444681650582</v>
       </c>
       <c r="I111" t="n">
-        <v>718.2251869095895</v>
+        <v>963.523551871411</v>
       </c>
       <c r="J111" t="n">
-        <v>0.9062071486419933</v>
+        <v>0.9246859000722089</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_25_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_25_2ndlvl</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-0.0041648636260402</v>
+        <v>-0.0008397234544043</v>
       </c>
       <c r="C112" t="n">
-        <v>0.5255598329019258</v>
+        <v>0.8913961751199782</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.6403423263318799</v>
+        <v>-0.0945923173001834</v>
       </c>
       <c r="E112" t="n">
-        <v>0.5223121772445984</v>
+        <v>0.9246859000722089</v>
       </c>
       <c r="F112" t="n">
-        <v>0.0713542818649604</v>
+        <v>0.1122655031021983</v>
       </c>
       <c r="G112" t="n">
-        <v>0.057596567522219</v>
+        <v>0.0989826926747997</v>
       </c>
       <c r="H112" t="n">
-        <v>689.834784579846</v>
+        <v>935.4623736268072</v>
       </c>
       <c r="I112" t="n">
-        <v>717.9819480252927</v>
+        <v>963.5412438476365</v>
       </c>
       <c r="J112" t="n">
-        <v>0.9062071486419933</v>
+        <v>0.9246859000722089</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_26_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_26_2ndlvl</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-2.023590887341669e-05</v>
+        <v>-0.0012017376914444</v>
       </c>
       <c r="C113" t="n">
-        <v>0.5211740953532046</v>
+        <v>0.8894976213158331</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.0026743334649167</v>
+        <v>-0.1162778177308183</v>
       </c>
       <c r="E113" t="n">
-        <v>0.997867509924629</v>
+        <v>0.9074905744974434</v>
       </c>
       <c r="F113" t="n">
-        <v>0.0704140999924435</v>
+        <v>0.112275626087494</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0566424570293685</v>
+        <v>0.0989929671262097</v>
       </c>
       <c r="H113" t="n">
-        <v>690.2516916658606</v>
+        <v>935.45772110788</v>
       </c>
       <c r="I113" t="n">
-        <v>718.3988551113073</v>
+        <v>963.5365913287091</v>
       </c>
       <c r="J113" t="n">
-        <v>0.997867509924629</v>
+        <v>0.9246859000722089</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_27_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_27_2ndlvl</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-0.0045601024713247</v>
+        <v>-0.0161781611129554</v>
       </c>
       <c r="C114" t="n">
-        <v>0.5315280721719828</v>
+        <v>0.9230752863230004</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.5500957483589396</v>
+        <v>-1.42692658794537</v>
       </c>
       <c r="E114" t="n">
-        <v>0.5825569465211961</v>
+        <v>0.154379213177544</v>
       </c>
       <c r="F114" t="n">
-        <v>0.07110812711705861</v>
+        <v>0.1167305875798021</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0573467660373112</v>
+        <v>0.1035145863964576</v>
       </c>
       <c r="H114" t="n">
-        <v>689.943978339606</v>
+        <v>933.4050565115756</v>
       </c>
       <c r="I114" t="n">
-        <v>718.0911417850527</v>
+        <v>961.4839267324046</v>
       </c>
       <c r="J114" t="n">
-        <v>0.9062071486419933</v>
+        <v>0.9246859000722089</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_28_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_28_2ndlvl</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-0.0010155881665811</v>
+        <v>-0.0013406361040899</v>
       </c>
       <c r="C115" t="n">
-        <v>0.5208169708735844</v>
+        <v>0.8895890911223159</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.1040697247368587</v>
+        <v>-0.1006496723902816</v>
       </c>
       <c r="E115" t="n">
-        <v>0.9171655323358872</v>
+        <v>0.9198788664438952</v>
       </c>
       <c r="F115" t="n">
-        <v>0.0704389418928317</v>
+        <v>0.1122681211888165</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0566676669579107</v>
+        <v>0.0989853499347839</v>
       </c>
       <c r="H115" t="n">
-        <v>690.2406813872853</v>
+        <v>935.4611703606068</v>
       </c>
       <c r="I115" t="n">
-        <v>718.3878448327321</v>
+        <v>963.5400405814358</v>
       </c>
       <c r="J115" t="n">
-        <v>0.997867509924629</v>
+        <v>0.9246859000722089</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_29_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_29_2ndlvl</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-0.0040487352069004</v>
+        <v>-0.0177590535212112</v>
       </c>
       <c r="C116" t="n">
-        <v>0.5273118310001299</v>
+        <v>0.9105668985221084</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.4835808306829218</v>
+        <v>-1.540231436168346</v>
       </c>
       <c r="E116" t="n">
-        <v>0.6289447260309449</v>
+        <v>0.1242926602334806</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0709505245884684</v>
+        <v>0.1174667544613418</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0571868286564456</v>
+        <v>0.1042617682438058</v>
       </c>
       <c r="H116" t="n">
-        <v>690.0138753167031</v>
+        <v>933.064864357355</v>
       </c>
       <c r="I116" t="n">
-        <v>718.1610387621498</v>
+        <v>961.143734578184</v>
       </c>
       <c r="J116" t="n">
-        <v>0.9062071486419933</v>
+        <v>0.9246859000722089</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_30_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_30_2ndlvl</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-0.0072103176342001</v>
+        <v>0.0121154494518379</v>
       </c>
       <c r="C117" t="n">
-        <v>0.5252870392835876</v>
+        <v>0.8828778956096346</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.6544955854469283</v>
+        <v>0.8037376317367426</v>
       </c>
       <c r="E117" t="n">
-        <v>0.513164070230205</v>
+        <v>0.4220246983847836</v>
       </c>
       <c r="F117" t="n">
-        <v>0.07139625851683511</v>
+        <v>0.1136735294225111</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0576391660504178</v>
+        <v>0.1004117867206036</v>
       </c>
       <c r="H117" t="n">
-        <v>689.8161609313256</v>
+        <v>934.8147353890648</v>
       </c>
       <c r="I117" t="n">
-        <v>717.9633243767723</v>
+        <v>962.8936056098941</v>
       </c>
       <c r="J117" t="n">
-        <v>0.9062071486419933</v>
+        <v>0.9246859000722089</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_38_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_38_2ndlvl</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-0.0045704599292938</v>
+        <v>-0.0108430706047896</v>
       </c>
       <c r="C118" t="n">
-        <v>0.5224821337608461</v>
+        <v>0.8946519799128074</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.5950573435224112</v>
+        <v>-1.031736667939447</v>
       </c>
       <c r="E118" t="n">
-        <v>0.5521374632544358</v>
+        <v>0.3028173511415937</v>
       </c>
       <c r="F118" t="n">
-        <v>0.07122611457958911</v>
+        <v>0.1145960569433478</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0574665014622497</v>
+        <v>0.1013481176457421</v>
       </c>
       <c r="H118" t="n">
-        <v>689.8916429456731</v>
+        <v>934.3898499103028</v>
       </c>
       <c r="I118" t="n">
-        <v>718.0388063911198</v>
+        <v>962.4687201311318</v>
       </c>
       <c r="J118" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_39_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_39_2ndlvl</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-2.771314827421795e-05</v>
+        <v>0.0084696551175214</v>
       </c>
       <c r="C119" t="n">
-        <v>0.52124499079176</v>
+        <v>0.8702622013094333</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.0037009149369913</v>
+        <v>0.8255963742245991</v>
       </c>
       <c r="E119" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.4095239835185121</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0704141150143488</v>
+        <v>0.1137521157632798</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0566424722738205</v>
+        <v>0.100491548916845</v>
       </c>
       <c r="H119" t="n">
-        <v>690.2516850080304</v>
+        <v>934.7785583711952</v>
       </c>
       <c r="I119" t="n">
-        <v>718.3988484534772</v>
+        <v>962.8574285920243</v>
       </c>
       <c r="J119" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_40_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_40_2ndlvl</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.0007522967601928</v>
+        <v>-0.0005442275240575</v>
       </c>
       <c r="C120" t="n">
-        <v>0.5201715221126425</v>
+        <v>0.8912074545373647</v>
       </c>
       <c r="D120" t="n">
-        <v>0.0995181938314227</v>
+        <v>-0.0522815437401177</v>
       </c>
       <c r="E120" t="n">
-        <v>0.9207760834202356</v>
+        <v>0.9583303931076094</v>
       </c>
       <c r="F120" t="n">
-        <v>0.07043681511670551</v>
+        <v>0.1122517458645006</v>
       </c>
       <c r="G120" t="n">
-        <v>0.05666550867399</v>
+        <v>0.0989687295931465</v>
       </c>
       <c r="H120" t="n">
-        <v>690.2416240158024</v>
+        <v>935.468696361261</v>
       </c>
       <c r="I120" t="n">
-        <v>718.3887874612491</v>
+        <v>963.54756658209</v>
       </c>
       <c r="J120" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_41_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_41_2ndlvl</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-0.003060089698313</v>
+        <v>-0.0026675775277265</v>
       </c>
       <c r="C121" t="n">
-        <v>0.522777303700291</v>
+        <v>0.8919423384968539</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.3338354666521109</v>
+        <v>-0.2122914344829683</v>
       </c>
       <c r="E121" t="n">
-        <v>0.7386765009042298</v>
+        <v>0.8319875437807035</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0706698125702568</v>
+        <v>0.1123454565170757</v>
       </c>
       <c r="G121" t="n">
-        <v>0.056901957941668</v>
+        <v>0.0990638424001242</v>
       </c>
       <c r="H121" t="n">
-        <v>690.1383421893183</v>
+        <v>935.425625632368</v>
       </c>
       <c r="I121" t="n">
-        <v>718.2855056347651</v>
+        <v>963.504495853197</v>
       </c>
       <c r="J121" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_42_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_42_2ndlvl</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.0004160413398737</v>
+        <v>-0.0007622819439921001</v>
       </c>
       <c r="C122" t="n">
-        <v>0.5207965039054946</v>
+        <v>0.8910571001749491</v>
       </c>
       <c r="D122" t="n">
-        <v>0.0426457086799351</v>
+        <v>-0.0573712735146874</v>
       </c>
       <c r="E122" t="n">
-        <v>0.9660049748327972</v>
+        <v>0.9542780220442908</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0704182578724311</v>
+        <v>0.1122529814033599</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0566466765075782</v>
+        <v>0.09896998361887149</v>
       </c>
       <c r="H122" t="n">
-        <v>690.2498488556523</v>
+        <v>935.4681285198676</v>
       </c>
       <c r="I122" t="n">
-        <v>718.397012301099</v>
+        <v>963.5469987406968</v>
       </c>
       <c r="J122" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_43_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_43_2ndlvl</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-0.003594199728025</v>
+        <v>0.0015635394444079</v>
       </c>
       <c r="C123" t="n">
-        <v>0.5207436101936018</v>
+        <v>0.8902271772914532</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.3454105106293357</v>
+        <v>0.1099328263298928</v>
       </c>
       <c r="E123" t="n">
-        <v>0.7299651074377493</v>
+        <v>0.9125176431270386</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0706878484290608</v>
+        <v>0.1122724487396867</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0569202609983802</v>
+        <v>0.0989897422370387</v>
       </c>
       <c r="H123" t="n">
-        <v>690.1303462735128</v>
+        <v>935.4591814210396</v>
       </c>
       <c r="I123" t="n">
-        <v>718.2775097189595</v>
+        <v>963.5380516418688</v>
       </c>
       <c r="J123" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_44_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_44_2ndlvl</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>-0.008697249169542801</v>
+        <v>-0.0001116912446552</v>
       </c>
       <c r="C124" t="n">
-        <v>0.5246269166777029</v>
+        <v>0.8904368865124793</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.7835692655681958</v>
+        <v>-0.0073539026969402</v>
       </c>
       <c r="E124" t="n">
-        <v>0.4337508841270163</v>
+        <v>0.994136144500414</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0718212044501205</v>
+        <v>0.1122458143788144</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0580704074790111</v>
+        <v>0.098962709357051</v>
       </c>
       <c r="H124" t="n">
-        <v>689.6275790978815</v>
+        <v>935.4714224021898</v>
       </c>
       <c r="I124" t="n">
-        <v>717.7747425433282</v>
+        <v>963.5502926230188</v>
       </c>
       <c r="J124" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_45_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_45_2ndlvl</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.0067437221951401</v>
+        <v>0.0064969634535518</v>
       </c>
       <c r="C125" t="n">
-        <v>0.4930124822922896</v>
+        <v>0.8631783092460927</v>
       </c>
       <c r="D125" t="n">
-        <v>0.8503970166529526</v>
+        <v>0.6008244851473624</v>
       </c>
       <c r="E125" t="n">
-        <v>0.3956068564494917</v>
+        <v>0.5482963355662356</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0720710098165453</v>
+        <v>0.1130441541197352</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0583239136656793</v>
+        <v>0.0997729943310031</v>
       </c>
       <c r="H125" t="n">
-        <v>689.5166805688418</v>
+        <v>935.1043510153322</v>
       </c>
       <c r="I125" t="n">
-        <v>717.6638440142885</v>
+        <v>963.1832212361612</v>
       </c>
       <c r="J125" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_46_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_46_2ndlvl</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-0.0051548269139794</v>
+        <v>0.0045395710189346</v>
       </c>
       <c r="C126" t="n">
-        <v>0.5227876593854262</v>
+        <v>0.8890983040454814</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.4556474861855528</v>
+        <v>0.2906159103481519</v>
       </c>
       <c r="E126" t="n">
-        <v>0.6488876866611915</v>
+        <v>0.7714953294888899</v>
       </c>
       <c r="F126" t="n">
-        <v>0.0708903718560781</v>
+        <v>0.1124326318517052</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0571257847724644</v>
+        <v>0.0991523221038505</v>
       </c>
       <c r="H126" t="n">
-        <v>690.0405500247043</v>
+        <v>935.3855545445512</v>
       </c>
       <c r="I126" t="n">
-        <v>718.187713470151</v>
+        <v>963.4644247653804</v>
       </c>
       <c r="J126" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_47_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_47_2ndlvl</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.000177362713155</v>
+        <v>0.0032750490229368</v>
       </c>
       <c r="C127" t="n">
-        <v>0.5212074144432381</v>
+        <v>0.891442588932553</v>
       </c>
       <c r="D127" t="n">
-        <v>0.0198540041370333</v>
+        <v>0.268725517102847</v>
       </c>
       <c r="E127" t="n">
-        <v>0.984169614704106</v>
+        <v>0.7882791119492798</v>
       </c>
       <c r="F127" t="n">
-        <v>0.0704149883300788</v>
+        <v>0.1124055355947635</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0566433585275615</v>
+        <v>0.0991248204166302</v>
       </c>
       <c r="H127" t="n">
-        <v>690.2512979472374</v>
+        <v>935.3980100543872</v>
       </c>
       <c r="I127" t="n">
-        <v>718.3984613926841</v>
+        <v>963.4768802752164</v>
       </c>
       <c r="J127" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_48_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_48_2ndlvl</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.0102203912477366</v>
+        <v>0.0090764656654209</v>
       </c>
       <c r="C128" t="n">
-        <v>0.526735298170261</v>
+        <v>0.898908142078028</v>
       </c>
       <c r="D128" t="n">
-        <v>1.020235372474817</v>
+        <v>0.6584497519306771</v>
       </c>
       <c r="E128" t="n">
-        <v>0.3082258869962933</v>
+        <v>0.5106270349309783</v>
       </c>
       <c r="F128" t="n">
-        <v>0.0727970642957558</v>
+        <v>0.1132044866311449</v>
       </c>
       <c r="G128" t="n">
-        <v>0.0590607245075447</v>
+        <v>0.0999357258326084</v>
       </c>
       <c r="H128" t="n">
-        <v>689.1941865655488</v>
+        <v>935.0305913370184</v>
       </c>
       <c r="I128" t="n">
-        <v>717.3413500109955</v>
+        <v>963.1094615578476</v>
       </c>
       <c r="J128" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_49_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_49_2ndlvl</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.0004637178961905</v>
+        <v>0.0043578475392874</v>
       </c>
       <c r="C129" t="n">
-        <v>0.5209285199534452</v>
+        <v>0.8888907852890809</v>
       </c>
       <c r="D129" t="n">
-        <v>0.0555513978112668</v>
+        <v>0.3826595257526425</v>
       </c>
       <c r="E129" t="n">
-        <v>0.9557265774674294</v>
+        <v>0.7021749710755796</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0704211666408306</v>
+        <v>0.1125697468100468</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0566496283688429</v>
+        <v>0.0992914886575787</v>
       </c>
       <c r="H129" t="n">
-        <v>690.2485596581549</v>
+        <v>935.322520203049</v>
       </c>
       <c r="I129" t="n">
-        <v>718.3957231036017</v>
+        <v>963.401390423878</v>
       </c>
       <c r="J129" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_50_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_50_2ndlvl</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.0021350311588808</v>
+        <v>-0.0053509032813063</v>
       </c>
       <c r="C130" t="n">
-        <v>0.5161916690444603</v>
+        <v>0.9027046455987424</v>
       </c>
       <c r="D130" t="n">
-        <v>0.2526618478902991</v>
+        <v>-0.4645650885093271</v>
       </c>
       <c r="E130" t="n">
-        <v>0.8006577173523062</v>
+        <v>0.6424950678351864</v>
       </c>
       <c r="F130" t="n">
-        <v>0.0705605861987698</v>
+        <v>0.1127232325893742</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0567911134017145</v>
+        <v>0.0994472709822327</v>
       </c>
       <c r="H130" t="n">
-        <v>690.1867626768005</v>
+        <v>935.2519483313037</v>
       </c>
       <c r="I130" t="n">
-        <v>718.3339261222472</v>
+        <v>963.3308185521328</v>
       </c>
       <c r="J130" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_74_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_74_2ndlvl</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-0.008454316264930799</v>
+        <v>-0.004460475580563</v>
       </c>
       <c r="C131" t="n">
-        <v>0.545944602002193</v>
+        <v>0.9047688763586832</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.9214753493252476</v>
+        <v>-0.3549448744556639</v>
       </c>
       <c r="E131" t="n">
-        <v>0.3573508814546192</v>
+        <v>0.7228174938789136</v>
       </c>
       <c r="F131" t="n">
-        <v>0.0723589616211165</v>
+        <v>0.1125245210004347</v>
       </c>
       <c r="G131" t="n">
-        <v>0.0586161314229108</v>
+        <v>0.09924558615256091</v>
       </c>
       <c r="H131" t="n">
-        <v>689.3888102728039</v>
+        <v>935.3433124400576</v>
       </c>
       <c r="I131" t="n">
-        <v>717.5359737182506</v>
+        <v>963.4221826608868</v>
       </c>
       <c r="J131" t="n">
-        <v>0.9062071486419933</v>
+        <v>0.9246859000722089</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_75_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_75_2ndlvl</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-0.0061671547892966</v>
+        <v>-0.007832073308888</v>
       </c>
       <c r="C132" t="n">
-        <v>0.5076450145567482</v>
+        <v>0.8742655043008249</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.549903372463131</v>
+        <v>-0.5103964358779657</v>
       </c>
       <c r="E132" t="n">
-        <v>0.5826887716145669</v>
+        <v>0.6100545877958417</v>
       </c>
       <c r="F132" t="n">
-        <v>0.0711076421312979</v>
+        <v>0.1128220384709269</v>
       </c>
       <c r="G132" t="n">
-        <v>0.0573462738665764</v>
+        <v>0.09954755525602819</v>
       </c>
       <c r="H132" t="n">
-        <v>689.9441934497677</v>
+        <v>935.2065115004192</v>
       </c>
       <c r="I132" t="n">
-        <v>718.0913568952144</v>
+        <v>963.2853817212484</v>
       </c>
       <c r="J132" t="n">
-        <v>0.9062071486419933</v>
+        <v>0.9246859000722089</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_76_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_76_2ndlvl</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-0.0052545268301633</v>
+        <v>-0.0040793373732105</v>
       </c>
       <c r="C133" t="n">
-        <v>0.5236230193413096</v>
+        <v>0.8928867498266239</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.5993270695508188</v>
+        <v>-0.3395763042444443</v>
       </c>
       <c r="E133" t="n">
-        <v>0.5492899113622132</v>
+        <v>0.7343534045503426</v>
       </c>
       <c r="F133" t="n">
-        <v>0.07123779918646241</v>
+        <v>0.1125009050145513</v>
       </c>
       <c r="G133" t="n">
-        <v>0.05747835917441</v>
+        <v>0.0992216168102803</v>
       </c>
       <c r="H133" t="n">
-        <v>689.8864596729846</v>
+        <v>935.3541692966932</v>
       </c>
       <c r="I133" t="n">
-        <v>718.0336231184314</v>
+        <v>963.4330395175224</v>
       </c>
       <c r="J133" t="n">
-        <v>0.9062071486419933</v>
+        <v>0.9246859000722089</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_77_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_77_2ndlvl</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-0.0010080157295786</v>
+        <v>0.0027959567419592</v>
       </c>
       <c r="C134" t="n">
-        <v>0.5212806130946224</v>
+        <v>0.8888044913901857</v>
       </c>
       <c r="D134" t="n">
-        <v>-0.1707856174317275</v>
+        <v>0.3459326307193966</v>
       </c>
       <c r="E134" t="n">
-        <v>0.8644776272561949</v>
+        <v>0.7295747637315093</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0704810266771707</v>
+        <v>0.1125105458190349</v>
       </c>
       <c r="G134" t="n">
-        <v>0.0567103752205362</v>
+        <v>0.09923140186620261</v>
       </c>
       <c r="H134" t="n">
-        <v>690.222028149278</v>
+        <v>935.3497372137582</v>
       </c>
       <c r="I134" t="n">
-        <v>718.3691915947247</v>
+        <v>963.4286074345872</v>
       </c>
       <c r="J134" t="n">
-        <v>0.997867509924629</v>
+        <v>0.9246859000722089</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_78_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_78_2ndlvl</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.0039118833431253</v>
+        <v>0.0060187126543782</v>
       </c>
       <c r="C135" t="n">
-        <v>0.5128953465359678</v>
+        <v>0.8787147214242473</v>
       </c>
       <c r="D135" t="n">
-        <v>0.4335506570533458</v>
+        <v>0.489052060808801</v>
       </c>
       <c r="E135" t="n">
-        <v>0.6648456045447114</v>
+        <v>0.6250722146290572</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0708453172780447</v>
+        <v>0.1127748700559794</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0570800627192009</v>
+        <v>0.09949968107926099</v>
       </c>
       <c r="H135" t="n">
-        <v>690.0605283303141</v>
+        <v>935.2282029789742</v>
       </c>
       <c r="I135" t="n">
-        <v>718.2076917757608</v>
+        <v>963.3070731998032</v>
       </c>
       <c r="J135" t="n">
-        <v>0.9062071486419933</v>
+        <v>0.9246859000722089</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_90_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_90_2ndlvl</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-0.0061877429155193</v>
+        <v>0.0001282915822084</v>
       </c>
       <c r="C136" t="n">
-        <v>0.4986032711815875</v>
+        <v>0.890835833992187</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.643840951772487</v>
+        <v>0.009744440900905701</v>
       </c>
       <c r="E136" t="n">
-        <v>0.5200430018336397</v>
+        <v>0.9922300300265759</v>
       </c>
       <c r="F136" t="n">
-        <v>0.0713645732827696</v>
+        <v>0.1122459048682711</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0576070114054774</v>
+        <v>0.0989628012004647</v>
       </c>
       <c r="H136" t="n">
-        <v>689.8302186969163</v>
+        <v>935.4713808144384</v>
       </c>
       <c r="I136" t="n">
-        <v>717.977382142363</v>
+        <v>963.5502510352676</v>
       </c>
       <c r="J136" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_91_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_91_2ndlvl</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-0.0066282819922693</v>
+        <v>-0.0130489791639328</v>
       </c>
       <c r="C137" t="n">
-        <v>0.5276778543626599</v>
+        <v>0.9076205285511176</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.8424256093603235</v>
+        <v>-1.211045086714155</v>
       </c>
       <c r="E137" t="n">
-        <v>0.4000469630551634</v>
+        <v>0.2265913623406845</v>
       </c>
       <c r="F137" t="n">
-        <v>0.072040146270184</v>
+        <v>0.1154807635479775</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0582925928815941</v>
+        <v>0.1022460617556779</v>
       </c>
       <c r="H137" t="n">
-        <v>689.5303837398519</v>
+        <v>933.9819674338984</v>
       </c>
       <c r="I137" t="n">
-        <v>717.6775471852986</v>
+        <v>962.0608376547276</v>
       </c>
       <c r="J137" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_92_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_92_2ndlvl</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-0.0048958315761978</v>
+        <v>0.0062292397589584</v>
       </c>
       <c r="C138" t="n">
-        <v>0.5149850902964079</v>
+        <v>0.8953847324310384</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.5260037669638148</v>
+        <v>0.4866726898429642</v>
       </c>
       <c r="E138" t="n">
-        <v>0.599173492131461</v>
+        <v>0.6267561860620932</v>
       </c>
       <c r="F138" t="n">
-        <v>0.0710487063158554</v>
+        <v>0.1127697364503649</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0572864649279422</v>
+        <v>0.0994944706615923</v>
       </c>
       <c r="H138" t="n">
-        <v>689.9703329539723</v>
+        <v>935.2305637157932</v>
       </c>
       <c r="I138" t="n">
-        <v>718.117496399419</v>
+        <v>963.3094339366224</v>
       </c>
       <c r="J138" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_93_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_93_2ndlvl</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>-0.0027257146332993</v>
+        <v>-0.0077600762080399</v>
       </c>
       <c r="C139" t="n">
-        <v>0.5180574877085649</v>
+        <v>0.8809641873569891</v>
       </c>
       <c r="D139" t="n">
-        <v>-0.302047496005786</v>
+        <v>-0.6285523020411673</v>
       </c>
       <c r="E139" t="n">
-        <v>0.7627709029131675</v>
+        <v>0.5300000403933791</v>
       </c>
       <c r="F139" t="n">
-        <v>0.0706234404244282</v>
+        <v>0.1131194776460826</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0568548988010864</v>
+        <v>0.0998494448926574</v>
       </c>
       <c r="H139" t="n">
-        <v>690.1588998422305</v>
+        <v>935.0697006954732</v>
       </c>
       <c r="I139" t="n">
-        <v>718.3060632876773</v>
+        <v>963.1485709163024</v>
       </c>
       <c r="J139" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_94_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_94_2ndlvl</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-0.008724389846570599</v>
+        <v>-0.0086459934233695</v>
       </c>
       <c r="C140" t="n">
-        <v>0.5254983607442453</v>
+        <v>0.8953417228179095</v>
       </c>
       <c r="D140" t="n">
-        <v>-0.9217696812205524</v>
+        <v>-0.6636665713533721</v>
       </c>
       <c r="E140" t="n">
-        <v>0.357197488562192</v>
+        <v>0.5072851068304129</v>
       </c>
       <c r="F140" t="n">
-        <v>0.07236020165960889</v>
+        <v>0.1132197228718153</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0586173898323438</v>
+        <v>0.0999511900469547</v>
       </c>
       <c r="H140" t="n">
-        <v>689.3882595250695</v>
+        <v>935.0235813335814</v>
       </c>
       <c r="I140" t="n">
-        <v>717.5354229705163</v>
+        <v>963.1024515544104</v>
       </c>
       <c r="J140" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_95_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_95_2ndlvl</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-0.0001882848507756</v>
+        <v>0.0041862060940348</v>
       </c>
       <c r="C141" t="n">
-        <v>0.521678188997121</v>
+        <v>0.879788597641543</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.0225671974688247</v>
+        <v>0.366113761752591</v>
       </c>
       <c r="E141" t="n">
-        <v>0.9820066240006043</v>
+        <v>0.7144732623659875</v>
       </c>
       <c r="F141" t="n">
-        <v>0.07041525250844501</v>
+        <v>0.1125423385237985</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0566436266196812</v>
+        <v>0.0992636702722843</v>
       </c>
       <c r="H141" t="n">
-        <v>690.2511808611172</v>
+        <v>935.3351210897844</v>
       </c>
       <c r="I141" t="n">
-        <v>718.3983443065639</v>
+        <v>963.4139913106134</v>
       </c>
       <c r="J141" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_96_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_96_2ndlvl</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.0004189928089756</v>
+        <v>0.008321426371040601</v>
       </c>
       <c r="C142" t="n">
-        <v>0.5203157217051835</v>
+        <v>0.8719510180193608</v>
       </c>
       <c r="D142" t="n">
-        <v>0.0594086711274511</v>
+        <v>0.8615533781965058</v>
       </c>
       <c r="E142" t="n">
-        <v>0.9526559091393664</v>
+        <v>0.3894482198038417</v>
       </c>
       <c r="F142" t="n">
-        <v>0.0704221844230204</v>
+        <v>0.1138859430916915</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0566506612292873</v>
+        <v>0.1006273786491732</v>
       </c>
       <c r="H142" t="n">
-        <v>690.2481085651689</v>
+        <v>934.716943924588</v>
       </c>
       <c r="I142" t="n">
-        <v>718.3952720106156</v>
+        <v>962.7958141454172</v>
       </c>
       <c r="J142" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_97_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_97_2ndlvl</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-0.0015711357527481</v>
+        <v>0.0041718374346714</v>
       </c>
       <c r="C143" t="n">
-        <v>0.5242443649428403</v>
+        <v>0.8822481437694989</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.1888707258122491</v>
+        <v>0.3670431244267281</v>
       </c>
       <c r="E143" t="n">
-        <v>0.8502887460454395</v>
+        <v>0.7137804646362169</v>
       </c>
       <c r="F143" t="n">
-        <v>0.07049595372159009</v>
+        <v>0.1125438459620543</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0567255234063543</v>
+        <v>0.09926520026572599</v>
       </c>
       <c r="H143" t="n">
-        <v>690.2154118328192</v>
+        <v>935.3344280591672</v>
       </c>
       <c r="I143" t="n">
-        <v>718.3625752782659</v>
+        <v>963.4132982799964</v>
       </c>
       <c r="J143" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_98_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_98_2ndlvl</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-0.0108673433370248</v>
+        <v>-4.419297343604984e-05</v>
       </c>
       <c r="C144" t="n">
-        <v>0.5343327922387551</v>
+        <v>0.8904422621813571</v>
       </c>
       <c r="D144" t="n">
-        <v>-1.117118861883095</v>
+        <v>-0.0033251176822971</v>
       </c>
       <c r="E144" t="n">
-        <v>0.2646057803437339</v>
+        <v>0.997348598346726</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0732696818939481</v>
+        <v>0.1122457191312555</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0595403438479325</v>
+        <v>0.0989626126843417</v>
       </c>
       <c r="H144" t="n">
-        <v>688.9841267327333</v>
+        <v>935.4714661766968</v>
       </c>
       <c r="I144" t="n">
-        <v>717.1312901781801</v>
+        <v>963.5503363975261</v>
       </c>
       <c r="J144" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>cl_p_fl-InfVentralCaudate-roi_99_2ndlvl</t>
+          <t>dawba_p-InfVentralCaudate-roi_99_2ndlvl</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-0.0107907458646285</v>
+        <v>-0.0030339737235856</v>
       </c>
       <c r="C145" t="n">
-        <v>0.5218450885933833</v>
+        <v>0.8904827092775556</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.8743682047987533</v>
+        <v>-0.1800277381401731</v>
       </c>
       <c r="E145" t="n">
-        <v>0.3824359578666774</v>
+        <v>0.8572217311589583</v>
       </c>
       <c r="F145" t="n">
-        <v>0.0721655595307952</v>
+        <v>0.1123174397407842</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0584198641164366</v>
+        <v>0.0990354064201974</v>
       </c>
       <c r="H145" t="n">
-        <v>689.4746984048858</v>
+        <v>935.4385030117724</v>
       </c>
       <c r="I145" t="n">
-        <v>717.6218618503325</v>
+        <v>963.5173732326016</v>
       </c>
       <c r="J145" t="n">
-        <v>0.9970489260795024</v>
+        <v>0.997348598346726</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_100_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_100_2ndlvl</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.0187909788129035</v>
+        <v>0.0050222302531432</v>
       </c>
       <c r="C146" t="n">
-        <v>0.5389166050867396</v>
+        <v>0.8956070112773291</v>
       </c>
       <c r="D146" t="n">
-        <v>1.668953456211047</v>
+        <v>0.3261097794522093</v>
       </c>
       <c r="E146" t="n">
-        <v>0.09589939468861559</v>
+        <v>0.7445114162943597</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0767636826983371</v>
+        <v>0.1124810699601001</v>
       </c>
       <c r="G146" t="n">
-        <v>0.06308610762720129</v>
+        <v>0.099201484971972</v>
       </c>
       <c r="H146" t="n">
-        <v>687.4278499702031</v>
+        <v>935.3632877418046</v>
       </c>
       <c r="I146" t="n">
-        <v>715.5750134156498</v>
+        <v>963.4421579626336</v>
       </c>
       <c r="J146" t="n">
-        <v>0.7438634825720358</v>
+        <v>0.8508701900506968</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_24_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_24_2ndlvl</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.0099995663335062</v>
+        <v>0.0167266230045078</v>
       </c>
       <c r="C147" t="n">
-        <v>0.5358742946384617</v>
+        <v>0.9143722120320852</v>
       </c>
       <c r="D147" t="n">
-        <v>0.8758968347662388</v>
+        <v>1.073571353694675</v>
       </c>
       <c r="E147" t="n">
-        <v>0.3816053091020118</v>
+        <v>0.2836604434320294</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0721716773937404</v>
+        <v>0.1147899680903665</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0584260726143883</v>
+        <v>0.1015449302064319</v>
       </c>
       <c r="H147" t="n">
-        <v>689.4719817910877</v>
+        <v>934.3004845834516</v>
       </c>
       <c r="I147" t="n">
-        <v>717.6191452365345</v>
+        <v>962.3793548042806</v>
       </c>
       <c r="J147" t="n">
-        <v>0.5116448620563183</v>
+        <v>0.7165216877553119</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_25_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_25_2ndlvl</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.0101471459527294</v>
+        <v>0.0166790229086178</v>
       </c>
       <c r="C148" t="n">
-        <v>0.5001015862891716</v>
+        <v>0.855406185911993</v>
       </c>
       <c r="D148" t="n">
-        <v>1.397212343146337</v>
+        <v>1.6795654236712</v>
       </c>
       <c r="E148" t="n">
-        <v>0.1631147214640558</v>
+        <v>0.0938207924713536</v>
       </c>
       <c r="F148" t="n">
-        <v>0.07487342740924779</v>
+        <v>0.1184472097142471</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0611678485560515</v>
+        <v>0.1052568936501212</v>
       </c>
       <c r="H148" t="n">
-        <v>688.270525891538</v>
+        <v>932.6113425038276</v>
       </c>
       <c r="I148" t="n">
-        <v>716.4176893369847</v>
+        <v>960.6902127246568</v>
       </c>
       <c r="J148" t="n">
-        <v>0.5116448620563183</v>
+        <v>0.7165216877553119</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_26_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_26_2ndlvl</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.0069308514424408</v>
+        <v>0.0103444933707136</v>
       </c>
       <c r="C149" t="n">
-        <v>0.5294967714339458</v>
+        <v>0.9009050342498202</v>
       </c>
       <c r="D149" t="n">
-        <v>0.8220547489242893</v>
+        <v>0.8997492853998074</v>
       </c>
       <c r="E149" t="n">
-        <v>0.4115294288178864</v>
+        <v>0.3687936784113075</v>
       </c>
       <c r="F149" t="n">
-        <v>0.0719625862055516</v>
+        <v>0.1140343042427686</v>
       </c>
       <c r="G149" t="n">
-        <v>0.0582138837789671</v>
+        <v>0.1007779596678475</v>
       </c>
       <c r="H149" t="n">
-        <v>689.5648177847789</v>
+        <v>934.6486271914504</v>
       </c>
       <c r="I149" t="n">
-        <v>717.7119812302257</v>
+        <v>962.7274974122794</v>
       </c>
       <c r="J149" t="n">
-        <v>0.5116448620563183</v>
+        <v>0.7165216877553119</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_27_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_27_2ndlvl</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.004156681967616</v>
+        <v>-0.0068554313695892</v>
       </c>
       <c r="C150" t="n">
-        <v>0.5200719306751025</v>
+        <v>0.8938615734581538</v>
       </c>
       <c r="D150" t="n">
-        <v>0.4658353067365149</v>
+        <v>-0.5620531490533871</v>
       </c>
       <c r="E150" t="n">
-        <v>0.6415838090848085</v>
+        <v>0.5743938307854936</v>
       </c>
       <c r="F150" t="n">
-        <v>0.0709118970869148</v>
+        <v>0.1129445079946795</v>
       </c>
       <c r="G150" t="n">
-        <v>0.0571476288956098</v>
+        <v>0.09967185724148279</v>
       </c>
       <c r="H150" t="n">
-        <v>690.031004867096</v>
+        <v>935.1501856931578</v>
       </c>
       <c r="I150" t="n">
-        <v>718.1781683125428</v>
+        <v>963.2290559139868</v>
       </c>
       <c r="J150" t="n">
-        <v>0.6415838090848085</v>
+        <v>0.7165216877553119</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_28_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_28_2ndlvl</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.0112224871834376</v>
+        <v>0.0044362130875679</v>
       </c>
       <c r="C151" t="n">
-        <v>0.5216675322547498</v>
+        <v>0.8901732792387991</v>
       </c>
       <c r="D151" t="n">
-        <v>1.030324278867704</v>
+        <v>0.298631233242672</v>
       </c>
       <c r="E151" t="n">
-        <v>0.3034727086360405</v>
+        <v>0.7653761208518065</v>
       </c>
       <c r="F151" t="n">
-        <v>0.0728443031560088</v>
+        <v>0.1124430833580406</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0591086632027645</v>
+        <v>0.0991629299918268</v>
       </c>
       <c r="H151" t="n">
-        <v>689.1731955769808</v>
+        <v>935.3807501321262</v>
       </c>
       <c r="I151" t="n">
-        <v>717.3203590224275</v>
+        <v>963.4596203529552</v>
       </c>
       <c r="J151" t="n">
-        <v>0.5116448620563183</v>
+        <v>0.8193047285687087</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_29_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_29_2ndlvl</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.0187756376134101</v>
+        <v>0.0075836900132988</v>
       </c>
       <c r="C152" t="n">
-        <v>0.5089285380960596</v>
+        <v>0.8854253566461817</v>
       </c>
       <c r="D152" t="n">
-        <v>1.79154517479623</v>
+        <v>0.5289952870556687</v>
       </c>
       <c r="E152" t="n">
-        <v>0.0739523302212905</v>
+        <v>0.5971014064627599</v>
       </c>
       <c r="F152" t="n">
-        <v>0.0777231483787392</v>
+        <v>0.1128647779063539</v>
       </c>
       <c r="G152" t="n">
-        <v>0.06405978761397969</v>
+        <v>0.09959093418425451</v>
       </c>
       <c r="H152" t="n">
-        <v>686.9994597505103</v>
+        <v>935.1868557938412</v>
       </c>
       <c r="I152" t="n">
-        <v>715.146623195957</v>
+        <v>963.2657260146703</v>
       </c>
       <c r="J152" t="n">
-        <v>0.5116448620563183</v>
+        <v>0.7165216877553119</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_30_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_30_2ndlvl</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.0081785042233021</v>
+        <v>0.0095393194761939</v>
       </c>
       <c r="C153" t="n">
-        <v>0.5263127862752678</v>
+        <v>0.8949050267073024</v>
       </c>
       <c r="D153" t="n">
-        <v>0.6974295697139578</v>
+        <v>0.5935994310376207</v>
       </c>
       <c r="E153" t="n">
-        <v>0.48593416589472</v>
+        <v>0.5531147369666928</v>
       </c>
       <c r="F153" t="n">
-        <v>0.071529183914989</v>
+        <v>0.1130250830183973</v>
       </c>
       <c r="G153" t="n">
-        <v>0.0577740607137295</v>
+        <v>0.099753637876528</v>
       </c>
       <c r="H153" t="n">
-        <v>689.7571807854721</v>
+        <v>935.1131236343194</v>
       </c>
       <c r="I153" t="n">
-        <v>717.9043442309188</v>
+        <v>963.1919938551486</v>
       </c>
       <c r="J153" t="n">
-        <v>0.5301099991578765</v>
+        <v>0.7165216877553119</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_38_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_38_2ndlvl</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.0107772030026874</v>
+        <v>0.0262138924879736</v>
       </c>
       <c r="C154" t="n">
-        <v>0.5161864088941669</v>
+        <v>0.8730489261606861</v>
       </c>
       <c r="D154" t="n">
-        <v>1.104939872733594</v>
+        <v>1.968169362474192</v>
       </c>
       <c r="E154" t="n">
-        <v>0.2698416294136156</v>
+        <v>0.0497370882012755</v>
       </c>
       <c r="F154" t="n">
-        <v>0.07320794313524639</v>
+        <v>0.1207394190480585</v>
       </c>
       <c r="G154" t="n">
-        <v>0.0594776904409538</v>
+        <v>0.1075834003804484</v>
       </c>
       <c r="H154" t="n">
-        <v>689.0115732517913</v>
+        <v>931.5490812196218</v>
       </c>
       <c r="I154" t="n">
-        <v>717.1587366972381</v>
+        <v>959.6279514404508</v>
       </c>
       <c r="J154" t="n">
-        <v>0.7438634825720358</v>
+        <v>0.4102122514803824</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_39_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_39_2ndlvl</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.003684852050335</v>
+        <v>0.0165699570469341</v>
       </c>
       <c r="C155" t="n">
-        <v>0.5155467330560193</v>
+        <v>0.8631272620884775</v>
       </c>
       <c r="D155" t="n">
-        <v>0.4212303760900815</v>
+        <v>1.389158369529209</v>
       </c>
       <c r="E155" t="n">
-        <v>0.6738103235238456</v>
+        <v>0.1655555239174859</v>
       </c>
       <c r="F155" t="n">
-        <v>0.0708211672155946</v>
+        <v>0.1164974372164384</v>
       </c>
       <c r="G155" t="n">
-        <v>0.0570555548780478</v>
+        <v>0.1032779474989786</v>
       </c>
       <c r="H155" t="n">
-        <v>690.0712366618887</v>
+        <v>933.5127391668808</v>
       </c>
       <c r="I155" t="n">
-        <v>718.2184001073355</v>
+        <v>961.59160938771</v>
       </c>
       <c r="J155" t="n">
-        <v>0.8984137646984608</v>
+        <v>0.4102122514803824</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_40_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_40_2ndlvl</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>5.732061447949119e-05</v>
+        <v>0.0029666511165027</v>
       </c>
       <c r="C156" t="n">
-        <v>0.5211821469180146</v>
+        <v>0.8892011399679876</v>
       </c>
       <c r="D156" t="n">
-        <v>0.0061479576575271</v>
+        <v>0.2305318718159635</v>
       </c>
       <c r="E156" t="n">
-        <v>0.9950976975260836</v>
+        <v>0.8177960639348876</v>
       </c>
       <c r="F156" t="n">
-        <v>0.0704141703318469</v>
+        <v>0.1123633340575955</v>
       </c>
       <c r="G156" t="n">
-        <v>0.0566425284108372</v>
+        <v>0.09908198743501589</v>
       </c>
       <c r="H156" t="n">
-        <v>690.2516604908662</v>
+        <v>935.4174083477964</v>
       </c>
       <c r="I156" t="n">
-        <v>718.398823936313</v>
+        <v>963.4962785686256</v>
       </c>
       <c r="J156" t="n">
-        <v>0.9950976975260836</v>
+        <v>0.8892447320010237</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_41_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_41_2ndlvl</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.0100860326288337</v>
+        <v>0.0230869339766727</v>
       </c>
       <c r="C157" t="n">
-        <v>0.5281563946043093</v>
+        <v>0.9005995175925905</v>
       </c>
       <c r="D157" t="n">
-        <v>0.9239210573975616</v>
+        <v>1.54182193724877</v>
       </c>
       <c r="E157" t="n">
-        <v>0.3560775497546823</v>
+        <v>0.1239056086875951</v>
       </c>
       <c r="F157" t="n">
-        <v>0.07236927746607159</v>
+        <v>0.1174774793757574</v>
       </c>
       <c r="G157" t="n">
-        <v>0.0586266000951987</v>
+        <v>0.1042726536307563</v>
       </c>
       <c r="H157" t="n">
-        <v>689.384228595649</v>
+        <v>933.0599061399824</v>
       </c>
       <c r="I157" t="n">
-        <v>717.5313920410957</v>
+        <v>961.1387763608116</v>
       </c>
       <c r="J157" t="n">
-        <v>0.7438634825720358</v>
+        <v>0.4102122514803824</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_42_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_42_2ndlvl</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.0069604758023373</v>
+        <v>0.0203393099762362</v>
       </c>
       <c r="C158" t="n">
-        <v>0.5144357959994993</v>
+        <v>0.867916245053483</v>
       </c>
       <c r="D158" t="n">
-        <v>0.6694844187683506</v>
+        <v>1.436305109151498</v>
       </c>
       <c r="E158" t="n">
-        <v>0.5035679972560503</v>
+        <v>0.1516952081631979</v>
       </c>
       <c r="F158" t="n">
-        <v>0.0714417096064015</v>
+        <v>0.1167894327937</v>
       </c>
       <c r="G158" t="n">
-        <v>0.0576852904894592</v>
+        <v>0.1035743120873713</v>
       </c>
       <c r="H158" t="n">
-        <v>689.7959948407168</v>
+        <v>933.3778738120192</v>
       </c>
       <c r="I158" t="n">
-        <v>717.9431582861636</v>
+        <v>961.4567440328484</v>
       </c>
       <c r="J158" t="n">
-        <v>0.7857313348221321</v>
+        <v>0.4102122514803824</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_43_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_43_2ndlvl</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.0057628406862219</v>
+        <v>0.0058780151028688</v>
       </c>
       <c r="C159" t="n">
-        <v>0.5225498576627181</v>
+        <v>0.890050908971219</v>
       </c>
       <c r="D159" t="n">
-        <v>0.4911163104116865</v>
+        <v>0.3647763183904919</v>
       </c>
       <c r="E159" t="n">
-        <v>0.623610203327433</v>
+        <v>0.7154706802848356</v>
       </c>
       <c r="F159" t="n">
-        <v>0.07096736318352539</v>
+        <v>0.1125401758717454</v>
       </c>
       <c r="G159" t="n">
-        <v>0.0572039167121702</v>
+        <v>0.0992614752613476</v>
       </c>
       <c r="H159" t="n">
-        <v>690.0064079382507</v>
+        <v>935.3361153467508</v>
       </c>
       <c r="I159" t="n">
-        <v>718.1535713836975</v>
+        <v>963.4149855675798</v>
       </c>
       <c r="J159" t="n">
-        <v>0.8803908752857877</v>
+        <v>0.8508701900506968</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_44_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_44_2ndlvl</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-0.0117174788078525</v>
+        <v>-0.0033489746452551</v>
       </c>
       <c r="C160" t="n">
-        <v>0.5136022568529233</v>
+        <v>0.8888586205077438</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.8926431704583191</v>
+        <v>-0.1864414551826451</v>
       </c>
       <c r="E160" t="n">
-        <v>0.3725783628623879</v>
+        <v>0.8521928681676477</v>
       </c>
       <c r="F160" t="n">
-        <v>0.0722393937647533</v>
+        <v>0.1123226423707536</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0584947921908978</v>
+        <v>0.0990406868950043</v>
       </c>
       <c r="H160" t="n">
-        <v>689.4419113973318</v>
+        <v>935.4361117523932</v>
       </c>
       <c r="I160" t="n">
-        <v>717.5890748427785</v>
+        <v>963.5149819732222</v>
       </c>
       <c r="J160" t="n">
-        <v>0.7438634825720358</v>
+        <v>0.8892447320010237</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_45_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_45_2ndlvl</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.0085194139685089</v>
+        <v>0.0174221586803001</v>
       </c>
       <c r="C161" t="n">
-        <v>0.5285791871846577</v>
+        <v>0.90430702184472</v>
       </c>
       <c r="D161" t="n">
-        <v>0.9155920452597204</v>
+        <v>1.371706570826362</v>
       </c>
       <c r="E161" t="n">
-        <v>0.360425730650049</v>
+        <v>0.1709217714501593</v>
       </c>
       <c r="F161" t="n">
-        <v>0.0723342572787458</v>
+        <v>0.1163917759626168</v>
       </c>
       <c r="G161" t="n">
-        <v>0.0585910610902827</v>
+        <v>0.1031707052787658</v>
       </c>
       <c r="H161" t="n">
-        <v>689.3997822469928</v>
+        <v>933.5615304389756</v>
       </c>
       <c r="I161" t="n">
-        <v>717.5469456924395</v>
+        <v>961.6404006598046</v>
       </c>
       <c r="J161" t="n">
-        <v>0.7438634825720358</v>
+        <v>0.4102122514803824</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_46_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_46_2ndlvl</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-0.0021155514123039</v>
+        <v>0.011410359590662</v>
       </c>
       <c r="C162" t="n">
-        <v>0.5212347935360171</v>
+        <v>0.8889506472012987</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.173327865771928</v>
+        <v>0.6821547175081584</v>
       </c>
       <c r="E162" t="n">
-        <v>0.8624803154121483</v>
+        <v>0.4955349533208442</v>
       </c>
       <c r="F162" t="n">
-        <v>0.07048303433956191</v>
+        <v>0.1132746831261007</v>
       </c>
       <c r="G162" t="n">
-        <v>0.0567124126260739</v>
+        <v>0.1000069726491846</v>
       </c>
       <c r="H162" t="n">
-        <v>690.2211382720166</v>
+        <v>934.998293808319</v>
       </c>
       <c r="I162" t="n">
-        <v>718.3683017174633</v>
+        <v>963.077164029148</v>
       </c>
       <c r="J162" t="n">
-        <v>0.9408876168132528</v>
+        <v>0.706211496498979</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_47_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_47_2ndlvl</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.0034939379591036</v>
+        <v>0.0073487648656615</v>
       </c>
       <c r="C163" t="n">
-        <v>0.5309176963939579</v>
+        <v>0.909970426875919</v>
       </c>
       <c r="D163" t="n">
-        <v>0.3571488607278868</v>
+        <v>0.5510561766254937</v>
       </c>
       <c r="E163" t="n">
-        <v>0.7211663900227415</v>
+        <v>0.5819020543684303</v>
       </c>
       <c r="F163" t="n">
-        <v>0.07070676576264159</v>
+        <v>0.1129174504351407</v>
       </c>
       <c r="G163" t="n">
-        <v>0.0569394585887548</v>
+        <v>0.09964439483067911</v>
       </c>
       <c r="H163" t="n">
-        <v>690.1219594029108</v>
+        <v>935.1626305920712</v>
       </c>
       <c r="I163" t="n">
-        <v>718.2691228483575</v>
+        <v>963.2415008129002</v>
       </c>
       <c r="J163" t="n">
-        <v>0.9109470189760946</v>
+        <v>0.7357984494007472</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_48_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_48_2ndlvl</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.008763890273203999</v>
+        <v>0.0095656026116787</v>
       </c>
       <c r="C164" t="n">
-        <v>0.5444103105571005</v>
+        <v>0.9163690634710516</v>
       </c>
       <c r="D164" t="n">
-        <v>0.8442413610060971</v>
+        <v>0.6747347209657524</v>
       </c>
       <c r="E164" t="n">
-        <v>0.399032945969304</v>
+        <v>0.5002331433534435</v>
       </c>
       <c r="F164" t="n">
-        <v>0.0720471510796284</v>
+        <v>0.1132524449014534</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0582997014659932</v>
+        <v>0.09998440168302131</v>
       </c>
       <c r="H164" t="n">
-        <v>689.5272736997226</v>
+        <v>935.0085259306142</v>
       </c>
       <c r="I164" t="n">
-        <v>717.6744371451693</v>
+        <v>963.0873961514432</v>
       </c>
       <c r="J164" t="n">
-        <v>0.7438634825720358</v>
+        <v>0.706211496498979</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_49_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_49_2ndlvl</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.007989767522108501</v>
+        <v>0.012019577765005</v>
       </c>
       <c r="C165" t="n">
-        <v>0.5360120506344792</v>
+        <v>0.9113206238812964</v>
       </c>
       <c r="D165" t="n">
-        <v>0.8372852392119744</v>
+        <v>0.9200456519902166</v>
       </c>
       <c r="E165" t="n">
-        <v>0.4029260530598527</v>
+        <v>0.3581020289897261</v>
       </c>
       <c r="F165" t="n">
-        <v>0.0720203969577807</v>
+        <v>0.1141157366896538</v>
       </c>
       <c r="G165" t="n">
-        <v>0.0582725509867848</v>
+        <v>0.1008606105553344</v>
       </c>
       <c r="H165" t="n">
-        <v>689.5391520395731</v>
+        <v>934.6111246499032</v>
       </c>
       <c r="I165" t="n">
-        <v>717.6863154850198</v>
+        <v>962.6899948707322</v>
       </c>
       <c r="J165" t="n">
-        <v>0.7438634825720358</v>
+        <v>0.6864912089349504</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_50_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_50_2ndlvl</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.0025520487572465</v>
+        <v>0.0182012417839028</v>
       </c>
       <c r="C166" t="n">
-        <v>0.522777864085711</v>
+        <v>0.9007929664059372</v>
       </c>
       <c r="D166" t="n">
-        <v>0.2620910368554847</v>
+        <v>1.374675543774075</v>
       </c>
       <c r="E166" t="n">
-        <v>0.7933845083076188</v>
+        <v>0.1699997262768651</v>
       </c>
       <c r="F166" t="n">
-        <v>0.0705717231299596</v>
+        <v>0.1164096589780724</v>
       </c>
       <c r="G166" t="n">
-        <v>0.0568024153244774</v>
+        <v>0.1031888558705124</v>
       </c>
       <c r="H166" t="n">
-        <v>690.1818258911721</v>
+        <v>933.5532729964332</v>
       </c>
       <c r="I166" t="n">
-        <v>718.3289893366189</v>
+        <v>961.6321432172622</v>
       </c>
       <c r="J166" t="n">
-        <v>0.9324307509476878</v>
+        <v>0.4102122514803824</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_74_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_74_2ndlvl</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.0121576018659612</v>
+        <v>0.0126132472254472</v>
       </c>
       <c r="C167" t="n">
-        <v>0.5294807484810877</v>
+        <v>0.9005415808149462</v>
       </c>
       <c r="D167" t="n">
-        <v>1.191162796938795</v>
+        <v>0.9058334447208728</v>
       </c>
       <c r="E167" t="n">
-        <v>0.2342872972710402</v>
+        <v>0.3655679598857092</v>
       </c>
       <c r="F167" t="n">
-        <v>0.0736594064764744</v>
+        <v>0.1140585258384287</v>
       </c>
       <c r="G167" t="n">
-        <v>0.0599358421279777</v>
+        <v>0.1008025436813978</v>
       </c>
       <c r="H167" t="n">
-        <v>688.8108289605213</v>
+        <v>934.6374726443072</v>
       </c>
       <c r="I167" t="n">
-        <v>716.9579924059681</v>
+        <v>962.7163428651364</v>
       </c>
       <c r="J167" t="n">
-        <v>0.5116448620563183</v>
+        <v>0.7165216877553119</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_75_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_75_2ndlvl</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.0190449787649659</v>
+        <v>0.0128638410647012</v>
       </c>
       <c r="C168" t="n">
-        <v>0.5593489380252052</v>
+        <v>0.9167457106943212</v>
       </c>
       <c r="D168" t="n">
-        <v>1.498236320431146</v>
+        <v>0.7402348231628556</v>
       </c>
       <c r="E168" t="n">
-        <v>0.1348508554200752</v>
+        <v>0.4595906943167742</v>
       </c>
       <c r="F168" t="n">
-        <v>0.0755379137124732</v>
+        <v>0.1134571137089022</v>
       </c>
       <c r="G168" t="n">
-        <v>0.0618421791008061</v>
+        <v>0.1001921328666414</v>
       </c>
       <c r="H168" t="n">
-        <v>687.9744942659188</v>
+        <v>934.9143452235392</v>
       </c>
       <c r="I168" t="n">
-        <v>716.1216577113655</v>
+        <v>962.9932154443684</v>
       </c>
       <c r="J168" t="n">
-        <v>0.5116448620563183</v>
+        <v>0.7165216877553119</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_76_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_76_2ndlvl</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.0131060523831185</v>
+        <v>0.0117141411272553</v>
       </c>
       <c r="C169" t="n">
-        <v>0.5466548312152759</v>
+        <v>0.9124428900956866</v>
       </c>
       <c r="D169" t="n">
-        <v>1.15347257122716</v>
+        <v>0.7541485536829181</v>
       </c>
       <c r="E169" t="n">
-        <v>0.2493967369609482</v>
+        <v>0.4512026397770802</v>
       </c>
       <c r="F169" t="n">
-        <v>0.0734579434635896</v>
+        <v>0.1135030171736629</v>
       </c>
       <c r="G169" t="n">
-        <v>0.0597313944778651</v>
+        <v>0.1002387231662863</v>
       </c>
       <c r="H169" t="n">
-        <v>688.9004220727813</v>
+        <v>934.8932192308836</v>
       </c>
       <c r="I169" t="n">
-        <v>717.0475855182281</v>
+        <v>962.9720894517126</v>
       </c>
       <c r="J169" t="n">
-        <v>0.5116448620563183</v>
+        <v>0.7165216877553119</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_77_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_77_2ndlvl</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.0075879068043994</v>
+        <v>0.0128121678142519</v>
       </c>
       <c r="C170" t="n">
-        <v>0.5150817164853158</v>
+        <v>0.8781694562064364</v>
       </c>
       <c r="D170" t="n">
-        <v>1.128600658517683</v>
+        <v>1.396660744479391</v>
       </c>
       <c r="E170" t="n">
-        <v>0.2597344173328737</v>
+        <v>0.1632881223651241</v>
       </c>
       <c r="F170" t="n">
-        <v>0.0733284985032181</v>
+        <v>0.1165432627594639</v>
       </c>
       <c r="G170" t="n">
-        <v>0.0596000318143769</v>
+        <v>0.1033244587109771</v>
       </c>
       <c r="H170" t="n">
-        <v>688.9579775806488</v>
+        <v>933.4915764592188</v>
       </c>
       <c r="I170" t="n">
-        <v>717.1051410260956</v>
+        <v>961.570446680048</v>
       </c>
       <c r="J170" t="n">
-        <v>0.5116448620563183</v>
+        <v>0.7165216877553119</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_78_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_78_2ndlvl</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.008406400062713501</v>
+        <v>-0.0033100509841774</v>
       </c>
       <c r="C171" t="n">
-        <v>0.5328366074735817</v>
+        <v>0.8857024947665627</v>
       </c>
       <c r="D171" t="n">
-        <v>0.7962198518882934</v>
+        <v>-0.2285892221490846</v>
       </c>
       <c r="E171" t="n">
-        <v>0.4263707183802653</v>
+        <v>0.8193047285687087</v>
       </c>
       <c r="F171" t="n">
-        <v>0.07186693507133721</v>
+        <v>0.1123613600173272</v>
       </c>
       <c r="G171" t="n">
-        <v>0.0581168155909125</v>
+        <v>0.0990799838579855</v>
       </c>
       <c r="H171" t="n">
-        <v>689.6072796898496</v>
+        <v>935.4183157095188</v>
       </c>
       <c r="I171" t="n">
-        <v>717.7544431352964</v>
+        <v>963.497185930348</v>
       </c>
       <c r="J171" t="n">
-        <v>0.5116448620563183</v>
+        <v>0.8193047285687087</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_90_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_90_2ndlvl</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.0148538667073744</v>
+        <v>0.0217447268316444</v>
       </c>
       <c r="C172" t="n">
-        <v>0.5374354113406341</v>
+        <v>0.9117889272873988</v>
       </c>
       <c r="D172" t="n">
-        <v>1.296849409877798</v>
+        <v>1.389771791493608</v>
       </c>
       <c r="E172" t="n">
-        <v>0.1954213511519041</v>
+        <v>0.1653692447397364</v>
       </c>
       <c r="F172" t="n">
-        <v>0.074258353520207</v>
+        <v>0.116501174995139</v>
       </c>
       <c r="G172" t="n">
-        <v>0.060543662461247</v>
+        <v>0.1032817412045425</v>
       </c>
       <c r="H172" t="n">
-        <v>688.544354626617</v>
+        <v>933.511013063302</v>
       </c>
       <c r="I172" t="n">
-        <v>716.6915180720637</v>
+        <v>961.589883284131</v>
       </c>
       <c r="J172" t="n">
-        <v>0.7438634825720358</v>
+        <v>0.4102122514803824</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_91_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_91_2ndlvl</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-0.0125127799757164</v>
+        <v>-0.0116300206397743</v>
       </c>
       <c r="C173" t="n">
-        <v>0.5154358813894637</v>
+        <v>0.8900951848047207</v>
       </c>
       <c r="D173" t="n">
-        <v>-1.330618710757931</v>
+        <v>-0.8951136851566914</v>
       </c>
       <c r="E173" t="n">
-        <v>0.1840631859403022</v>
+        <v>0.3712632871484344</v>
       </c>
       <c r="F173" t="n">
-        <v>0.0744602830473413</v>
+        <v>0.1140159581780583</v>
       </c>
       <c r="G173" t="n">
-        <v>0.0607485835369315</v>
+        <v>0.1007593390984282</v>
       </c>
       <c r="H173" t="n">
-        <v>688.4544763756364</v>
+        <v>934.6570757317708</v>
       </c>
       <c r="I173" t="n">
-        <v>716.6016398210832</v>
+        <v>962.7359459526</v>
       </c>
       <c r="J173" t="n">
-        <v>0.7438634825720358</v>
+        <v>0.6864912089349504</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_92_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_92_2ndlvl</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>-0.0066469232243316</v>
+        <v>-0.0019140648500231</v>
       </c>
       <c r="C174" t="n">
-        <v>0.5291536717618417</v>
+        <v>0.8928492048797319</v>
       </c>
       <c r="D174" t="n">
-        <v>-0.6380205254845007</v>
+        <v>-0.1347467634514716</v>
       </c>
       <c r="E174" t="n">
-        <v>0.5238208898814214</v>
+        <v>0.8928797049353409</v>
       </c>
       <c r="F174" t="n">
-        <v>0.07134748297754751</v>
+        <v>0.1122858890434238</v>
       </c>
       <c r="G174" t="n">
-        <v>0.0575896679105482</v>
+        <v>0.0990033836425773</v>
       </c>
       <c r="H174" t="n">
-        <v>689.8378009415278</v>
+        <v>935.45300420436</v>
       </c>
       <c r="I174" t="n">
-        <v>717.9849643869745</v>
+        <v>963.5318744251892</v>
       </c>
       <c r="J174" t="n">
-        <v>0.7857313348221321</v>
+        <v>0.8928797049353409</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_93_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_93_2ndlvl</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-0.0070920936388538</v>
+        <v>0.0108049976340313</v>
       </c>
       <c r="C175" t="n">
-        <v>0.5257501895298003</v>
+        <v>0.8823073238805728</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.7089772728738748</v>
+        <v>0.7927711529673066</v>
       </c>
       <c r="E175" t="n">
-        <v>0.4787464869458604</v>
+        <v>0.4283799441739254</v>
       </c>
       <c r="F175" t="n">
-        <v>0.07156637005878309</v>
+        <v>0.1136348920374211</v>
       </c>
       <c r="G175" t="n">
-        <v>0.0578117977633577</v>
+        <v>0.1003725712200259</v>
       </c>
       <c r="H175" t="n">
-        <v>689.7406794611547</v>
+        <v>934.8325208327484</v>
       </c>
       <c r="I175" t="n">
-        <v>717.8878429066015</v>
+        <v>962.9113910535776</v>
       </c>
       <c r="J175" t="n">
-        <v>0.7857313348221321</v>
+        <v>0.706211496498979</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_94_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_94_2ndlvl</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.0025023568643827</v>
+        <v>0.0131083230110981</v>
       </c>
       <c r="C176" t="n">
-        <v>0.5223428844296165</v>
+        <v>0.8958367328307236</v>
       </c>
       <c r="D176" t="n">
-        <v>0.2330028458265544</v>
+        <v>0.8940163315046712</v>
       </c>
       <c r="E176" t="n">
-        <v>0.8158769070792268</v>
+        <v>0.3718494048397648</v>
       </c>
       <c r="F176" t="n">
-        <v>0.0705386780415093</v>
+        <v>0.1140116290017142</v>
       </c>
       <c r="G176" t="n">
-        <v>0.0567688806791613</v>
+        <v>0.1007549451463782</v>
       </c>
       <c r="H176" t="n">
-        <v>690.1964739654327</v>
+        <v>934.659069333856</v>
       </c>
       <c r="I176" t="n">
-        <v>718.3436374108794</v>
+        <v>962.737939554685</v>
       </c>
       <c r="J176" t="n">
-        <v>0.9324307509476878</v>
+        <v>0.6864912089349504</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_95_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_95_2ndlvl</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.0100826947717857</v>
+        <v>0.0244414869580529</v>
       </c>
       <c r="C177" t="n">
-        <v>0.529085525826597</v>
+        <v>0.9088346188551626</v>
       </c>
       <c r="D177" t="n">
-        <v>0.9699606064235434</v>
+        <v>1.728250976159091</v>
       </c>
       <c r="E177" t="n">
-        <v>0.3326450307305787</v>
+        <v>0.08471304062834881</v>
       </c>
       <c r="F177" t="n">
-        <v>0.07256852653263191</v>
+        <v>0.1188092504054879</v>
       </c>
       <c r="G177" t="n">
-        <v>0.0588288009997819</v>
+        <v>0.1056243514090613</v>
       </c>
       <c r="H177" t="n">
-        <v>689.2957241606867</v>
+        <v>932.4437485223306</v>
       </c>
       <c r="I177" t="n">
-        <v>717.4428876061335</v>
+        <v>960.5226187431596</v>
       </c>
       <c r="J177" t="n">
-        <v>0.7438634825720358</v>
+        <v>0.4102122514803824</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_96_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_96_2ndlvl</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.0099692765809962</v>
+        <v>0.0243599233827075</v>
       </c>
       <c r="C178" t="n">
-        <v>0.5053025238742556</v>
+        <v>0.850345251967535</v>
       </c>
       <c r="D178" t="n">
-        <v>1.187098832109949</v>
+        <v>2.1298458921259</v>
       </c>
       <c r="E178" t="n">
-        <v>0.2358844513884258</v>
+        <v>0.0337926944216935</v>
       </c>
       <c r="F178" t="n">
-        <v>0.0736373763631558</v>
+        <v>0.1221759284691617</v>
       </c>
       <c r="G178" t="n">
-        <v>0.05991348564261</v>
+        <v>0.1090414037081017</v>
       </c>
       <c r="H178" t="n">
-        <v>688.8206269752313</v>
+        <v>930.8819580123676</v>
       </c>
       <c r="I178" t="n">
-        <v>716.9677904206781</v>
+        <v>958.9608282331966</v>
       </c>
       <c r="J178" t="n">
-        <v>0.7438634825720358</v>
+        <v>0.4102122514803824</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_97_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_97_2ndlvl</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.009385644375895201</v>
+        <v>0.0232292008929724</v>
       </c>
       <c r="C179" t="n">
-        <v>0.5315469339437706</v>
+        <v>0.911037343221624</v>
       </c>
       <c r="D179" t="n">
-        <v>0.9204615886393492</v>
+        <v>1.663869757065444</v>
       </c>
       <c r="E179" t="n">
-        <v>0.3578795276884463</v>
+        <v>0.0969196777176982</v>
       </c>
       <c r="F179" t="n">
-        <v>0.0723546935902791</v>
+        <v>0.1183326350473304</v>
       </c>
       <c r="G179" t="n">
-        <v>0.0586118001619869</v>
+        <v>0.1051406046490361</v>
       </c>
       <c r="H179" t="n">
-        <v>689.3907058601994</v>
+        <v>932.6643664714006</v>
       </c>
       <c r="I179" t="n">
-        <v>717.5378693056462</v>
+        <v>960.7432366922296</v>
       </c>
       <c r="J179" t="n">
-        <v>0.7438634825720358</v>
+        <v>0.4102122514803824</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_98_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_98_2ndlvl</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.0014060015925758</v>
+        <v>0.0111049880511872</v>
       </c>
       <c r="C180" t="n">
-        <v>0.5235662176653426</v>
+        <v>0.9064903979273492</v>
       </c>
       <c r="D180" t="n">
-        <v>0.1234020178871524</v>
+        <v>0.713208468452163</v>
       </c>
       <c r="E180" t="n">
-        <v>0.9018499757185252</v>
+        <v>0.4761316075469565</v>
       </c>
       <c r="F180" t="n">
-        <v>0.07044903482596269</v>
+        <v>0.1133703795063628</v>
       </c>
       <c r="G180" t="n">
-        <v>0.056677909415977</v>
+        <v>0.1001041008954854</v>
       </c>
       <c r="H180" t="n">
-        <v>690.2362079737438</v>
+        <v>934.9542596193789</v>
       </c>
       <c r="I180" t="n">
-        <v>718.3833714191906</v>
+        <v>963.0331298402079</v>
       </c>
       <c r="J180" t="n">
-        <v>0.9410608442280262</v>
+        <v>0.706211496498979</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>cl_p_fl-SupVentralCaudate-roi_99_2ndlvl</t>
+          <t>dawba_p-SupVentralCaudate-roi_99_2ndlvl</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>-0.0135431888805467</v>
+        <v>-0.0101977946570188</v>
       </c>
       <c r="C181" t="n">
-        <v>0.5090969083402644</v>
+        <v>0.881958818223525</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.9964335865268278</v>
+        <v>-0.5501729012341577</v>
       </c>
       <c r="E181" t="n">
-        <v>0.3196344781142125</v>
+        <v>0.5825071057755915</v>
       </c>
       <c r="F181" t="n">
-        <v>0.0726874415843668</v>
+        <v>0.1129153002999556</v>
       </c>
       <c r="G181" t="n">
-        <v>0.058949477755987</v>
+        <v>0.0996422125238951</v>
       </c>
       <c r="H181" t="n">
-        <v>689.2428942277797</v>
+        <v>935.1636195125416</v>
       </c>
       <c r="I181" t="n">
-        <v>717.3900576732265</v>
+        <v>963.2424897333708</v>
       </c>
       <c r="J181" t="n">
-        <v>0.7438634825720358</v>
+        <v>0.7357984494007472</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_100_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_100_2ndlvl</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>-0.0101121615795065</v>
+        <v>0.0139522439881877</v>
       </c>
       <c r="C182" t="n">
-        <v>0.5484310672405484</v>
+        <v>0.8568664469660563</v>
       </c>
       <c r="D182" t="n">
-        <v>-0.8361262627503594</v>
+        <v>0.8412751956490511</v>
       </c>
       <c r="E182" t="n">
-        <v>0.4035769063562986</v>
+        <v>0.4006951715192658</v>
       </c>
       <c r="F182" t="n">
-        <v>0.0720159607513805</v>
+        <v>0.1138097738942699</v>
       </c>
       <c r="G182" t="n">
-        <v>0.0582680490588083</v>
+        <v>0.1005500697630121</v>
       </c>
       <c r="H182" t="n">
-        <v>689.5411216008245</v>
+        <v>934.7520135600508</v>
       </c>
       <c r="I182" t="n">
-        <v>717.6882850462712</v>
+        <v>962.8308837808798</v>
       </c>
       <c r="J182" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.9316969624011776</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_24_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_24_2ndlvl</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.005377079689765</v>
+        <v>-8.885607302818767e-05</v>
       </c>
       <c r="C183" t="n">
-        <v>0.5323271050871137</v>
+        <v>0.8902077694138556</v>
       </c>
       <c r="D183" t="n">
-        <v>0.4188728714224459</v>
+        <v>-0.0050545182783714</v>
       </c>
       <c r="E183" t="n">
-        <v>0.6755310982873803</v>
+        <v>0.995969608612092</v>
       </c>
       <c r="F183" t="n">
-        <v>0.0708166252754709</v>
+        <v>0.112245751213824</v>
       </c>
       <c r="G183" t="n">
-        <v>0.0570509456499223</v>
+        <v>0.0989626452469486</v>
       </c>
       <c r="H183" t="n">
-        <v>690.0732505635096</v>
+        <v>935.4714514319768</v>
       </c>
       <c r="I183" t="n">
-        <v>718.2204140089564</v>
+        <v>963.550321652806</v>
       </c>
       <c r="J183" t="n">
-        <v>0.8120910914396475</v>
+        <v>0.995969608612092</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_25_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_25_2ndlvl</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.0161219264335101</v>
+        <v>-0.0048488588350244</v>
       </c>
       <c r="C184" t="n">
-        <v>0.5273455541901393</v>
+        <v>0.8872313944036854</v>
       </c>
       <c r="D184" t="n">
-        <v>1.99950690745307</v>
+        <v>-0.4375209031505928</v>
       </c>
       <c r="E184" t="n">
-        <v>0.046221093511828</v>
+        <v>0.6619691653727539</v>
       </c>
       <c r="F184" t="n">
-        <v>0.079500949895873</v>
+        <v>0.1126692778857467</v>
       </c>
       <c r="G184" t="n">
-        <v>0.0658639269313674</v>
+        <v>0.0993925089763065</v>
       </c>
       <c r="H184" t="n">
-        <v>686.2045128971122</v>
+        <v>935.2767577826515</v>
       </c>
       <c r="I184" t="n">
-        <v>714.3516763425589</v>
+        <v>963.3556280034808</v>
       </c>
       <c r="J184" t="n">
-        <v>0.2744261971121408</v>
+        <v>0.8130202856477083</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_26_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_26_2ndlvl</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.0199811103316539</v>
+        <v>0.0165254094808031</v>
       </c>
       <c r="C185" t="n">
-        <v>0.513223175363027</v>
+        <v>0.8859362632890471</v>
       </c>
       <c r="D185" t="n">
-        <v>2.053043881025138</v>
+        <v>1.241168936466169</v>
       </c>
       <c r="E185" t="n">
-        <v>0.0407101970610317</v>
+        <v>0.2152689185665817</v>
       </c>
       <c r="F185" t="n">
-        <v>0.0799889884085099</v>
+        <v>0.1156430814963458</v>
       </c>
       <c r="G185" t="n">
-        <v>0.0663591956441915</v>
+        <v>0.102410808401528</v>
       </c>
       <c r="H185" t="n">
-        <v>685.9860170832574</v>
+        <v>933.9070885646972</v>
       </c>
       <c r="I185" t="n">
-        <v>714.1331805287041</v>
+        <v>961.9859587855262</v>
       </c>
       <c r="J185" t="n">
-        <v>0.2744261971121408</v>
+        <v>0.8130202856477083</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_27_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_27_2ndlvl</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.009261985212794401</v>
+        <v>0.0059472655513406</v>
       </c>
       <c r="C186" t="n">
-        <v>0.5156235214425884</v>
+        <v>0.887676310663446</v>
       </c>
       <c r="D186" t="n">
-        <v>0.8853778656506058</v>
+        <v>0.4161581686409086</v>
       </c>
       <c r="E186" t="n">
-        <v>0.3764782266002119</v>
+        <v>0.6775169047064237</v>
       </c>
       <c r="F186" t="n">
-        <v>0.0722098591128375</v>
+        <v>0.1126289407462507</v>
       </c>
       <c r="G186" t="n">
-        <v>0.0584648199885832</v>
+        <v>0.0993515682885887</v>
       </c>
       <c r="H186" t="n">
-        <v>689.4550269390211</v>
+        <v>935.295304620312</v>
       </c>
       <c r="I186" t="n">
-        <v>717.6021903844678</v>
+        <v>963.3741748411412</v>
       </c>
       <c r="J186" t="n">
-        <v>0.7529564532004238</v>
+        <v>0.8130202856477083</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_28_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_28_2ndlvl</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.0018557928467546</v>
+        <v>0.0116502810465069</v>
       </c>
       <c r="C187" t="n">
-        <v>0.5210284468501236</v>
+        <v>0.889036900092822</v>
       </c>
       <c r="D187" t="n">
-        <v>0.1643812763543894</v>
+        <v>0.7566618755108533</v>
       </c>
       <c r="E187" t="n">
-        <v>0.869513009615261</v>
+        <v>0.4496967804813714</v>
       </c>
       <c r="F187" t="n">
-        <v>0.0704761005022518</v>
+        <v>0.1135113996306663</v>
       </c>
       <c r="G187" t="n">
-        <v>0.0567053760652481</v>
+        <v>0.1002472310465866</v>
       </c>
       <c r="H187" t="n">
-        <v>690.2242116213175</v>
+        <v>934.8893612835996</v>
       </c>
       <c r="I187" t="n">
-        <v>718.3713750667642</v>
+        <v>962.9682315044288</v>
       </c>
       <c r="J187" t="n">
-        <v>0.869513009615261</v>
+        <v>0.8130202856477083</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_29_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_29_2ndlvl</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.0038286823378451</v>
+        <v>-0.0065614856980588</v>
       </c>
       <c r="C188" t="n">
-        <v>0.5184770762648976</v>
+        <v>0.8941630151095941</v>
       </c>
       <c r="D188" t="n">
-        <v>0.3614500074170872</v>
+        <v>-0.4544190576452439</v>
       </c>
       <c r="E188" t="n">
-        <v>0.7179515575695716</v>
+        <v>0.6497731145211407</v>
       </c>
       <c r="F188" t="n">
-        <v>0.0707138554724899</v>
+        <v>0.1127026122717096</v>
       </c>
       <c r="G188" t="n">
-        <v>0.0569466533313416</v>
+        <v>0.0994263421311367</v>
       </c>
       <c r="H188" t="n">
-        <v>690.1188161845033</v>
+        <v>935.2614301436956</v>
       </c>
       <c r="I188" t="n">
-        <v>718.26597962995</v>
+        <v>963.3403003645248</v>
       </c>
       <c r="J188" t="n">
-        <v>0.8120910914396475</v>
+        <v>0.8130202856477083</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_30_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_30_2ndlvl</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>-0.00463064949265</v>
+        <v>0.0134788242598384</v>
       </c>
       <c r="C189" t="n">
-        <v>0.5302708823769319</v>
+        <v>0.8657699701827059</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.3950334412882391</v>
+        <v>0.843521093352042</v>
       </c>
       <c r="E189" t="n">
-        <v>0.693026176644632</v>
+        <v>0.3994399617910338</v>
       </c>
       <c r="F189" t="n">
-        <v>0.0707721263640127</v>
+        <v>0.1138181212712872</v>
       </c>
       <c r="G189" t="n">
-        <v>0.0570057874953314</v>
+        <v>0.1005585420384387</v>
       </c>
       <c r="H189" t="n">
-        <v>690.0929809127963</v>
+        <v>934.7481704282231</v>
       </c>
       <c r="I189" t="n">
-        <v>718.240144358243</v>
+        <v>962.8270406490524</v>
       </c>
       <c r="J189" t="n">
-        <v>0.8120910914396475</v>
+        <v>0.8130202856477083</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_38_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_38_2ndlvl</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>2.129958360098269e-05</v>
+        <v>-0.0040568403541333</v>
       </c>
       <c r="C190" t="n">
-        <v>0.5211890872701581</v>
+        <v>0.8891146061928386</v>
       </c>
       <c r="D190" t="n">
-        <v>0.0021407889262246</v>
+        <v>-0.298045811912241</v>
       </c>
       <c r="E190" t="n">
-        <v>0.9982929529327266</v>
+        <v>0.7658225622024406</v>
       </c>
       <c r="F190" t="n">
-        <v>0.0704140940956965</v>
+        <v>0.1124423103864777</v>
       </c>
       <c r="G190" t="n">
-        <v>0.0566424510452624</v>
+        <v>0.0991621454546046</v>
       </c>
       <c r="H190" t="n">
-        <v>690.2516942793468</v>
+        <v>935.3811054583643</v>
       </c>
       <c r="I190" t="n">
-        <v>718.3988577247935</v>
+        <v>963.4599756791936</v>
       </c>
       <c r="J190" t="n">
-        <v>0.9982929529327266</v>
+        <v>0.9316969624011776</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_39_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_39_2ndlvl</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.007432030417994</v>
+        <v>-0.0098300317715033</v>
       </c>
       <c r="C191" t="n">
-        <v>0.5139860614129218</v>
+        <v>0.8990685688848357</v>
       </c>
       <c r="D191" t="n">
-        <v>0.8222793066120065</v>
+        <v>-0.7947824672565321</v>
       </c>
       <c r="E191" t="n">
-        <v>0.411401791523694</v>
+        <v>0.4272101884500419</v>
       </c>
       <c r="F191" t="n">
-        <v>0.0719634309084719</v>
+        <v>0.1136419388550527</v>
       </c>
       <c r="G191" t="n">
-        <v>0.0582147409960047</v>
+        <v>0.1003797234763252</v>
       </c>
       <c r="H191" t="n">
-        <v>689.5644427807583</v>
+        <v>934.8292771208776</v>
       </c>
       <c r="I191" t="n">
-        <v>717.711606226205</v>
+        <v>962.9081473417068</v>
       </c>
       <c r="J191" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.9316969624011776</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_40_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_40_2ndlvl</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>-0.0049417446760662</v>
+        <v>-0.0147597061803238</v>
       </c>
       <c r="C192" t="n">
-        <v>0.5274391053502119</v>
+        <v>0.9047224215969044</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.4850204540769817</v>
+        <v>-1.045204530530385</v>
       </c>
       <c r="E192" t="n">
-        <v>0.6279240718720982</v>
+        <v>0.2965580881563065</v>
       </c>
       <c r="F192" t="n">
-        <v>0.0709537214628251</v>
+        <v>0.1146576509433027</v>
       </c>
       <c r="G192" t="n">
-        <v>0.057190072891904</v>
+        <v>0.1014106332516813</v>
       </c>
       <c r="H192" t="n">
-        <v>690.0124576155624</v>
+        <v>934.3614659999666</v>
       </c>
       <c r="I192" t="n">
-        <v>718.1596210610091</v>
+        <v>962.4403362207958</v>
       </c>
       <c r="J192" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.9316969624011776</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_41_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_41_2ndlvl</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-0.0025173391744402</v>
+        <v>0.0033515890153681</v>
       </c>
       <c r="C193" t="n">
-        <v>0.5219948530788836</v>
+        <v>0.8893048060282869</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.2333807247786264</v>
+        <v>0.2277708200069321</v>
       </c>
       <c r="E193" t="n">
-        <v>0.8155836907206858</v>
+        <v>0.8199405022957871</v>
       </c>
       <c r="F193" t="n">
-        <v>0.0705390824440188</v>
+        <v>0.1123605333895167</v>
       </c>
       <c r="G193" t="n">
-        <v>0.0567692910728191</v>
+        <v>0.0990791448616791</v>
       </c>
       <c r="H193" t="n">
-        <v>690.1962947069029</v>
+        <v>935.4186956659272</v>
       </c>
       <c r="I193" t="n">
-        <v>718.3434581523496</v>
+        <v>963.4975658867564</v>
       </c>
       <c r="J193" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.9316969624011776</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_42_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_42_2ndlvl</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>-0.0038007559724318</v>
+        <v>0.0076497367414644</v>
       </c>
       <c r="C194" t="n">
-        <v>0.5245955102413222</v>
+        <v>0.8833973658943264</v>
       </c>
       <c r="D194" t="n">
-        <v>-0.3254294597016824</v>
+        <v>0.4800353001817303</v>
       </c>
       <c r="E194" t="n">
-        <v>0.7450241192492861</v>
+        <v>0.6314640289210918</v>
       </c>
       <c r="F194" t="n">
-        <v>0.0706570994783178</v>
+        <v>0.1127555479955173</v>
       </c>
       <c r="G194" t="n">
-        <v>0.0568890565076263</v>
+        <v>0.0994800699106622</v>
       </c>
       <c r="H194" t="n">
-        <v>690.1439782464743</v>
+        <v>935.2370883391392</v>
       </c>
       <c r="I194" t="n">
-        <v>718.291141691921</v>
+        <v>963.3159585599684</v>
       </c>
       <c r="J194" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.9316969624011776</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_43_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_43_2ndlvl</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.0039970701672515</v>
+        <v>0.0212730382209343</v>
       </c>
       <c r="C195" t="n">
-        <v>0.5201560621527134</v>
+        <v>0.883775019242351</v>
       </c>
       <c r="D195" t="n">
-        <v>0.3150627352468206</v>
+        <v>1.232162549493176</v>
       </c>
       <c r="E195" t="n">
-        <v>0.7528762863425195</v>
+        <v>0.2186103560564756</v>
       </c>
       <c r="F195" t="n">
-        <v>0.0706418670224714</v>
+        <v>0.1155941402574733</v>
       </c>
       <c r="G195" t="n">
-        <v>0.0568735983857673</v>
+        <v>0.1023611348747922</v>
       </c>
       <c r="H195" t="n">
-        <v>690.1507311041914</v>
+        <v>933.929667087618</v>
       </c>
       <c r="I195" t="n">
-        <v>718.2978945496382</v>
+        <v>962.008537308447</v>
       </c>
       <c r="J195" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.926168348099044</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_44_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_44_2ndlvl</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.0021718663943055</v>
+        <v>-0.0016370213354605</v>
       </c>
       <c r="C196" t="n">
-        <v>0.5171522166689413</v>
+        <v>0.8935262887370916</v>
       </c>
       <c r="D196" t="n">
-        <v>0.1692154451161123</v>
+        <v>-0.09314105816501191</v>
       </c>
       <c r="E196" t="n">
-        <v>0.8657116648374283</v>
+        <v>0.925838016073619</v>
       </c>
       <c r="F196" t="n">
-        <v>0.0704798014965408</v>
+        <v>0.1122648999654589</v>
       </c>
       <c r="G196" t="n">
-        <v>0.0567091318890822</v>
+        <v>0.0989820805135706</v>
       </c>
       <c r="H196" t="n">
-        <v>690.2225711979959</v>
+        <v>935.4626508264736</v>
       </c>
       <c r="I196" t="n">
-        <v>718.3697346434426</v>
+        <v>963.5415210473026</v>
       </c>
       <c r="J196" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.9316969624011776</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_45_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_45_2ndlvl</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>-0.0012164871198924</v>
+        <v>0.0173468165247749</v>
       </c>
       <c r="C197" t="n">
-        <v>0.5237966477447842</v>
+        <v>0.8531097440642693</v>
       </c>
       <c r="D197" t="n">
-        <v>-0.1237729977716473</v>
+        <v>1.288929730276599</v>
       </c>
       <c r="E197" t="n">
-        <v>0.9015564152770624</v>
+        <v>0.1981655767159325</v>
       </c>
       <c r="F197" t="n">
-        <v>0.070449245279722</v>
+        <v>0.1159084788802544</v>
       </c>
       <c r="G197" t="n">
-        <v>0.0566781229875698</v>
+        <v>0.1026801768186124</v>
       </c>
       <c r="H197" t="n">
-        <v>690.2361146954172</v>
+        <v>933.7846285245608</v>
       </c>
       <c r="I197" t="n">
-        <v>718.3832781408639</v>
+        <v>961.86349874539</v>
       </c>
       <c r="J197" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.926168348099044</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_46_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_46_2ndlvl</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>-0.0006720649418349</v>
+        <v>0.0092651261049528</v>
       </c>
       <c r="C198" t="n">
-        <v>0.5218672066384458</v>
+        <v>0.8797010824223439</v>
       </c>
       <c r="D198" t="n">
-        <v>-0.0561166276732375</v>
+        <v>0.5649157935292263</v>
       </c>
       <c r="E198" t="n">
-        <v>0.9552765713066356</v>
+        <v>0.5724469266051617</v>
       </c>
       <c r="F198" t="n">
-        <v>0.0704213115119318</v>
+        <v>0.1129516388280693</v>
       </c>
       <c r="G198" t="n">
-        <v>0.0566497753861826</v>
+        <v>0.0996790947706339</v>
       </c>
       <c r="H198" t="n">
-        <v>690.2484954496165</v>
+        <v>935.1469058625912</v>
       </c>
       <c r="I198" t="n">
-        <v>718.3956588950632</v>
+        <v>963.2257760834202</v>
       </c>
       <c r="J198" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.9316969624011776</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_47_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_47_2ndlvl</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>-0.0074785603334739</v>
+        <v>-0.006140914497824</v>
       </c>
       <c r="C199" t="n">
-        <v>0.5105220000902753</v>
+        <v>0.8826207127279687</v>
       </c>
       <c r="D199" t="n">
-        <v>-0.6618661731441874</v>
+        <v>-0.3983775751758672</v>
       </c>
       <c r="E199" t="n">
-        <v>0.5084333960588172</v>
+        <v>0.6905639100595742</v>
       </c>
       <c r="F199" t="n">
-        <v>0.0714184805239253</v>
+        <v>0.1125969042184885</v>
       </c>
       <c r="G199" t="n">
-        <v>0.0576617172724278</v>
+        <v>0.0993190524112839</v>
       </c>
       <c r="H199" t="n">
-        <v>689.8063014228381</v>
+        <v>935.3100342728612</v>
       </c>
       <c r="I199" t="n">
-        <v>717.9534648682849</v>
+        <v>963.3889044936903</v>
       </c>
       <c r="J199" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.9316969624011776</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_48_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_48_2ndlvl</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>-0.0021279521557388</v>
+        <v>0.0220640661572967</v>
       </c>
       <c r="C200" t="n">
-        <v>0.5224210886265052</v>
+        <v>0.879178271311043</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.1768363414115162</v>
+        <v>1.344634896547305</v>
       </c>
       <c r="E200" t="n">
-        <v>0.8597253403684164</v>
+        <v>0.1795032420278699</v>
       </c>
       <c r="F200" t="n">
-        <v>0.07048585375441339</v>
+        <v>0.1162304660353825</v>
       </c>
       <c r="G200" t="n">
-        <v>0.0567152738100342</v>
+        <v>0.1030069817366601</v>
       </c>
       <c r="H200" t="n">
-        <v>690.219888589952</v>
+        <v>933.6360073867546</v>
       </c>
       <c r="I200" t="n">
-        <v>718.3670520353987</v>
+        <v>961.7148776075836</v>
       </c>
       <c r="J200" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.926168348099044</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_49_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_49_2ndlvl</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.0030731722064169</v>
+        <v>0.0213806632192561</v>
       </c>
       <c r="C201" t="n">
-        <v>0.5190846534002247</v>
+        <v>0.8719113527054587</v>
       </c>
       <c r="D201" t="n">
-        <v>0.3131216722111916</v>
+        <v>1.599534237073674</v>
       </c>
       <c r="E201" t="n">
-        <v>0.7543494088051902</v>
+        <v>0.1104894990513768</v>
       </c>
       <c r="F201" t="n">
-        <v>0.0706390696535345</v>
+        <v>0.1178739443712524</v>
       </c>
       <c r="G201" t="n">
-        <v>0.0568707595743276</v>
+        <v>0.1046750507708222</v>
       </c>
       <c r="H201" t="n">
-        <v>690.1519712227489</v>
+        <v>932.8765747695776</v>
       </c>
       <c r="I201" t="n">
-        <v>718.2991346681956</v>
+        <v>960.9554449904068</v>
       </c>
       <c r="J201" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.926168348099044</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_50_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_50_2ndlvl</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>-0.0133488836791299</v>
+        <v>0.018743460898754</v>
       </c>
       <c r="C202" t="n">
-        <v>0.5478086434282106</v>
+        <v>0.8552636067828246</v>
       </c>
       <c r="D202" t="n">
-        <v>-1.172150153817792</v>
+        <v>1.198212250738324</v>
       </c>
       <c r="E202" t="n">
-        <v>0.2418258141085746</v>
+        <v>0.2315420870247609</v>
       </c>
       <c r="F202" t="n">
-        <v>0.07355698086115579</v>
+        <v>0.1154128093012873</v>
       </c>
       <c r="G202" t="n">
-        <v>0.0598318990961358</v>
+        <v>0.1021770907372169</v>
       </c>
       <c r="H202" t="n">
-        <v>688.8563813426406</v>
+        <v>934.013311317158</v>
       </c>
       <c r="I202" t="n">
-        <v>717.0035447880873</v>
+        <v>962.0921815379872</v>
       </c>
       <c r="J202" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.926168348099044</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_74_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_74_2ndlvl</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>-0.0136951250678233</v>
+        <v>-0.0262125662493151</v>
       </c>
       <c r="C203" t="n">
-        <v>0.5194409395967763</v>
+        <v>0.8848412939004535</v>
       </c>
       <c r="D203" t="n">
-        <v>-1.200022406479718</v>
+        <v>-1.678577174219502</v>
       </c>
       <c r="E203" t="n">
-        <v>0.2308321283530972</v>
+        <v>0.09401352616744101</v>
       </c>
       <c r="F203" t="n">
-        <v>0.07370769033764051</v>
+        <v>0.1184399648746589</v>
       </c>
       <c r="G203" t="n">
-        <v>0.0599848413056055</v>
+        <v>0.105249540408943</v>
       </c>
       <c r="H203" t="n">
-        <v>688.7893536312527</v>
+        <v>932.6146955445512</v>
       </c>
       <c r="I203" t="n">
-        <v>716.9365170766994</v>
+        <v>960.6935657653804</v>
       </c>
       <c r="J203" t="n">
-        <v>0.6924963850592918</v>
+        <v>0.8130202856477083</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_75_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_75_2ndlvl</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>-0.0137263454851354</v>
+        <v>0.0084651321308524</v>
       </c>
       <c r="C204" t="n">
-        <v>0.5154621521065621</v>
+        <v>0.8941373977469579</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.9951286273273738</v>
+        <v>0.4487463670030662</v>
       </c>
       <c r="E204" t="n">
-        <v>0.3202678841599397</v>
+        <v>0.653857028841065</v>
       </c>
       <c r="F204" t="n">
-        <v>0.072681505482906</v>
+        <v>0.1126912814033103</v>
       </c>
       <c r="G204" t="n">
-        <v>0.0589434537122824</v>
+        <v>0.0994148417235594</v>
       </c>
       <c r="H204" t="n">
-        <v>689.2455315974044</v>
+        <v>935.2666403075632</v>
       </c>
       <c r="I204" t="n">
-        <v>717.3926950428511</v>
+        <v>963.3455105283922</v>
       </c>
       <c r="J204" t="n">
-        <v>0.7529564532004238</v>
+        <v>0.8130202856477083</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_76_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_76_2ndlvl</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>-0.0042934760761128</v>
+        <v>-0.0118052147206953</v>
       </c>
       <c r="C205" t="n">
-        <v>0.5133947825026404</v>
+        <v>0.8693701177418687</v>
       </c>
       <c r="D205" t="n">
-        <v>-0.3262326684231018</v>
+        <v>-0.6535246974780209</v>
       </c>
       <c r="E205" t="n">
-        <v>0.7444168338196768</v>
+        <v>0.5137926248841007</v>
       </c>
       <c r="F205" t="n">
-        <v>0.07065830024256781</v>
+        <v>0.1131902123837685</v>
       </c>
       <c r="G205" t="n">
-        <v>0.0568902750609762</v>
+        <v>0.0999212380054709</v>
       </c>
       <c r="H205" t="n">
-        <v>690.1434459185355</v>
+        <v>935.0371586301208</v>
       </c>
       <c r="I205" t="n">
-        <v>718.2906093639822</v>
+        <v>963.11602885095</v>
       </c>
       <c r="J205" t="n">
-        <v>0.8120910914396475</v>
+        <v>0.8130202856477083</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_77_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_77_2ndlvl</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.0137583128590696</v>
+        <v>-0.002193689452371</v>
       </c>
       <c r="C206" t="n">
-        <v>0.5364766529782445</v>
+        <v>0.887332090306912</v>
       </c>
       <c r="D206" t="n">
-        <v>1.825866453679205</v>
+        <v>-0.2124398450032953</v>
       </c>
       <c r="E206" t="n">
-        <v>0.06860654927803519</v>
+        <v>0.8318718481486778</v>
       </c>
       <c r="F206" t="n">
-        <v>0.0780035673443599</v>
+        <v>0.1123455960348907</v>
       </c>
       <c r="G206" t="n">
-        <v>0.06434436093464679</v>
+        <v>0.09906398400548749</v>
       </c>
       <c r="H206" t="n">
-        <v>686.8741717948574</v>
+        <v>935.4255615046354</v>
       </c>
       <c r="I206" t="n">
-        <v>715.0213352403041</v>
+        <v>963.5044317254644</v>
       </c>
       <c r="J206" t="n">
-        <v>0.2744261971121408</v>
+        <v>0.9074965616167394</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_78_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_78_2ndlvl</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.0065385443640962</v>
+        <v>0.0145996398412583</v>
       </c>
       <c r="C207" t="n">
-        <v>0.5093359600243625</v>
+        <v>0.864887280624552</v>
       </c>
       <c r="D207" t="n">
-        <v>0.5535296802412464</v>
+        <v>0.906235931702955</v>
       </c>
       <c r="E207" t="n">
-        <v>0.5802062075451173</v>
+        <v>0.3653551933343542</v>
       </c>
       <c r="F207" t="n">
-        <v>0.0711168126221918</v>
+        <v>0.1140601338855733</v>
       </c>
       <c r="G207" t="n">
-        <v>0.0573555802165947</v>
+        <v>0.1008041757890981</v>
       </c>
       <c r="H207" t="n">
-        <v>689.9401259592058</v>
+        <v>934.636732094452</v>
       </c>
       <c r="I207" t="n">
-        <v>718.0872894046526</v>
+        <v>962.715602315281</v>
       </c>
       <c r="J207" t="n">
-        <v>0.8120910914396475</v>
+        <v>0.8130202856477083</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_90_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_90_2ndlvl</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.0007855872385229</v>
+        <v>0.008521143572499499</v>
       </c>
       <c r="C208" t="n">
-        <v>0.5217237438816145</v>
+        <v>0.8967314329227477</v>
       </c>
       <c r="D208" t="n">
-        <v>0.0665389422088799</v>
+        <v>0.5298586760305264</v>
       </c>
       <c r="E208" t="n">
-        <v>0.9469815889480028</v>
+        <v>0.5965031595176238</v>
       </c>
       <c r="F208" t="n">
-        <v>0.0704242456317038</v>
+        <v>0.1128667989889427</v>
       </c>
       <c r="G208" t="n">
-        <v>0.0566527529743956</v>
+        <v>0.0995929855074805</v>
       </c>
       <c r="H208" t="n">
-        <v>690.247195011828</v>
+        <v>935.1859262820656</v>
       </c>
       <c r="I208" t="n">
-        <v>718.3943584572747</v>
+        <v>963.2647965028948</v>
       </c>
       <c r="J208" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.9316969624011776</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_91_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_91_2ndlvl</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>-0.0039280770511789</v>
+        <v>0.0167651437615289</v>
       </c>
       <c r="C209" t="n">
-        <v>0.5215292790355506</v>
+        <v>0.8815879151726128</v>
       </c>
       <c r="D209" t="n">
-        <v>-0.3993217229554099</v>
+        <v>1.24209962588937</v>
       </c>
       <c r="E209" t="n">
-        <v>0.6898666492643923</v>
+        <v>0.2149257429291828</v>
       </c>
       <c r="F209" t="n">
-        <v>0.0707799389403527</v>
+        <v>0.1156481589266549</v>
       </c>
       <c r="G209" t="n">
-        <v>0.057013715813543</v>
+        <v>0.1024159618033629</v>
       </c>
       <c r="H209" t="n">
-        <v>690.0895169670036</v>
+        <v>933.904746074386</v>
       </c>
       <c r="I209" t="n">
-        <v>718.2366804124504</v>
+        <v>961.9836162952153</v>
       </c>
       <c r="J209" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.926168348099044</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_92_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_92_2ndlvl</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>-0.00255708655088</v>
+        <v>0.0038333724458028</v>
       </c>
       <c r="C210" t="n">
-        <v>0.5224887092147192</v>
+        <v>0.8880900852038597</v>
       </c>
       <c r="D210" t="n">
-        <v>-0.2342356202451622</v>
+        <v>0.2573390065180178</v>
       </c>
       <c r="E210" t="n">
-        <v>0.8149204276071924</v>
+        <v>0.7970490810328887</v>
       </c>
       <c r="F210" t="n">
-        <v>0.0705399997621466</v>
+        <v>0.1123922791164446</v>
       </c>
       <c r="G210" t="n">
-        <v>0.0567702219808451</v>
+        <v>0.0991113655870149</v>
       </c>
       <c r="H210" t="n">
-        <v>690.1958880892087</v>
+        <v>935.4041036060956</v>
       </c>
       <c r="I210" t="n">
-        <v>718.3430515346554</v>
+        <v>963.4829738269246</v>
       </c>
       <c r="J210" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.9316969624011776</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_93_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_93_2ndlvl</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>-0.0124037227247911</v>
+        <v>-0.0053899317318923</v>
       </c>
       <c r="C211" t="n">
-        <v>0.5180259614366003</v>
+        <v>0.8891448289128534</v>
       </c>
       <c r="D211" t="n">
-        <v>-1.156638023725284</v>
+        <v>-0.3675589000129456</v>
       </c>
       <c r="E211" t="n">
-        <v>0.2481020575685061</v>
+        <v>0.7133960794663143</v>
       </c>
       <c r="F211" t="n">
-        <v>0.0734746177198818</v>
+        <v>0.1125446842035248</v>
       </c>
       <c r="G211" t="n">
-        <v>0.0597483157601763</v>
+        <v>0.0992660510494628</v>
       </c>
       <c r="H211" t="n">
-        <v>688.8930075627113</v>
+        <v>935.334042684994</v>
       </c>
       <c r="I211" t="n">
-        <v>717.040171008158</v>
+        <v>963.4129129058232</v>
       </c>
       <c r="J211" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.9316969624011776</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_94_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_94_2ndlvl</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>-0.0147192657020132</v>
+        <v>-0.0018620023704955</v>
       </c>
       <c r="C212" t="n">
-        <v>0.5249180878055275</v>
+        <v>0.890975174523686</v>
       </c>
       <c r="D212" t="n">
-        <v>-1.325113594005023</v>
+        <v>-0.1227974937587601</v>
       </c>
       <c r="E212" t="n">
-        <v>0.1858805688775623</v>
+        <v>0.9023289785310848</v>
       </c>
       <c r="F212" t="n">
-        <v>0.0744270161727108</v>
+        <v>0.1122790765569442</v>
       </c>
       <c r="G212" t="n">
-        <v>0.0607148238197139</v>
+        <v>0.0989964692236317</v>
       </c>
       <c r="H212" t="n">
-        <v>688.4692847147975</v>
+        <v>935.45613526174</v>
       </c>
       <c r="I212" t="n">
-        <v>716.6164481602442</v>
+        <v>963.5350054825692</v>
       </c>
       <c r="J212" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.9316969624011776</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_95_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_95_2ndlvl</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>-0.0098182334254228</v>
+        <v>-0.0011970094210541</v>
       </c>
       <c r="C213" t="n">
-        <v>0.5210328633196114</v>
+        <v>0.8902943326375933</v>
       </c>
       <c r="D213" t="n">
-        <v>-0.9594388510231548</v>
+        <v>-0.0857638325473634</v>
       </c>
       <c r="E213" t="n">
-        <v>0.3379101274982354</v>
+        <v>0.9316969624011776</v>
       </c>
       <c r="F213" t="n">
-        <v>0.0725221443507767</v>
+        <v>0.1122619781933988</v>
       </c>
       <c r="G213" t="n">
-        <v>0.0587817316744919</v>
+        <v>0.0989791150242228</v>
       </c>
       <c r="H213" t="n">
-        <v>689.3163283580222</v>
+        <v>935.4639936606576</v>
       </c>
       <c r="I213" t="n">
-        <v>717.463491803469</v>
+        <v>963.5428638814868</v>
       </c>
       <c r="J213" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.9316969624011776</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_96_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_96_2ndlvl</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.0068752569889755</v>
+        <v>-0.0074219261412407</v>
       </c>
       <c r="C214" t="n">
-        <v>0.5077919893432479</v>
+        <v>0.9036608122244651</v>
       </c>
       <c r="D214" t="n">
-        <v>0.7988714248894861</v>
+        <v>-0.6264649366239511</v>
       </c>
       <c r="E214" t="n">
-        <v>0.4248332001033926</v>
+        <v>0.5313664821873197</v>
       </c>
       <c r="F214" t="n">
-        <v>0.0718766125123077</v>
+        <v>0.1131136894386866</v>
       </c>
       <c r="G214" t="n">
-        <v>0.0581266364013789</v>
+        <v>0.0998435700786669</v>
       </c>
       <c r="H214" t="n">
-        <v>689.6029838333427</v>
+        <v>935.0723634903502</v>
       </c>
       <c r="I214" t="n">
-        <v>717.7501472787894</v>
+        <v>963.1512337111792</v>
       </c>
       <c r="J214" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.9316969624011776</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_97_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_97_2ndlvl</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>-0.0010193342137619</v>
+        <v>0.0075286194954785</v>
       </c>
       <c r="C215" t="n">
-        <v>0.5229936931415906</v>
+        <v>0.8768427999375424</v>
       </c>
       <c r="D215" t="n">
-        <v>-0.1001159893924491</v>
+        <v>0.5415460765948593</v>
       </c>
       <c r="E215" t="n">
-        <v>0.9203017804911112</v>
+        <v>0.5884319960662432</v>
       </c>
       <c r="F215" t="n">
-        <v>0.0704370890221957</v>
+        <v>0.1128944810518881</v>
       </c>
       <c r="G215" t="n">
-        <v>0.0566657866373393</v>
+        <v>0.0996210817658815</v>
       </c>
       <c r="H215" t="n">
-        <v>690.2415026156864</v>
+        <v>935.1731948704966</v>
       </c>
       <c r="I215" t="n">
-        <v>718.3886660611331</v>
+        <v>963.2520650913256</v>
       </c>
       <c r="J215" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.9316969624011776</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_98_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_98_2ndlvl</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>-0.0047844018187934</v>
+        <v>0.0132643653360962</v>
       </c>
       <c r="C216" t="n">
-        <v>0.5270019245719832</v>
+        <v>0.8726231267736755</v>
       </c>
       <c r="D216" t="n">
-        <v>-0.3838608646300184</v>
+        <v>0.776924614456952</v>
       </c>
       <c r="E216" t="n">
-        <v>0.7012830142207018</v>
+        <v>0.4376613038370665</v>
       </c>
       <c r="F216" t="n">
-        <v>0.0707521672573502</v>
+        <v>0.1135799929735259</v>
       </c>
       <c r="G216" t="n">
-        <v>0.0569855326981998</v>
+        <v>0.1003168507237532</v>
       </c>
       <c r="H216" t="n">
-        <v>690.1018302638179</v>
+        <v>934.8577904696458</v>
       </c>
       <c r="I216" t="n">
-        <v>718.2489937092646</v>
+        <v>962.9366606904748</v>
       </c>
       <c r="J216" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.9316969624011776</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>cl_p_fl-VRPutamen-roi_99_2ndlvl</t>
+          <t>dawba_p-VRPutamen-roi_99_2ndlvl</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>-0.009892144243347899</v>
+        <v>-0.0061369176882535</v>
       </c>
       <c r="C217" t="n">
-        <v>0.5376915697473992</v>
+        <v>0.901486189160672</v>
       </c>
       <c r="D217" t="n">
-        <v>-0.7453122008081758</v>
+        <v>-0.3362231521447384</v>
       </c>
       <c r="E217" t="n">
-        <v>0.4565153156600688</v>
+        <v>0.7368784606705749</v>
       </c>
       <c r="F217" t="n">
-        <v>0.07168733951875619</v>
+        <v>0.1124958911543211</v>
       </c>
       <c r="G217" t="n">
-        <v>0.0579345593634785</v>
+        <v>0.0992165279296976</v>
       </c>
       <c r="H217" t="n">
-        <v>689.6869947786146</v>
+        <v>935.3564742558838</v>
       </c>
       <c r="I217" t="n">
-        <v>717.8341582240613</v>
+        <v>963.4353444767128</v>
       </c>
       <c r="J217" t="n">
-        <v>0.9968103352764892</v>
+        <v>0.9316969624011776</v>
       </c>
     </row>
   </sheetData>
